--- a/tame_output/ON/bt/strategyON_20240722.xlsx
+++ b/tame_output/ON/bt/strategyON_20240722.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -48287,16 +48287,16 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.344408523803232</v>
+        <v>-3.344170349499061</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.665383011051409</v>
+        <v>2.665478280773077</v>
       </c>
       <c r="F2032" t="n">
-        <v>1.061620342171619</v>
+        <v>1.06185851647579</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.64047505018942</v>
+        <v>4.640617954771923</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240722.xlsx
+++ b/tame_output/ON/bt/strategyON_20240722.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>53.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.7%</t>
+          <t>-67.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.3%</t>
+          <t>457.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-496.0%</t>
+          <t>-506.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-109.7%</t>
+          <t>-113.9%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.5%</t>
+          <t>-131.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-117.8%</t>
+          <t>-117.6%</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.710602780646815</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.117352496412494</v>
+        <v>1.074042068544504</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.06711007596175828</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.36189621417198</v>
+        <v>-4.470172283841955</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.215267771759315</v>
+        <v>1.171957343891325</v>
       </c>
       <c r="F1925" t="n">
         <v>0.173320420843102</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.289653646000786</v>
+        <v>-4.39792971567076</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.248094112862613</v>
+        <v>1.204783684994623</v>
       </c>
       <c r="F1926" t="n">
         <v>0.173320420843102</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.236655323719398</v>
+        <v>-4.344931393389373</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.269972025692508</v>
+        <v>1.226661597824519</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2286566798450408</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.127850438239671</v>
+        <v>-4.236126507909646</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.310492051104393</v>
+        <v>1.267181623236403</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2286566798450408</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.90782964020266</v>
+        <v>-4.016105709872635</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.400079407329811</v>
+        <v>1.356768979461821</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3698765249130211</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.774961951139382</v>
+        <v>-3.883238020809357</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.469120665756946</v>
+        <v>1.425810237888956</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3698765249130211</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.654788867774883</v>
+        <v>-3.763064937444858</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518335743543047</v>
+        <v>1.475025315675057</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4900496082775201</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.510116722675146</v>
+        <v>-3.61839279234512</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586292704144382</v>
+        <v>1.542982276276392</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6347217533772576</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.569991550032838</v>
+        <v>-3.678267619702813</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.548380264602731</v>
+        <v>1.505069836734741</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5748469260195654</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.450171319122</v>
+        <v>-3.558447388791975</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.611597526201274</v>
+        <v>1.568287098333284</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5748469260195654</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.452641025583806</v>
+        <v>-3.560917095253781</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.518253842938994</v>
+        <v>1.474943415071004</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5723772195577592</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.521011211907816</v>
+        <v>-3.629287281577791</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.410167629894691</v>
+        <v>1.366857202026701</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5816529185939742</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.534799264754863</v>
+        <v>-3.643075334424838</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.395089117387764</v>
+        <v>1.351778689519774</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5816529185939742</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.590319340647453</v>
+        <v>-3.698595410317427</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.50991192372293</v>
+        <v>1.46660149585494</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5816529185939742</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.414845080854983</v>
+        <v>-3.523121150524958</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.584668859631706</v>
+        <v>1.541358431763716</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5816529185939742</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.525781333496232</v>
+        <v>-3.634057403166207</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.516036387336413</v>
+        <v>1.472725959468423</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5816529185939742</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.49211778802395</v>
+        <v>-3.600393857693925</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.458040118926776</v>
+        <v>1.414729691058786</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6153164640662561</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.432265168820227</v>
+        <v>-3.540541238490202</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.492153553040398</v>
+        <v>1.448843125172408</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6153164640662561</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.346021705793849</v>
+        <v>-3.454297775463824</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.521597208824809</v>
+        <v>1.478286780956819</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6153164640662561</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.391328525192829</v>
+        <v>-3.499604594862804</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.495250256509742</v>
+        <v>1.451939828641752</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5745063010570253</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.420361629895131</v>
+        <v>-3.528637699565106</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.484188887661923</v>
+        <v>1.440878459793933</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5745063010570253</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.327551148444272</v>
+        <v>-3.435827218114246</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.450585772133633</v>
+        <v>1.407275344265643</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6673167825078846</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.371940617773699</v>
+        <v>-3.480216687443674</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.434703460326462</v>
+        <v>1.391393032458472</v>
       </c>
       <c r="F1947" t="n">
         <v>0.622927313178457</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.259269399537449</v>
+        <v>-3.367545469207424</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.474847656132686</v>
+        <v>1.431537228264696</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7355985314147071</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.146892398354777</v>
+        <v>-3.255168468024751</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.525289752436422</v>
+        <v>1.481979324568432</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7355985314147071</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.17467279625613</v>
+        <v>-3.282948865926104</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.52567479504442</v>
+        <v>1.48236436717643</v>
       </c>
       <c r="F1950" t="n">
         <v>0.707818133513354</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.293053468986268</v>
+        <v>-3.401329538656243</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.316678245953018</v>
+        <v>1.273367818085028</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6406002813623778</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.401667547429599</v>
+        <v>-3.509943617099574</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.393382275294891</v>
+        <v>1.350071847426901</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6406002813623778</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.366258509181456</v>
+        <v>-3.474534578851431</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.422058916696471</v>
+        <v>1.378748488828481</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6406002813623778</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.327874846623305</v>
+        <v>-3.43615091629328</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.4348318230621</v>
+        <v>1.39152139519411</v>
       </c>
       <c r="F1954" t="n">
         <v>0.678983943920529</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.150758516588139</v>
+        <v>-3.259034586258114</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.502407383921468</v>
+        <v>1.459096956053478</v>
       </c>
       <c r="F1955" t="n">
         <v>0.678983943920529</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.195850761421685</v>
+        <v>-3.30412683109166</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.485053877749963</v>
+        <v>1.441743449881973</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6170879007511392</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.016475340182917</v>
+        <v>-3.124751409852892</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.550591021551885</v>
+        <v>1.507280593683895</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7738646589218579</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.061489553703523</v>
+        <v>-3.169765623373498</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.513392791475232</v>
+        <v>1.470082363607242</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7435157636072532</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.328494063975959</v>
+        <v>-3.436770133645934</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.412282549705203</v>
+        <v>1.368972121837214</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5491527255643047</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.429691845413132</v>
+        <v>-3.537967915083106</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.371007359026836</v>
+        <v>1.327696931158846</v>
       </c>
       <c r="F1960" t="n">
         <v>0.4807439120189855</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.423180878798819</v>
+        <v>-3.531456948468794</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.371211707226877</v>
+        <v>1.327901279358888</v>
       </c>
       <c r="F1961" t="n">
         <v>0.4807439120189855</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.404142751091522</v>
+        <v>-3.512418820761496</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.375351677518041</v>
+        <v>1.332041249650051</v>
       </c>
       <c r="F1962" t="n">
         <v>0.422560300687791</v>
@@ -46700,10 +46700,10 @@
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.43526938224214</v>
+        <v>-3.543545451912114</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.540482893996475</v>
+        <v>1.497172466128485</v>
       </c>
       <c r="F1963" t="n">
         <v>0.422560300687791</v>
@@ -46723,10 +46723,10 @@
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.449136143576057</v>
+        <v>-3.557412213246032</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.535769518449041</v>
+        <v>1.492459090581051</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3847023839539681</v>
@@ -46746,10 +46746,10 @@
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.404331972036127</v>
+        <v>-3.512608041706102</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.559699717461939</v>
+        <v>1.516389289593949</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3847023839539681</v>
@@ -46769,10 +46769,10 @@
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.256589001801125</v>
+        <v>-3.3648650714711</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.516747126833139</v>
+        <v>1.47343669896515</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5525097411888512</v>
@@ -46792,10 +46792,10 @@
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.358603684332346</v>
+        <v>-3.466879754002321</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.478734875352132</v>
+        <v>1.435424447484142</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5525097411888512</v>
@@ -46815,10 +46815,10 @@
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.352450978279562</v>
+        <v>-3.460727047949536</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.481858306164904</v>
+        <v>1.438547878296914</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5586624472416355</v>
@@ -46838,10 +46838,10 @@
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.369260276430063</v>
+        <v>-3.477536346100038</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.474215063644814</v>
+        <v>1.430904635776824</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5418531490911338</v>
@@ -46861,10 +46861,10 @@
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.306962277653941</v>
+        <v>-3.415238347323916</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.565469816952084</v>
+        <v>1.522159389084094</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5418531490911338</v>
@@ -46884,10 +46884,10 @@
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.105172079988783</v>
+        <v>-3.213448149658758</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.448477897732274</v>
+        <v>1.405167469864284</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7398713412602882</v>
@@ -46907,10 +46907,10 @@
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.940359076909936</v>
+        <v>-3.048635146579911</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.584693331285988</v>
+        <v>1.541382903417998</v>
       </c>
       <c r="F1972" t="n">
         <v>0.9046843443391351</v>
@@ -46930,10 +46930,10 @@
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.038099621534911</v>
+        <v>-3.146375691204885</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.560224849552042</v>
+        <v>1.516914421684052</v>
       </c>
       <c r="F1973" t="n">
         <v>0.888795066206155</v>
@@ -46953,10 +46953,10 @@
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.21443738165784</v>
+        <v>-3.322713451327814</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.488225726327542</v>
+        <v>1.444915298459552</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7124573060832255</v>
@@ -46976,10 +46976,10 @@
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.138015335225913</v>
+        <v>-3.246291404895888</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.517286162940241</v>
+        <v>1.473975735072251</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7124573060832255</v>
@@ -46999,10 +46999,10 @@
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.093642203587344</v>
+        <v>-3.201918273257319</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.534898283031104</v>
+        <v>1.491587855163115</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7568304377217941</v>
@@ -47022,10 +47022,10 @@
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.970807982700177</v>
+        <v>-3.079084052370152</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.578425765524562</v>
+        <v>1.535115337656572</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7568304377217941</v>
@@ -47045,10 +47045,10 @@
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.923152252139121</v>
+        <v>-3.031428321809096</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.603869814776789</v>
+        <v>1.560559386908799</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8044861682828498</v>
@@ -47068,10 +47068,10 @@
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.822634093640366</v>
+        <v>-2.930910163310341</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.648969451551016</v>
+        <v>1.605659023683026</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9050043267816044</v>
@@ -47091,10 +47091,10 @@
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.883300684042756</v>
+        <v>-2.99157675371273</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.611457487865932</v>
+        <v>1.568147059997942</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8233060100630707</v>
@@ -47114,10 +47114,10 @@
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.838462282434357</v>
+        <v>-2.946738352104332</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.63349055111992</v>
+        <v>1.59018012325193</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8278494430079402</v>
@@ -47137,10 +47137,10 @@
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.857960738676366</v>
+        <v>-2.96623680834634</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.629852108254195</v>
+        <v>1.586541680386205</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7797648017280359</v>
@@ -47160,10 +47160,10 @@
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.813757901590465</v>
+        <v>-2.92203397126044</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.653412845616392</v>
+        <v>1.610102417748402</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8239676388139363</v>
@@ -47183,10 +47183,10 @@
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.850736929253908</v>
+        <v>-2.959012998923883</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.637031235020262</v>
+        <v>1.593720807152273</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8609415406052668</v>
@@ -47206,10 +47206,10 @@
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.692445511714636</v>
+        <v>-2.800721581384611</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.751595567219011</v>
+        <v>1.708285139351021</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8609415406052668</v>
@@ -47229,10 +47229,10 @@
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.48480350808016</v>
+        <v>-2.593079577750135</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.833093073267055</v>
+        <v>1.789782645399065</v>
       </c>
       <c r="F1986" t="n">
         <v>1.068583544239743</v>
@@ -47252,10 +47252,10 @@
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.433771415357632</v>
+        <v>-2.542047485027607</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.848454138594336</v>
+        <v>1.805143710726346</v>
       </c>
       <c r="F1987" t="n">
         <v>1.119615636962271</v>
@@ -47275,10 +47275,10 @@
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.368547234230427</v>
+        <v>-2.476823303900401</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.891731215137923</v>
+        <v>1.848420787269933</v>
       </c>
       <c r="F1988" t="n">
         <v>1.184839818089477</v>
@@ -47298,10 +47298,10 @@
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.331120214159293</v>
+        <v>-2.439396283829268</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.902662995465657</v>
+        <v>1.859352567597667</v>
       </c>
       <c r="F1989" t="n">
         <v>1.190091356118658</v>
@@ -47321,10 +47321,10 @@
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.351231870194001</v>
+        <v>-2.459507939863976</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.895875125383014</v>
+        <v>1.852564697515024</v>
       </c>
       <c r="F1990" t="n">
         <v>1.201118701116078</v>
@@ -47344,10 +47344,10 @@
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.297487055766796</v>
+        <v>-2.405763125436771</v>
       </c>
       <c r="E1991" t="n">
-        <v>2.077930822175106</v>
+        <v>2.034620394307117</v>
       </c>
       <c r="F1991" t="n">
         <v>1.21118201055654</v>
@@ -47367,10 +47367,10 @@
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.222704794741784</v>
+        <v>-2.330980864411758</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.227956635802929</v>
+        <v>2.184646207934939</v>
       </c>
       <c r="F1992" t="n">
         <v>1.285964271581552</v>
@@ -47390,10 +47390,10 @@
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.196620710477976</v>
+        <v>-2.304896780147951</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.230098245522311</v>
+        <v>2.186787817654321</v>
       </c>
       <c r="F1993" t="n">
         <v>1.285964271581552</v>
@@ -47413,10 +47413,10 @@
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.118489529629029</v>
+        <v>-2.226765599299004</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.259543913445669</v>
+        <v>2.216233485577679</v>
       </c>
       <c r="F1994" t="n">
         <v>1.360141082465237</v>
@@ -47436,10 +47436,10 @@
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.109597068235746</v>
+        <v>-2.217873137905721</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.280655303729774</v>
+        <v>2.237344875861784</v>
       </c>
       <c r="F1995" t="n">
         <v>1.360141082465237</v>
@@ -47459,10 +47459,10 @@
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.278073185205624</v>
+        <v>-2.386349254875598</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.205119904346406</v>
+        <v>2.161809476478417</v>
       </c>
       <c r="F1996" t="n">
         <v>1.332193246748656</v>
@@ -47482,10 +47482,10 @@
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.58027365634404</v>
+        <v>-1.688549726014015</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.465509413078902</v>
+        <v>2.422198985210912</v>
       </c>
       <c r="F1997" t="n">
         <v>1.261845187378245</v>
@@ -47505,10 +47505,10 @@
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.557552552660888</v>
+        <v>-1.665828622330863</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.465261877049067</v>
+        <v>2.421951449181077</v>
       </c>
       <c r="F1998" t="n">
         <v>1.261845187378245</v>
@@ -47528,10 +47528,10 @@
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.555827509370844</v>
+        <v>-1.664103579040819</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.624858020216254</v>
+        <v>2.581547592348264</v>
       </c>
       <c r="F1999" t="n">
         <v>1.263570230668289</v>
@@ -47551,10 +47551,10 @@
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.7106085161491</v>
+        <v>-1.818884585819074</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.600023439998598</v>
+        <v>2.556713012130608</v>
       </c>
       <c r="F2000" t="n">
         <v>1.230202556613813</v>
@@ -47574,10 +47574,10 @@
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.703553825933926</v>
+        <v>-1.811829895603901</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.599520672074213</v>
+        <v>2.556210244206223</v>
       </c>
       <c r="F2001" t="n">
         <v>1.237257246828987</v>
@@ -47597,10 +47597,10 @@
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.676602601607438</v>
+        <v>-1.784878671277413</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.62030731544955</v>
+        <v>2.57699688758156</v>
       </c>
       <c r="F2002" t="n">
         <v>1.252137592856706</v>
@@ -47620,10 +47620,10 @@
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.812555609663754</v>
+        <v>-1.920831679333729</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.750029244371983</v>
+        <v>2.706718816503993</v>
       </c>
       <c r="F2003" t="n">
         <v>1.252137592856706</v>
@@ -47643,10 +47643,10 @@
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.834963727468626</v>
+        <v>-1.943239797138601</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.733182692153027</v>
+        <v>2.689872264285037</v>
       </c>
       <c r="F2004" t="n">
         <v>1.252137592856706</v>
@@ -47666,10 +47666,10 @@
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.982969494948025</v>
+        <v>-2.091245564618</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.676034384710905</v>
+        <v>2.632723956842915</v>
       </c>
       <c r="F2005" t="n">
         <v>1.165410583993165</v>
@@ -47689,10 +47689,10 @@
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.992410420836555</v>
+        <v>-2.10068649050653</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.72851173207734</v>
+        <v>2.68520130420935</v>
       </c>
       <c r="F2006" t="n">
         <v>1.287837701536556</v>
@@ -47712,10 +47712,10 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.044684028172196</v>
+        <v>-2.152960097842171</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.710493383688385</v>
+        <v>2.667182955820394</v>
       </c>
       <c r="F2007" t="n">
         <v>1.235564094200915</v>
@@ -47735,10 +47735,10 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.121014005773102</v>
+        <v>-2.229290075443077</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.678073205541797</v>
+        <v>2.634762777673807</v>
       </c>
       <c r="F2008" t="n">
         <v>1.235564094200915</v>
@@ -47758,10 +47758,10 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.232770958388403</v>
+        <v>-2.341047028058378</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.628190654098539</v>
+        <v>2.584880226230549</v>
       </c>
       <c r="F2009" t="n">
         <v>1.123807141585614</v>
@@ -47781,10 +47781,10 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.230929939330152</v>
+        <v>-2.339206009000127</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.627361071931992</v>
+        <v>2.584050644064002</v>
       </c>
       <c r="F2010" t="n">
         <v>1.125075368257082</v>
@@ -47804,10 +47804,10 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.363231231427705</v>
+        <v>-2.47150730109768</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.587513961958889</v>
+        <v>2.544203534090899</v>
       </c>
       <c r="F2011" t="n">
         <v>1.125075368257082</v>
@@ -47827,10 +47827,10 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.364792874242565</v>
+        <v>-2.473068943912541</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.586889304832945</v>
+        <v>2.543578876964955</v>
       </c>
       <c r="F2012" t="n">
         <v>1.125075368257082</v>
@@ -47850,10 +47850,10 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.392693661352038</v>
+        <v>-2.500969731022014</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.574253031116158</v>
+        <v>2.530942603248168</v>
       </c>
       <c r="F2013" t="n">
         <v>1.090478444114147</v>
@@ -47873,10 +47873,10 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.515219764054932</v>
+        <v>-2.623495833724907</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.5220070340122</v>
+        <v>2.478696606144209</v>
       </c>
       <c r="F2014" t="n">
         <v>0.9679523414112534</v>
@@ -47896,10 +47896,10 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.535281085331439</v>
+        <v>-2.643557155001414</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.5806884650921</v>
+        <v>2.53737803722411</v>
       </c>
       <c r="F2015" t="n">
         <v>0.9478910201347464</v>
@@ -47919,10 +47919,10 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.792001903326263</v>
+        <v>-2.900277972996238</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.618311856896018</v>
+        <v>2.575001429028028</v>
       </c>
       <c r="F2016" t="n">
         <v>0.8394764459909315</v>
@@ -47942,10 +47942,10 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.945988321102403</v>
+        <v>-3.054264390772379</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.625697558931201</v>
+        <v>2.582387131063211</v>
       </c>
       <c r="F2017" t="n">
         <v>0.8394764459909315</v>
@@ -47965,10 +47965,10 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.895466417274737</v>
+        <v>-3.003742486944713</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.631957522582389</v>
+        <v>2.588647094714398</v>
       </c>
       <c r="F2018" t="n">
         <v>0.8394764459909315</v>
@@ -47988,10 +47988,10 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.147941571282462</v>
+        <v>-3.256217640952437</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.542837950034713</v>
+        <v>2.499527522166723</v>
       </c>
       <c r="F2019" t="n">
         <v>0.8394764459909315</v>
@@ -48011,10 +48011,10 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.41741437320417</v>
+        <v>-3.525690442874145</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.436259363784973</v>
+        <v>2.392948935916983</v>
       </c>
       <c r="F2020" t="n">
         <v>0.8394764459909315</v>
@@ -48034,10 +48034,10 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.574958444933611</v>
+        <v>-3.683234514603587</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.377363477320518</v>
+        <v>2.334053049452528</v>
       </c>
       <c r="F2021" t="n">
         <v>0.7725746408506571</v>
@@ -48057,10 +48057,10 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.703808995635657</v>
+        <v>-3.812085065305633</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.320901109775889</v>
+        <v>2.277590681907899</v>
       </c>
       <c r="F2022" t="n">
         <v>0.7315812319999355</v>
@@ -48080,10 +48080,10 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.820776688274548</v>
+        <v>-3.929052757944524</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.436318089419377</v>
+        <v>2.393007661551387</v>
       </c>
       <c r="F2023" t="n">
         <v>0.7315812319999355</v>
@@ -48103,10 +48103,10 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.905494630495502</v>
+        <v>-4.013770700165478</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.39727755049481</v>
+        <v>2.353967122626819</v>
       </c>
       <c r="F2024" t="n">
         <v>0.6464652030718891</v>
@@ -48126,10 +48126,10 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.987429448764386</v>
+        <v>-4.095705518434361</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.374733040755748</v>
+        <v>2.331422612887757</v>
       </c>
       <c r="F2025" t="n">
         <v>0.636530457484809</v>
@@ -48149,10 +48149,10 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.933691275364124</v>
+        <v>-4.041967345034099</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.405153948571755</v>
+        <v>2.361843520703764</v>
       </c>
       <c r="F2026" t="n">
         <v>0.6902686308850711</v>
@@ -48172,10 +48172,10 @@
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.823684991886902</v>
+        <v>-3.931961061556877</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.441309349206819</v>
+        <v>2.397998921338829</v>
       </c>
       <c r="F2027" t="n">
         <v>0.7134732028023463</v>
@@ -48195,10 +48195,10 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.680625416145976</v>
+        <v>-3.788901485815952</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.502783190225164</v>
+        <v>2.459472762357174</v>
       </c>
       <c r="F2028" t="n">
         <v>0.7214866293923256</v>
@@ -48218,10 +48218,10 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.379178690674139</v>
+        <v>-3.487454760344114</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.630622763296435</v>
+        <v>2.587312335428445</v>
       </c>
       <c r="F2029" t="n">
         <v>1.022933354864163</v>
@@ -48241,10 +48241,10 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.434133887117208</v>
+        <v>-3.542409956787183</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.609611862471918</v>
+        <v>2.566301434603927</v>
       </c>
       <c r="F2030" t="n">
         <v>1.022933354864163</v>
@@ -48264,10 +48264,10 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.383095511110688</v>
+        <v>-3.491371580780663</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.630870117254281</v>
+        <v>2.587559689386291</v>
       </c>
       <c r="F2031" t="n">
         <v>1.022933354864163</v>
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.769877042536676</v>
+        <v>3.810790926480911</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.344170349499061</v>
+        <v>-3.450232285914032</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.665478280773077</v>
+        <v>2.623053506207089</v>
       </c>
       <c r="F2032" t="n">
-        <v>1.06185851647579</v>
+        <v>1.064072649730794</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.640617954771923</v>
+        <v>4.641946434724925</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240722.xlsx
+++ b/tame_output/ON/bt/strategyON_20240722.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>110.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.4%</t>
+          <t>122.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-47.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.2%</t>
+          <t>-66.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.1%</t>
+          <t>456.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-506.6%</t>
+          <t>-497.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-113.9%</t>
+          <t>-110.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1298,57 +1298,57 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.4%</t>
+          <t>-133.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-117.6%</t>
+          <t>-98.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>100.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -44383,10 +44383,10 @@
         <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3846419795235408</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>2.83837196775276</v>
       </c>
     </row>
     <row r="1863">
@@ -44406,10 +44406,10 @@
         <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.7613982729162152</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.659840012179184</v>
       </c>
     </row>
     <row r="1864">
@@ -44429,10 +44429,10 @@
         <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.169987050096894</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.413448289885536</v>
       </c>
     </row>
     <row r="1865">
@@ -44452,10 +44452,10 @@
         <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.169987050096894</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.408633722356996</v>
       </c>
     </row>
     <row r="1866">
@@ -44475,10 +44475,10 @@
         <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.169987050096894</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.406627772965874</v>
       </c>
     </row>
     <row r="1867">
@@ -44498,10 +44498,10 @@
         <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.169987050096894</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.416886463634553</v>
       </c>
     </row>
     <row r="1868">
@@ -44521,10 +44521,10 @@
         <v>0.3165746066023623</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.169987050096894</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.412986028780248</v>
       </c>
     </row>
     <row r="1869">
@@ -44544,10 +44544,10 @@
         <v>0.2956983997604259</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.169987050096894</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.411390948835249</v>
       </c>
     </row>
     <row r="1870">
@@ -44567,10 +44567,10 @@
         <v>0.1808128389655548</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.238730185830772</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.37392404332413</v>
       </c>
     </row>
     <row r="1871">
@@ -44590,10 +44590,10 @@
         <v>0.1020986511074309</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.238730185830772</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.369897738789727</v>
       </c>
     </row>
     <row r="1872">
@@ -44613,10 +44613,10 @@
         <v>-0.05120400571120598</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.238730185830772</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.369795637468143</v>
       </c>
     </row>
     <row r="1873">
@@ -44636,10 +44636,10 @@
         <v>-0.05042706782033113</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.243216631032161</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.36967528631874</v>
       </c>
     </row>
     <row r="1874">
@@ -44659,10 +44659,10 @@
         <v>-0.1888888935238819</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.243216631032161</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.37502558961679</v>
       </c>
     </row>
     <row r="1875">
@@ -44682,10 +44682,10 @@
         <v>-0.2011124989483934</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.293565694486383</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.352732171501434</v>
       </c>
     </row>
     <row r="1876">
@@ -44705,10 +44705,10 @@
         <v>-0.2371184592951829</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.39118497190778</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.297202355670365</v>
       </c>
     </row>
     <row r="1877">
@@ -44728,10 +44728,10 @@
         <v>-0.255853502776954</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.445256471416139</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.267653012286921</v>
       </c>
     </row>
     <row r="1878">
@@ -44751,10 +44751,10 @@
         <v>-0.3320435757902573</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.572895416030128</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.196582842637171</v>
       </c>
     </row>
     <row r="1879">
@@ -44774,10 +44774,10 @@
         <v>-0.3410221567092107</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.673308783947165</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.140817376371384</v>
       </c>
     </row>
     <row r="1880">
@@ -44797,10 +44797,10 @@
         <v>-0.29626252254881</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.599838952279717</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.200270976865274</v>
       </c>
     </row>
     <row r="1881">
@@ -44820,10 +44820,10 @@
         <v>-0.3517570687559104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.774963369666261</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.109751547180865</v>
       </c>
     </row>
     <row r="1882">
@@ -44843,10 +44843,10 @@
         <v>-0.4527570712633024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.774963369666261</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.102532382279269</v>
       </c>
     </row>
     <row r="1883">
@@ -44866,10 +44866,10 @@
         <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.879338100692707</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.033235352889425</v>
       </c>
     </row>
     <row r="1884">
@@ -44889,10 +44889,10 @@
         <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.975013587275104</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>1.976945850778543</v>
       </c>
     </row>
     <row r="1885">
@@ -44912,10 +44912,10 @@
         <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.949761964465361</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>1.994790553093504</v>
       </c>
     </row>
     <row r="1886">
@@ -44935,10 +44935,10 @@
         <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.949761964465361</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>1.998780888779904</v>
       </c>
     </row>
     <row r="1887">
@@ -44958,10 +44958,10 @@
         <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.949761964465361</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>1.997305661881162</v>
       </c>
     </row>
     <row r="1888">
@@ -44981,10 +44981,10 @@
         <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.900171120040528</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.042113578700935</v>
       </c>
     </row>
     <row r="1889">
@@ -45004,10 +45004,10 @@
         <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.868921529305354</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.047812199495356</v>
       </c>
     </row>
     <row r="1890">
@@ -45027,10 +45027,10 @@
         <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.826994853718191</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.082547277883863</v>
       </c>
     </row>
     <row r="1891">
@@ -45050,10 +45050,10 @@
         <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.826994853718191</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.083686422439921</v>
       </c>
     </row>
     <row r="1892">
@@ -45073,10 +45073,10 @@
         <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.822039507629745</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.089293404255097</v>
       </c>
     </row>
     <row r="1893">
@@ -45096,10 +45096,10 @@
         <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.822039507629745</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.095027108493733</v>
       </c>
     </row>
     <row r="1894">
@@ -45119,10 +45119,10 @@
         <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.750673115020097</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.128109681665657</v>
       </c>
     </row>
     <row r="1895">
@@ -45142,10 +45142,10 @@
         <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.750673115020097</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.118226200352749</v>
       </c>
     </row>
     <row r="1896">
@@ -45165,10 +45165,10 @@
         <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.750673115020097</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.116391639853376</v>
       </c>
     </row>
     <row r="1897">
@@ -45188,10 +45188,10 @@
         <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.68268736515954</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.156882774796249</v>
       </c>
     </row>
     <row r="1898">
@@ -45211,10 +45211,10 @@
         <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.658733824183583</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.171923405527317</v>
       </c>
     </row>
     <row r="1899">
@@ -45234,10 +45234,10 @@
         <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.394673885860787</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.317099052359243</v>
       </c>
     </row>
     <row r="1900">
@@ -45257,10 +45257,10 @@
         <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.394673885860787</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.314312018698942</v>
       </c>
     </row>
     <row r="1901">
@@ -45280,10 +45280,10 @@
         <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.354489587494596</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.338766221606497</v>
       </c>
     </row>
     <row r="1902">
@@ -45303,10 +45303,10 @@
         <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.191089716555233</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.436172965390872</v>
       </c>
     </row>
     <row r="1903">
@@ -45326,10 +45326,10 @@
         <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.9576084943256347</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.584186127566483</v>
       </c>
     </row>
     <row r="1904">
@@ -45349,10 +45349,10 @@
         <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.8647050030830987</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.637036011999045</v>
       </c>
     </row>
     <row r="1905">
@@ -45372,10 +45372,10 @@
         <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.7324295294522121</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.711768782924605</v>
       </c>
     </row>
     <row r="1906">
@@ -45395,10 +45395,10 @@
         <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5766911968924705</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.808026843148086</v>
       </c>
     </row>
     <row r="1907">
@@ -45418,10 +45418,10 @@
         <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5766911968924705</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.820933184371745</v>
       </c>
     </row>
     <row r="1908">
@@ -45441,10 +45441,10 @@
         <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.6822811866655749</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.629603260908664</v>
       </c>
     </row>
     <row r="1909">
@@ -45464,10 +45464,10 @@
         <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.6878771963257062</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.674789996989671</v>
       </c>
     </row>
     <row r="1910">
@@ -45487,10 +45487,10 @@
         <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.6675562804171487</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.567103623846638</v>
       </c>
     </row>
     <row r="1911">
@@ -45510,10 +45510,10 @@
         <v>0.5089641519027821</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6145867581631598</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.590171350945553</v>
       </c>
     </row>
     <row r="1912">
@@ -45533,10 +45533,10 @@
         <v>0.5194229025159651</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6145867581631598</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.58321073885046</v>
       </c>
     </row>
     <row r="1913">
@@ -45556,10 +45556,10 @@
         <v>0.5472305394886159</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6145867581631598</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.597673093231603</v>
       </c>
     </row>
     <row r="1914">
@@ -45579,10 +45579,10 @@
         <v>0.5850663147968196</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6145867581631598</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.592205213690798</v>
       </c>
     </row>
     <row r="1915">
@@ -45602,10 +45602,10 @@
         <v>0.6318808627342487</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.4912956233460293</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.663677988591654</v>
       </c>
     </row>
     <row r="1916">
@@ -45625,10 +45625,10 @@
         <v>0.6480415205329515</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4701464244425859</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.684068486171045</v>
       </c>
     </row>
     <row r="1917">
@@ -45648,10 +45648,10 @@
         <v>0.7413284056733795</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4701464244425859</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.679849194518095</v>
       </c>
     </row>
     <row r="1918">
@@ -45671,10 +45671,10 @@
         <v>0.7841578477043138</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4569273560501572</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.689904949473569</v>
       </c>
     </row>
     <row r="1919">
@@ -45694,10 +45694,10 @@
         <v>0.8768400802676455</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4569273560501572</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.682647024457271</v>
       </c>
     </row>
     <row r="1920">
@@ -45717,10 +45717,10 @@
         <v>0.9507960407752671</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4569273560501572</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.686246147977919</v>
       </c>
     </row>
     <row r="1921">
@@ -45740,10 +45740,10 @@
         <v>1.032702132038806</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.2854808930276941</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.802441531845951</v>
       </c>
     </row>
     <row r="1922">
@@ -45763,10 +45763,10 @@
         <v>1.061438435950439</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.2111913272893548</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.846035748905252</v>
       </c>
     </row>
     <row r="1923">
@@ -45786,10 +45786,10 @@
         <v>1.09158753389833</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1475555850554203</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.88891199529993</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.710602780646815</v>
+        <v>-4.602326710976841</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.074042068544504</v>
+        <v>1.117352496412494</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1475555850554203</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.870106254083725</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.470172283841955</v>
+        <v>-4.36189621417198</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.171957343891325</v>
+        <v>1.215267771759315</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.09287491174944001</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>3.016107628791519</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.39792971567076</v>
+        <v>-4.289653646000786</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.204783684994623</v>
+        <v>1.248094112862613</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.09287491174944001</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>3.020036942626339</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.344931393389373</v>
+        <v>-4.236655323719398</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.226661597824519</v>
+        <v>1.269972025692508</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1482111707513789</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>3.053917281944842</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.236126507909646</v>
+        <v>-4.127850438239671</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.267181623236403</v>
+        <v>1.310492051104393</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1482111707513789</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>3.050915353164836</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.016105709872635</v>
+        <v>-3.90782964020266</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.356768979461821</v>
+        <v>1.400079407329811</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.2894310158193591</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.137226297216238</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.883238020809357</v>
+        <v>-3.774961951139382</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.425810237888956</v>
+        <v>1.469120665756946</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.2894310158193591</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.153120480018061</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.763064937444858</v>
+        <v>-3.654788867774883</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.475025315675057</v>
+        <v>1.518335743543047</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.409604099183858</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.226370174477063</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.61839279234512</v>
+        <v>-3.510116722675146</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.542982276276392</v>
+        <v>1.586292704144382</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.5542762442835955</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.323261564098345</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.678267619702813</v>
+        <v>-3.569991550032838</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.505069836734741</v>
+        <v>1.548380264602731</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.4944014169259033</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.273374159085156</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.558447388791975</v>
+        <v>-3.450171319122</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.568287098333284</v>
+        <v>1.611597526201274</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.4944014169259033</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.288663328319364</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.560917095253781</v>
+        <v>-3.452641025583806</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.474943415071004</v>
+        <v>1.518253842938994</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.4919317104640972</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.194825703764722</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.629287281577791</v>
+        <v>-3.521011211907816</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.366857202026701</v>
+        <v>1.410167629894691</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5012074095003122</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.119652984671752</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.643075334424838</v>
+        <v>-3.534799264754863</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.351778689519774</v>
+        <v>1.395089117387764</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5012074095003122</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.110089693303644</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.698595410317427</v>
+        <v>-3.590319340647453</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.46660149585494</v>
+        <v>1.50991192372293</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5012074095003122</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.295387835452043</v>
+        <v>3.247120529995846</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.523121150524958</v>
+        <v>-3.414845080854983</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.541358431763716</v>
+        <v>1.584668859631706</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5012074095003122</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.299955067443831</v>
+        <v>3.251687761987634</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.634057403166207</v>
+        <v>-3.525781333496232</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.472725959468423</v>
+        <v>1.516036387336413</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5012074095003122</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.275697096205038</v>
+        <v>3.227429790748841</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.600393857693925</v>
+        <v>-3.49211778802395</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.414729691058786</v>
+        <v>1.458040118926776</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5348709549725941</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.224433536889857</v>
+        <v>3.17616623143366</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.540541238490202</v>
+        <v>-3.432265168820227</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.448843125172408</v>
+        <v>1.492153553040398</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5348709549725941</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.234605923321989</v>
+        <v>3.186338617865792</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.454297775463824</v>
+        <v>-3.346021705793849</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.478286780956819</v>
+        <v>1.521597208824809</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5348709549725941</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.22955219389585</v>
+        <v>3.181284888439652</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.499604594862804</v>
+        <v>-3.391328525192829</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.451939828641752</v>
+        <v>1.495250256509742</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.4940607919633633</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.196841871534837</v>
+        <v>3.14857456607864</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.528637699565106</v>
+        <v>-3.420361629895131</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.440878459793933</v>
+        <v>1.484188887661923</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.4940607919633633</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.197393744567938</v>
+        <v>3.149126439111741</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.435827218114246</v>
+        <v>-3.327551148444272</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.407275344265643</v>
+        <v>1.450585772133633</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6673167825078846</v>
+        <v>0.5868712734142226</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.18235272532982</v>
+        <v>3.134085419873622</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.480216687443674</v>
+        <v>-3.371940617773699</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.391393032458472</v>
+        <v>1.434703460326462</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.622927313178457</v>
+        <v>0.542481804084795</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.157592519656764</v>
+        <v>3.109325214200567</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.367545469207424</v>
+        <v>-3.259269399537449</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.431537228264696</v>
+        <v>1.474847656132686</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.6551530223210451</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.220270959110237</v>
+        <v>3.172003653654039</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.255168468024751</v>
+        <v>-3.146892398354777</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.481979324568432</v>
+        <v>1.525289752436422</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.6551530223210451</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.225762254940904</v>
+        <v>3.177494949484707</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.282948865926104</v>
+        <v>-3.17467279625613</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.48236436717643</v>
+        <v>1.52567479504442</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.707818133513354</v>
+        <v>0.627372624419692</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.220591217968631</v>
+        <v>3.172323912512434</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.401329538656243</v>
+        <v>-3.293053468986268</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.273367818085028</v>
+        <v>1.316678245953018</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.5601547722687158</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.018616226678699</v>
+        <v>2.970348921222502</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.509943617099574</v>
+        <v>-3.401667547429599</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.350071847426901</v>
+        <v>1.393382275294891</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.5601547722687158</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.138765887397904</v>
+        <v>3.090498581941707</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.474534578851431</v>
+        <v>-3.366258509181456</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.378748488828481</v>
+        <v>1.422058916696471</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.5601547722687158</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.153278913500227</v>
+        <v>3.10501160804403</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.43615091629328</v>
+        <v>-3.327874846623305</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.39152139519411</v>
+        <v>1.4348318230621</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.678983943920529</v>
+        <v>0.598538434826867</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.173728552377487</v>
+        <v>3.12546124692129</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.259034586258114</v>
+        <v>-3.431065473941308</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.459096956053478</v>
+        <v>1.390284600980201</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.678983943920529</v>
+        <v>0.598538434826867</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.170457581222789</v>
+        <v>3.122190275766592</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.30412683109166</v>
+        <v>-3.476157718774854</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.441743449881973</v>
+        <v>1.372931094808695</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6170879007511392</v>
+        <v>0.5366423916574772</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.134003347083068</v>
+        <v>3.085736041626871</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.124751409852892</v>
+        <v>-3.296782297536086</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.507280593683895</v>
+        <v>1.438468238610617</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7738646589218579</v>
+        <v>0.6934191498281959</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.221856377291914</v>
+        <v>3.173589071835716</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.169765623373498</v>
+        <v>-3.341796511056692</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.470082363607242</v>
+        <v>1.401270008533964</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7435157636072532</v>
+        <v>0.6630702545135913</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.18445449543474</v>
+        <v>3.136187189978543</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.436770133645934</v>
+        <v>-3.608801021329128</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.368972121837214</v>
+        <v>1.300159766763936</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5491527255643047</v>
+        <v>0.4687072164706427</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.073528234947917</v>
+        <v>3.02526092949172</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.537967915083106</v>
+        <v>-3.7099988027663</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.327696931158846</v>
+        <v>1.258884576085568</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.4002984029253235</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.031686868717227</v>
+        <v>2.98341956326103</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.531456948468794</v>
+        <v>-3.703487836151988</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.327901279358888</v>
+        <v>1.25908892428561</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.4002984029253235</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.029286830271544</v>
+        <v>2.981019524815347</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.512418820761496</v>
+        <v>-3.68444970844469</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.332041249650051</v>
+        <v>1.263228894576774</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.422560300687791</v>
+        <v>0.3421147915941289</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.990901382681072</v>
+        <v>2.942634077224875</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.543545451912114</v>
+        <v>-3.715576339595308</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.497172466128485</v>
+        <v>1.428360111055207</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.422560300687791</v>
+        <v>0.3421147915941289</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.168483251619753</v>
+        <v>3.120215946163555</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.557412213246032</v>
+        <v>-3.729443100929226</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.492459090581051</v>
+        <v>1.423646735507774</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.304256874860306</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.146601830565592</v>
+        <v>3.098334525109395</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.512608041706102</v>
+        <v>-3.684638929389296</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.516389289593949</v>
+        <v>1.447576934520672</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.304256874860306</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.152610360962518</v>
+        <v>3.104343055506321</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.3648650714711</v>
+        <v>-3.536895959154294</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.47343669896515</v>
+        <v>1.404624343891872</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.4720642320951892</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.151244996580647</v>
+        <v>3.10297769112445</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.466879754002321</v>
+        <v>-3.638910641685515</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.435424447484142</v>
+        <v>1.366612092410865</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.4720642320951892</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.154038618112128</v>
+        <v>3.105771312655931</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.460727047949536</v>
+        <v>-3.63275793563273</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.438547878296914</v>
+        <v>1.369735523223637</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5586624472416355</v>
+        <v>0.4782169381479734</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.158392590135457</v>
+        <v>3.11012528467926</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.477536346100038</v>
+        <v>-3.649567233783232</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.430904635776824</v>
+        <v>1.362092280703546</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.4614076399974718</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.147387487985267</v>
+        <v>3.09912018252907</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.415238347323916</v>
+        <v>-3.58726923500711</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.522159389084094</v>
+        <v>1.453347034010816</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.4614076399974718</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.213723041782088</v>
+        <v>3.165455736325891</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.213448149658758</v>
+        <v>-3.385479037341952</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.405167469864284</v>
+        <v>1.336355114791006</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7398713412602882</v>
+        <v>0.6594258321666262</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.134825958797707</v>
+        <v>3.08655865334151</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.048635146579911</v>
+        <v>-3.220666034263105</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.541382903417998</v>
+        <v>1.47257054834472</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9046843443391351</v>
+        <v>0.8242388352454731</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.304003992967191</v>
+        <v>3.255736687510994</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.146375691204885</v>
+        <v>-3.318406578888079</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.516914421684052</v>
+        <v>1.448102066610774</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.888795066206155</v>
+        <v>0.808349557112493</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.309098162203446</v>
+        <v>3.260830856747249</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.322713451327814</v>
+        <v>-3.494744339011008</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.444915298459552</v>
+        <v>1.376102943386274</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.6320117969895636</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.20183148695436</v>
+        <v>3.153564181498163</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.246291404895888</v>
+        <v>-3.418322292579082</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.473975735072251</v>
+        <v>1.405163379998973</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.6320117969895636</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.200323104994289</v>
+        <v>3.152055799538092</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.201918273257319</v>
+        <v>-3.373949160940513</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.491587855163115</v>
+        <v>1.422775500089837</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.6763849286281322</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.226809851412866</v>
+        <v>3.178542545956669</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.079084052370152</v>
+        <v>-3.251114940053346</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.535115337656572</v>
+        <v>1.466302982583295</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.6763849286281322</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.221203645551457</v>
+        <v>3.172936340095259</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.031428321809096</v>
+        <v>-3.20345920949229</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.560559386908799</v>
+        <v>1.491747031835521</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8044861682828498</v>
+        <v>0.7240406591891878</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.256178840915895</v>
+        <v>3.207911535459698</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.930910163310341</v>
+        <v>-3.102941050993535</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.605659023683026</v>
+        <v>1.536846668609748</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9050043267816044</v>
+        <v>0.8245588176879424</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.321382109389872</v>
+        <v>3.273114803933675</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.99157675371273</v>
+        <v>-3.163607641395924</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.568147059997942</v>
+        <v>1.499334704924665</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8233060100630707</v>
+        <v>0.7428605009694087</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.259117791834624</v>
+        <v>3.210850486378427</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.946738352104332</v>
+        <v>-3.118769239787526</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.59018012325193</v>
+        <v>1.521367768178653</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8278494430079402</v>
+        <v>0.7474039339142782</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.265941554212175</v>
+        <v>3.217674248755977</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.96623680834634</v>
+        <v>-3.138267696029534</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.586541680386205</v>
+        <v>1.517729325312927</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7797648017280359</v>
+        <v>0.6993192926343739</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.24125170907531</v>
+        <v>3.192984403619113</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.92203397126044</v>
+        <v>-3.094064858943634</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.610102417748402</v>
+        <v>1.541290062675125</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8239676388139363</v>
+        <v>0.7435221297202743</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.273653013854688</v>
+        <v>3.22538570839849</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.959012998923883</v>
+        <v>-3.131043886607077</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.593720807152273</v>
+        <v>1.524908452078995</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.7804960315116048</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.294247355398733</v>
+        <v>3.245980049942536</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.800721581384611</v>
+        <v>-2.972752469067805</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.708285139351021</v>
+        <v>1.639472784277743</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.7804960315116048</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.345495120581773</v>
+        <v>3.297227815125576</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.593079577750135</v>
+        <v>-2.765110465433329</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.789782645399065</v>
+        <v>1.720970290325787</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.068583544239743</v>
+        <v>0.988138035146081</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.468521027356712</v>
+        <v>3.420253721900515</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.542047485027607</v>
+        <v>-2.714078372710801</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.805143710726346</v>
+        <v>1.736331355653068</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.119615636962271</v>
+        <v>1.039170127868609</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.494088511228499</v>
+        <v>3.445821205772301</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.476823303900401</v>
+        <v>-2.648854191583595</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.848420787269933</v>
+        <v>1.779608432196655</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.184839818089477</v>
+        <v>1.104394308995815</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.550410423997527</v>
+        <v>3.50214311854133</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.439396283829268</v>
+        <v>-2.611427171512462</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.859352567597667</v>
+        <v>1.790540212524389</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.190091356118658</v>
+        <v>1.109645847024996</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.549522319114316</v>
+        <v>3.501255013658119</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.459507939863976</v>
+        <v>-2.63153882754717</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.852564697515024</v>
+        <v>1.783752342441746</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.201118701116078</v>
+        <v>1.120673192022416</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.557395518444008</v>
+        <v>3.509128212987811</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.405763125436771</v>
+        <v>-2.577794013119965</v>
       </c>
       <c r="E1991" t="n">
-        <v>2.034620394307117</v>
+        <v>1.965808039233839</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.21118201055654</v>
+        <v>1.130736501462878</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.723991275129496</v>
+        <v>3.675723969673299</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.330980864411758</v>
+        <v>-2.503011752094952</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.184646207934939</v>
+        <v>2.115833852861661</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.285964271581552</v>
+        <v>1.20551876248789</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.888973540962321</v>
+        <v>3.840706235506124</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.304896780147951</v>
+        <v>-2.476927667831144</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.186787817654321</v>
+        <v>2.117975462581043</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.285964271581552</v>
+        <v>1.20551876248789</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.88068151697618</v>
+        <v>3.832414211519983</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.226765599299004</v>
+        <v>-2.398796486982198</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.216233485577679</v>
+        <v>2.147421130504402</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.360141082465237</v>
+        <v>1.279695573371575</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.92338079909017</v>
+        <v>3.875113493633973</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.217873137905721</v>
+        <v>-2.389904025588915</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.237344875861784</v>
+        <v>2.168532520788506</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.360141082465237</v>
+        <v>1.279695573371575</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.940935204816961</v>
+        <v>3.892667899360764</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.386349254875598</v>
+        <v>-2.558380142558792</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.161809476478417</v>
+        <v>2.092997121405139</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.332193246748656</v>
+        <v>1.251747737654994</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.916021550791597</v>
+        <v>3.8677542453354</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.688549726014015</v>
+        <v>-1.860580613697209</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.422198985210912</v>
+        <v>2.353386630137634</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.261845187378245</v>
+        <v>1.181399678284583</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.855082412357213</v>
+        <v>3.806815106901015</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.665828622330863</v>
+        <v>-1.837859510014057</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.421951449181077</v>
+        <v>2.353139094107799</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.261845187378245</v>
+        <v>1.181399678284583</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.845746434854117</v>
+        <v>3.79747912939792</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.664103579040819</v>
+        <v>-1.836134466724013</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.581547592348264</v>
+        <v>2.512735237274986</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.263570230668289</v>
+        <v>1.183124721574627</v>
       </c>
       <c r="G1999" t="n">
-        <v>4.005687586679312</v>
+        <v>3.957420281223115</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.818884585819074</v>
+        <v>-1.990915473502268</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.556713012130608</v>
+        <v>2.487900657057331</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.230202556613813</v>
+        <v>1.149757047520151</v>
       </c>
       <c r="G2000" t="n">
-        <v>4.022744804740273</v>
+        <v>3.974477499284076</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.811829895603901</v>
+        <v>-1.983860783287094</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.556210244206223</v>
+        <v>2.487397889132945</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.237257246828987</v>
+        <v>1.156811737735325</v>
       </c>
       <c r="G2001" t="n">
-        <v>4.023652974858923</v>
+        <v>3.975385669402725</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.784878671277413</v>
+        <v>-1.956909558960606</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.57699688758156</v>
+        <v>2.508184532508282</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.252137592856706</v>
+        <v>1.171692083763044</v>
       </c>
       <c r="G2002" t="n">
-        <v>4.042587336120295</v>
+        <v>3.994320030664099</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.920831679333729</v>
+        <v>-2.092862567016923</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.706718816503993</v>
+        <v>2.637906461430715</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.252137592856706</v>
+        <v>1.171692083763044</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.226690468265256</v>
+        <v>4.178423162809058</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.943239797138601</v>
+        <v>-2.115270684821795</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.689872264285037</v>
+        <v>2.62105990921176</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.252137592856706</v>
+        <v>1.171692083763044</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.218807163168249</v>
+        <v>4.170539857712051</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.091245564618</v>
+        <v>-2.263276452301194</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.632723956842915</v>
+        <v>2.563911601769637</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.165410583993165</v>
+        <v>1.084965074899503</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.168824957399761</v>
+        <v>4.120557651943564</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.10068649050653</v>
+        <v>-2.272717378189724</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.68520130420935</v>
+        <v>2.616388949136073</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.287837701536556</v>
+        <v>1.207392192442894</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.298534945647643</v>
+        <v>4.250267640191446</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.152960097842171</v>
+        <v>-2.324990985525365</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.667182955820394</v>
+        <v>2.598370600747117</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.235564094200915</v>
+        <v>1.155118585107253</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.270061875791559</v>
+        <v>4.221794570335362</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.229290075443077</v>
+        <v>-2.401320963126271</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.634762777673807</v>
+        <v>2.56595042260053</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.235564094200915</v>
+        <v>1.155118585107253</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.268173688685335</v>
+        <v>4.219906383229137</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.341047028058378</v>
+        <v>-2.513077915741572</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.584880226230549</v>
+        <v>2.516067871157271</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.123807141585614</v>
+        <v>1.043361632491952</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.195939746719016</v>
+        <v>4.147672441262819</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.339206009000127</v>
+        <v>-2.511236896683321</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.584050644064002</v>
+        <v>2.515238288990724</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.125075368257082</v>
+        <v>1.04462985916342</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.195134692932049</v>
+        <v>4.146867387475853</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.47150730109768</v>
+        <v>-2.643538188780874</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.544203534090899</v>
+        <v>2.475391179017621</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.125075368257082</v>
+        <v>1.04462985916342</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.208208099797968</v>
+        <v>4.159940794341771</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.473068943912541</v>
+        <v>-2.645099831595735</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.543578876964955</v>
+        <v>2.474766521891677</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.125075368257082</v>
+        <v>1.04462985916342</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.208208099797968</v>
+        <v>4.159940794341771</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.500969731022014</v>
+        <v>-2.673000618705208</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.530942603248168</v>
+        <v>2.462130248174891</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.090478444114147</v>
+        <v>1.010032935020485</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.185973986439209</v>
+        <v>4.137706680983012</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.623495833724907</v>
+        <v>-2.795526721408101</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.478696606144209</v>
+        <v>2.409884251070932</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9679523414112534</v>
+        <v>0.8875068323175914</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.109222768794671</v>
+        <v>4.060955463338474</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.643557155001414</v>
+        <v>-2.815588042684608</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.53737803722411</v>
+        <v>2.468565682150833</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9478910201347464</v>
+        <v>0.8674455110410844</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.163891935619271</v>
+        <v>4.115624630163074</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.900277972996238</v>
+        <v>-3.072308860679432</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.575001429028028</v>
+        <v>2.50618907395475</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7590309368972695</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.239154910134829</v>
+        <v>4.190887604678633</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.054264390772379</v>
+        <v>-3.226295278455573</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.582387131063211</v>
+        <v>2.513574775989934</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7590309368972695</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.308135179280469</v>
+        <v>4.259867873824271</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.003742486944713</v>
+        <v>-3.175773374627907</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.588647094714398</v>
+        <v>2.519834739641121</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7590309368972695</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.29418638140059</v>
+        <v>4.245919075944393</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.256217640952437</v>
+        <v>-3.428248528635631</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.499527522166723</v>
+        <v>2.430715167093445</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7590309368972695</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.306056870456004</v>
+        <v>4.257789564999807</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.525690442874145</v>
+        <v>-3.697721330557339</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.392948935916983</v>
+        <v>2.324136580843706</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7590309368972695</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.307267404974947</v>
+        <v>4.259000099518751</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.683234514603587</v>
+        <v>-3.85526540228678</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.334053049452528</v>
+        <v>2.26524069437925</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7725746408506571</v>
+        <v>0.6921291317569951</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.271248064118105</v>
+        <v>4.222980758661907</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.812085065305633</v>
+        <v>-3.984115952988827</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.277590681907899</v>
+        <v>2.208778326834621</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.6511357229062735</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.24172987154386</v>
+        <v>4.193462566087664</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.929052757944524</v>
+        <v>-4.101083645627718</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.393007661551387</v>
+        <v>2.324195306478109</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.6511357229062735</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.403933928242905</v>
+        <v>4.355666622786708</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.013770700165478</v>
+        <v>-4.185801587848672</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.353967122626819</v>
+        <v>2.285154767553542</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6464652030718891</v>
+        <v>0.5660196939782272</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.347710948849891</v>
+        <v>4.299443643393694</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.095705518434361</v>
+        <v>-4.267736406117555</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.331422612887757</v>
+        <v>2.26261025781448</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.636530457484809</v>
+        <v>0.556084948391147</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.351979519066135</v>
+        <v>4.303712213609938</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.041967345034099</v>
+        <v>-4.213998232717293</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.361843520703764</v>
+        <v>2.293031165630487</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6902686308850711</v>
+        <v>0.6098231217914091</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.393148061562195</v>
+        <v>4.344880756105997</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.931961061556877</v>
+        <v>-4.103991949240071</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.397998921338829</v>
+        <v>2.329186566265551</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7134732028023463</v>
+        <v>0.6330276937086843</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.399223691956735</v>
+        <v>4.350956386500538</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.788901485815952</v>
+        <v>-3.960932373499146</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.459472762357174</v>
+        <v>2.390660407283896</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7214866293923256</v>
+        <v>0.6410411202986636</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.408281758632697</v>
+        <v>4.360014453176499</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.487454760344114</v>
+        <v>-3.659485648027308</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.587312335428445</v>
+        <v>2.518499980355167</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9424878457705008</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.596410676798335</v>
+        <v>4.548143371342139</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.542409956787183</v>
+        <v>-3.714440844470377</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.566301434603927</v>
+        <v>2.497489079530649</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9424878457705008</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.597381854551045</v>
+        <v>4.549114549094849</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.491371580780663</v>
+        <v>-3.663402468463857</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.587559689386291</v>
+        <v>2.518747334313013</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9424878457705008</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.598224758930801</v>
+        <v>4.549957453474605</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.810790926480911</v>
+        <v>3.464573276778279</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.450232285914032</v>
+        <v>-3.355082983833149</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.623053506207089</v>
+        <v>2.661113227039442</v>
       </c>
       <c r="F2032" t="n">
-        <v>1.064072649730794</v>
+        <v>1.25080733040121</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.641946434724925</v>
+        <v>4.753987243127175</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240722.xlsx
+++ b/tame_output/ON/bt/strategyON_20240722.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>49.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>86.4%</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.4%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.5%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.1%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.5%</t>
+          <t>-66.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.0%</t>
+          <t>456.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-497.1%</t>
+          <t>-499.6%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-110.1%</t>
+          <t>-111.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1298,57 +1298,57 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-133.0%</t>
+          <t>-131.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-98.9%</t>
+          <t>-121.5%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,57 +1456,57 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>-48.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2032"/>
+  <dimension ref="A1:G2033"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44383,10 +44383,10 @@
         <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.3846419795235408</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.83837196775276</v>
+        <v>2.886639273208957</v>
       </c>
     </row>
     <row r="1863">
@@ -44406,10 +44406,10 @@
         <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7613982729162152</v>
+        <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.659840012179184</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44429,10 +44429,10 @@
         <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.169987050096894</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.413448289885536</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44452,10 +44452,10 @@
         <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.169987050096894</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.408633722356996</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44475,10 +44475,10 @@
         <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.169987050096894</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.406627772965874</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44498,10 +44498,10 @@
         <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.169987050096894</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.416886463634553</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44521,10 +44521,10 @@
         <v>0.3165746066023623</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.169987050096894</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.412986028780248</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44544,10 +44544,10 @@
         <v>0.2956983997604259</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.169987050096894</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.411390948835249</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44567,10 +44567,10 @@
         <v>0.1808128389655548</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.238730185830772</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.37392404332413</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44590,10 +44590,10 @@
         <v>0.1020986511074309</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.238730185830772</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.369897738789727</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44613,10 +44613,10 @@
         <v>-0.05120400571120598</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.238730185830772</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.369795637468143</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44636,10 +44636,10 @@
         <v>-0.05042706782033113</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.243216631032161</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.36967528631874</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44659,10 +44659,10 @@
         <v>-0.1888888935238819</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.243216631032161</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.37502558961679</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44682,10 +44682,10 @@
         <v>-0.2011124989483934</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.293565694486383</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.352732171501434</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44705,10 +44705,10 @@
         <v>-0.2371184592951829</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.39118497190778</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.297202355670365</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44728,10 +44728,10 @@
         <v>-0.255853502776954</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.445256471416139</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.267653012286921</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44751,10 +44751,10 @@
         <v>-0.3320435757902573</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.572895416030128</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.196582842637171</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44774,10 +44774,10 @@
         <v>-0.3410221567092107</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.673308783947165</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.140817376371384</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44797,10 +44797,10 @@
         <v>-0.29626252254881</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.599838952279717</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.200270976865274</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44820,10 +44820,10 @@
         <v>-0.3517570687559104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.774963369666261</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.109751547180865</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44843,10 +44843,10 @@
         <v>-0.4527570712633024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.774963369666261</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.102532382279269</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44866,10 +44866,10 @@
         <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.879338100692707</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.033235352889425</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44889,10 +44889,10 @@
         <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.975013587275104</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.976945850778543</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44912,10 +44912,10 @@
         <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.949761964465361</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.994790553093504</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44935,10 +44935,10 @@
         <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.949761964465361</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.998780888779904</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44958,10 +44958,10 @@
         <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.949761964465361</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.997305661881162</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44981,10 +44981,10 @@
         <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.900171120040528</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.042113578700935</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -45004,10 +45004,10 @@
         <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.868921529305354</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.047812199495356</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45027,10 +45027,10 @@
         <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.826994853718191</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.082547277883863</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45050,10 +45050,10 @@
         <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.826994853718191</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.083686422439921</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45073,10 +45073,10 @@
         <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.822039507629745</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.089293404255097</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45096,10 +45096,10 @@
         <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.822039507629745</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.095027108493733</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45119,10 +45119,10 @@
         <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.750673115020097</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.128109681665657</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45142,10 +45142,10 @@
         <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.750673115020097</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.118226200352749</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45165,10 +45165,10 @@
         <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.750673115020097</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.116391639853376</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45188,10 +45188,10 @@
         <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.68268736515954</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.156882774796249</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45211,10 +45211,10 @@
         <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.658733824183583</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.171923405527317</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45234,10 +45234,10 @@
         <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.394673885860787</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.317099052359243</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45257,10 +45257,10 @@
         <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.394673885860787</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.314312018698942</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45280,10 +45280,10 @@
         <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.354489587494596</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.338766221606497</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45303,10 +45303,10 @@
         <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.191089716555233</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.436172965390872</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45326,10 +45326,10 @@
         <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9576084943256347</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.584186127566483</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45349,10 +45349,10 @@
         <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8647050030830987</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.637036011999045</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45372,10 +45372,10 @@
         <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7324295294522121</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.711768782924605</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45395,10 +45395,10 @@
         <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5766911968924705</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.808026843148086</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45418,10 +45418,10 @@
         <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5766911968924705</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.820933184371745</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45441,10 +45441,10 @@
         <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6822811866655749</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.629603260908664</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45464,10 +45464,10 @@
         <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6878771963257062</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.674789996989671</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45487,10 +45487,10 @@
         <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6675562804171487</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.567103623846638</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45510,10 +45510,10 @@
         <v>0.5089641519027821</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.6145867581631598</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.590171350945553</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45533,10 +45533,10 @@
         <v>0.5194229025159651</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.6145867581631598</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.58321073885046</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45556,10 +45556,10 @@
         <v>0.5472305394886159</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.6145867581631598</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.597673093231603</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45579,10 +45579,10 @@
         <v>0.5850663147968196</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.6145867581631598</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.592205213690798</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45602,10 +45602,10 @@
         <v>0.6318808627342487</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4912956233460293</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.663677988591654</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45625,10 +45625,10 @@
         <v>0.6480415205329515</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.4701464244425859</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.684068486171045</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45648,10 +45648,10 @@
         <v>0.7413284056733795</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.4701464244425859</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.679849194518095</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45671,10 +45671,10 @@
         <v>0.7841578477043138</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4569273560501572</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.689904949473569</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45694,10 +45694,10 @@
         <v>0.8768400802676455</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4569273560501572</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.682647024457271</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45717,10 +45717,10 @@
         <v>0.9507960407752671</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4569273560501572</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.686246147977919</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45740,10 +45740,10 @@
         <v>1.032702132038806</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2854808930276941</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.802441531845951</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45763,10 +45763,10 @@
         <v>1.061438435950439</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.2111913272893548</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.846035748905252</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45786,10 +45786,10 @@
         <v>1.09158753389833</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1475555850554203</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.88891199529993</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45809,10 +45809,10 @@
         <v>1.117352496412494</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1475555850554203</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.870106254083725</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45832,10 +45832,10 @@
         <v>1.215267771759315</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.09287491174944001</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.016107628791519</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45855,10 +45855,10 @@
         <v>1.248094112862613</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.09287491174944001</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.020036942626339</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45878,10 +45878,10 @@
         <v>1.269972025692508</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1482111707513789</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.053917281944842</v>
+        <v>3.10218458740104</v>
       </c>
     </row>
     <row r="1928">
@@ -45901,10 +45901,10 @@
         <v>1.310492051104393</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1482111707513789</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.050915353164836</v>
+        <v>3.099182658621033</v>
       </c>
     </row>
     <row r="1929">
@@ -45924,10 +45924,10 @@
         <v>1.400079407329811</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2894310158193591</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.137226297216238</v>
+        <v>3.185493602672435</v>
       </c>
     </row>
     <row r="1930">
@@ -45947,10 +45947,10 @@
         <v>1.469120665756946</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2894310158193591</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.153120480018061</v>
+        <v>3.201387785474259</v>
       </c>
     </row>
     <row r="1931">
@@ -45970,10 +45970,10 @@
         <v>1.518335743543047</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.409604099183858</v>
+        <v>0.4900496082775201</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.226370174477063</v>
+        <v>3.27463747993326</v>
       </c>
     </row>
     <row r="1932">
@@ -45993,10 +45993,10 @@
         <v>1.586292704144382</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5542762442835955</v>
+        <v>0.6347217533772576</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.323261564098345</v>
+        <v>3.371528869554542</v>
       </c>
     </row>
     <row r="1933">
@@ -46016,10 +46016,10 @@
         <v>1.548380264602731</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4944014169259033</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.273374159085156</v>
+        <v>3.321641464541353</v>
       </c>
     </row>
     <row r="1934">
@@ -46039,10 +46039,10 @@
         <v>1.611597526201274</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4944014169259033</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.288663328319364</v>
+        <v>3.336930633775562</v>
       </c>
     </row>
     <row r="1935">
@@ -46062,10 +46062,10 @@
         <v>1.518253842938994</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4919317104640972</v>
+        <v>0.5723772195577592</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.194825703764722</v>
+        <v>3.243093009220919</v>
       </c>
     </row>
     <row r="1936">
@@ -46085,10 +46085,10 @@
         <v>1.410167629894691</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5012074095003122</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.119652984671752</v>
+        <v>3.16792029012795</v>
       </c>
     </row>
     <row r="1937">
@@ -46108,10 +46108,10 @@
         <v>1.395089117387764</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5012074095003122</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.110089693303644</v>
+        <v>3.158356998759841</v>
       </c>
     </row>
     <row r="1938">
@@ -46131,10 +46131,10 @@
         <v>1.50991192372293</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5012074095003122</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.247120529995846</v>
+        <v>3.295387835452043</v>
       </c>
     </row>
     <row r="1939">
@@ -46154,10 +46154,10 @@
         <v>1.584668859631706</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5012074095003122</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.251687761987634</v>
+        <v>3.299955067443831</v>
       </c>
     </row>
     <row r="1940">
@@ -46177,10 +46177,10 @@
         <v>1.516036387336413</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5012074095003122</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.227429790748841</v>
+        <v>3.275697096205038</v>
       </c>
     </row>
     <row r="1941">
@@ -46200,10 +46200,10 @@
         <v>1.458040118926776</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5348709549725941</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.17616623143366</v>
+        <v>3.224433536889857</v>
       </c>
     </row>
     <row r="1942">
@@ -46223,10 +46223,10 @@
         <v>1.492153553040398</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5348709549725941</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.186338617865792</v>
+        <v>3.234605923321989</v>
       </c>
     </row>
     <row r="1943">
@@ -46246,10 +46246,10 @@
         <v>1.521597208824809</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5348709549725941</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.181284888439652</v>
+        <v>3.22955219389585</v>
       </c>
     </row>
     <row r="1944">
@@ -46269,10 +46269,10 @@
         <v>1.495250256509742</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4940607919633633</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.14857456607864</v>
+        <v>3.196841871534837</v>
       </c>
     </row>
     <row r="1945">
@@ -46292,10 +46292,10 @@
         <v>1.484188887661923</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4940607919633633</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.149126439111741</v>
+        <v>3.197393744567938</v>
       </c>
     </row>
     <row r="1946">
@@ -46315,10 +46315,10 @@
         <v>1.450585772133633</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5868712734142226</v>
+        <v>0.6673167825078846</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.134085419873622</v>
+        <v>3.18235272532982</v>
       </c>
     </row>
     <row r="1947">
@@ -46338,10 +46338,10 @@
         <v>1.434703460326462</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.542481804084795</v>
+        <v>0.622927313178457</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.109325214200567</v>
+        <v>3.157592519656764</v>
       </c>
     </row>
     <row r="1948">
@@ -46361,10 +46361,10 @@
         <v>1.474847656132686</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6551530223210451</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.172003653654039</v>
+        <v>3.220270959110237</v>
       </c>
     </row>
     <row r="1949">
@@ -46384,10 +46384,10 @@
         <v>1.525289752436422</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6551530223210451</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.177494949484707</v>
+        <v>3.225762254940904</v>
       </c>
     </row>
     <row r="1950">
@@ -46407,10 +46407,10 @@
         <v>1.52567479504442</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.627372624419692</v>
+        <v>0.707818133513354</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.172323912512434</v>
+        <v>3.220591217968631</v>
       </c>
     </row>
     <row r="1951">
@@ -46430,10 +46430,10 @@
         <v>1.316678245953018</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5601547722687158</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.970348921222502</v>
+        <v>3.018616226678699</v>
       </c>
     </row>
     <row r="1952">
@@ -46453,10 +46453,10 @@
         <v>1.393382275294891</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5601547722687158</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.090498581941707</v>
+        <v>3.138765887397904</v>
       </c>
     </row>
     <row r="1953">
@@ -46476,10 +46476,10 @@
         <v>1.422058916696471</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5601547722687158</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.10501160804403</v>
+        <v>3.153278913500227</v>
       </c>
     </row>
     <row r="1954">
@@ -46499,10 +46499,10 @@
         <v>1.4348318230621</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.598538434826867</v>
+        <v>0.678983943920529</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.12546124692129</v>
+        <v>3.173728552377487</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.431065473941308</v>
+        <v>-3.150758516588139</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.390284600980201</v>
+        <v>1.502407383921468</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.598538434826867</v>
+        <v>0.678983943920529</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.122190275766592</v>
+        <v>3.170457581222789</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.476157718774854</v>
+        <v>-3.195850761421685</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.372931094808695</v>
+        <v>1.485053877749963</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5366423916574772</v>
+        <v>0.6170879007511392</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.085736041626871</v>
+        <v>3.134003347083068</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.296782297536086</v>
+        <v>-3.016475340182917</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.438468238610617</v>
+        <v>1.550591021551885</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6934191498281959</v>
+        <v>0.7738646589218579</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.173589071835716</v>
+        <v>3.221856377291914</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.341796511056692</v>
+        <v>-3.061489553703523</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.401270008533964</v>
+        <v>1.513392791475232</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6630702545135913</v>
+        <v>0.7435157636072532</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.136187189978543</v>
+        <v>3.18445449543474</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.608801021329128</v>
+        <v>-3.328494063975959</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.300159766763936</v>
+        <v>1.412282549705203</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4687072164706427</v>
+        <v>0.5491527255643047</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.02526092949172</v>
+        <v>3.073528234947917</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.7099988027663</v>
+        <v>-3.429691845413132</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.258884576085568</v>
+        <v>1.371007359026836</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4002984029253235</v>
+        <v>0.4807439120189855</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.98341956326103</v>
+        <v>3.031686868717227</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.703487836151988</v>
+        <v>-3.423180878798819</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.25908892428561</v>
+        <v>1.371211707226877</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4002984029253235</v>
+        <v>0.4807439120189855</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.981019524815347</v>
+        <v>3.029286830271544</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.68444970844469</v>
+        <v>-3.404142751091522</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.263228894576774</v>
+        <v>1.375351677518041</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3421147915941289</v>
+        <v>0.422560300687791</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.942634077224875</v>
+        <v>2.990901382681072</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.715576339595308</v>
+        <v>-3.43526938224214</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.428360111055207</v>
+        <v>1.540482893996475</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3421147915941289</v>
+        <v>0.422560300687791</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.120215946163555</v>
+        <v>3.168483251619753</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.729443100929226</v>
+        <v>-3.449136143576057</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.423646735507774</v>
+        <v>1.535769518449041</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.304256874860306</v>
+        <v>0.3847023839539681</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.098334525109395</v>
+        <v>3.146601830565592</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.684638929389296</v>
+        <v>-3.404331972036127</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.447576934520672</v>
+        <v>1.559699717461939</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.304256874860306</v>
+        <v>0.3847023839539681</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.104343055506321</v>
+        <v>3.152610360962518</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.536895959154294</v>
+        <v>-3.256589001801125</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.404624343891872</v>
+        <v>1.516747126833139</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4720642320951892</v>
+        <v>0.5525097411888512</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.10297769112445</v>
+        <v>3.151244996580647</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.638910641685515</v>
+        <v>-3.358603684332346</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.366612092410865</v>
+        <v>1.478734875352132</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4720642320951892</v>
+        <v>0.5525097411888512</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.105771312655931</v>
+        <v>3.154038618112128</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.63275793563273</v>
+        <v>-3.352450978279562</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.369735523223637</v>
+        <v>1.481858306164904</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4782169381479734</v>
+        <v>0.5586624472416355</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.11012528467926</v>
+        <v>3.158392590135457</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.649567233783232</v>
+        <v>-3.369260276430063</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.362092280703546</v>
+        <v>1.474215063644814</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4614076399974718</v>
+        <v>0.5418531490911338</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.09912018252907</v>
+        <v>3.147387487985267</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.58726923500711</v>
+        <v>-3.306962277653941</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.453347034010816</v>
+        <v>1.565469816952084</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4614076399974718</v>
+        <v>0.5418531490911338</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.165455736325891</v>
+        <v>3.213723041782088</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.385479037341952</v>
+        <v>-3.105172079988783</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.336355114791006</v>
+        <v>1.448477897732274</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6594258321666262</v>
+        <v>0.7398713412602882</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.08655865334151</v>
+        <v>3.134825958797707</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.220666034263105</v>
+        <v>-2.940359076909936</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.47257054834472</v>
+        <v>1.584693331285988</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8242388352454731</v>
+        <v>0.9046843443391351</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.255736687510994</v>
+        <v>3.304003992967191</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.318406578888079</v>
+        <v>-3.038099621534911</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.448102066610774</v>
+        <v>1.560224849552042</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.808349557112493</v>
+        <v>0.888795066206155</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.260830856747249</v>
+        <v>3.309098162203446</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.494744339011008</v>
+        <v>-3.21443738165784</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.376102943386274</v>
+        <v>1.488225726327542</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6320117969895636</v>
+        <v>0.7124573060832255</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.153564181498163</v>
+        <v>3.20183148695436</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.418322292579082</v>
+        <v>-3.138015335225913</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.405163379998973</v>
+        <v>1.517286162940241</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6320117969895636</v>
+        <v>0.7124573060832255</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.152055799538092</v>
+        <v>3.200323104994289</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.373949160940513</v>
+        <v>-3.093642203587344</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.422775500089837</v>
+        <v>1.534898283031104</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6763849286281322</v>
+        <v>0.7568304377217941</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.178542545956669</v>
+        <v>3.226809851412866</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.251114940053346</v>
+        <v>-2.970807982700177</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.466302982583295</v>
+        <v>1.578425765524562</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6763849286281322</v>
+        <v>0.7568304377217941</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.172936340095259</v>
+        <v>3.221203645551457</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.20345920949229</v>
+        <v>-2.923152252139121</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.491747031835521</v>
+        <v>1.603869814776789</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7240406591891878</v>
+        <v>0.8044861682828498</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.207911535459698</v>
+        <v>3.256178840915895</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.102941050993535</v>
+        <v>-2.822634093640366</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.536846668609748</v>
+        <v>1.648969451551016</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8245588176879424</v>
+        <v>0.9050043267816044</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.273114803933675</v>
+        <v>3.321382109389872</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.163607641395924</v>
+        <v>-2.883300684042756</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.499334704924665</v>
+        <v>1.611457487865932</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7428605009694087</v>
+        <v>0.8233060100630707</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.210850486378427</v>
+        <v>3.259117791834624</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.118769239787526</v>
+        <v>-2.838462282434357</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.521367768178653</v>
+        <v>1.63349055111992</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7474039339142782</v>
+        <v>0.8278494430079402</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.217674248755977</v>
+        <v>3.265941554212175</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.138267696029534</v>
+        <v>-2.857960738676366</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.517729325312927</v>
+        <v>1.629852108254195</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6993192926343739</v>
+        <v>0.7797648017280359</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.192984403619113</v>
+        <v>3.24125170907531</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.094064858943634</v>
+        <v>-2.813757901590465</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.541290062675125</v>
+        <v>1.653412845616392</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7435221297202743</v>
+        <v>0.8239676388139363</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.22538570839849</v>
+        <v>3.273653013854688</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.131043886607077</v>
+        <v>-2.850736929253908</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.524908452078995</v>
+        <v>1.637031235020262</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7804960315116048</v>
+        <v>0.8609415406052668</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.245980049942536</v>
+        <v>3.294247355398733</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.972752469067805</v>
+        <v>-2.692445511714636</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.639472784277743</v>
+        <v>1.751595567219011</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7804960315116048</v>
+        <v>0.8609415406052668</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.297227815125576</v>
+        <v>3.345495120581773</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.765110465433329</v>
+        <v>-2.48480350808016</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.720970290325787</v>
+        <v>1.833093073267055</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.988138035146081</v>
+        <v>1.068583544239743</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.420253721900515</v>
+        <v>3.468521027356712</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.714078372710801</v>
+        <v>-2.433771415357632</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.736331355653068</v>
+        <v>1.848454138594336</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.039170127868609</v>
+        <v>1.119615636962271</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.445821205772301</v>
+        <v>3.494088511228499</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.648854191583595</v>
+        <v>-2.368547234230427</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.779608432196655</v>
+        <v>1.891731215137923</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.104394308995815</v>
+        <v>1.184839818089477</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.50214311854133</v>
+        <v>3.550410423997527</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.611427171512462</v>
+        <v>-2.331120214159293</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.790540212524389</v>
+        <v>1.902662995465657</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.109645847024996</v>
+        <v>1.190091356118658</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.501255013658119</v>
+        <v>3.549522319114316</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.63153882754717</v>
+        <v>-2.351231870194001</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.783752342441746</v>
+        <v>1.895875125383014</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.120673192022416</v>
+        <v>1.201118701116078</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.509128212987811</v>
+        <v>3.557395518444008</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.577794013119965</v>
+        <v>-2.297487055766796</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.965808039233839</v>
+        <v>2.077930822175106</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.130736501462878</v>
+        <v>1.21118201055654</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.675723969673299</v>
+        <v>3.723991275129496</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.503011752094952</v>
+        <v>-2.222704794741784</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.115833852861661</v>
+        <v>2.227956635802929</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.20551876248789</v>
+        <v>1.285964271581552</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.840706235506124</v>
+        <v>3.888973540962321</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.476927667831144</v>
+        <v>-2.196620710477976</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.117975462581043</v>
+        <v>2.230098245522311</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.20551876248789</v>
+        <v>1.285964271581552</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.832414211519983</v>
+        <v>3.88068151697618</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.398796486982198</v>
+        <v>-2.118489529629029</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.147421130504402</v>
+        <v>2.259543913445669</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.279695573371575</v>
+        <v>1.360141082465237</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.875113493633973</v>
+        <v>3.92338079909017</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.389904025588915</v>
+        <v>-2.109597068235746</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.168532520788506</v>
+        <v>2.280655303729774</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.279695573371575</v>
+        <v>1.360141082465237</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.892667899360764</v>
+        <v>3.940935204816961</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.558380142558792</v>
+        <v>-2.278073185205624</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.092997121405139</v>
+        <v>2.205119904346406</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.251747737654994</v>
+        <v>1.332193246748656</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.8677542453354</v>
+        <v>3.916021550791597</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.860580613697209</v>
+        <v>-1.58027365634404</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.353386630137634</v>
+        <v>2.465509413078902</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.181399678284583</v>
+        <v>1.261845187378245</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.806815106901015</v>
+        <v>3.855082412357213</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.837859510014057</v>
+        <v>-1.557552552660888</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.353139094107799</v>
+        <v>2.465261877049067</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.181399678284583</v>
+        <v>1.261845187378245</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.79747912939792</v>
+        <v>3.845746434854117</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.836134466724013</v>
+        <v>-1.555827509370844</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.512735237274986</v>
+        <v>2.624858020216254</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.183124721574627</v>
+        <v>1.263570230668289</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.957420281223115</v>
+        <v>4.005687586679312</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.990915473502268</v>
+        <v>-1.7106085161491</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.487900657057331</v>
+        <v>2.600023439998598</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.149757047520151</v>
+        <v>1.230202556613813</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.974477499284076</v>
+        <v>4.022744804740273</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.983860783287094</v>
+        <v>-1.703553825933926</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.487397889132945</v>
+        <v>2.599520672074213</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.156811737735325</v>
+        <v>1.237257246828987</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.975385669402725</v>
+        <v>4.023652974858923</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.956909558960606</v>
+        <v>-1.676602601607438</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.508184532508282</v>
+        <v>2.62030731544955</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.171692083763044</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.994320030664099</v>
+        <v>4.042587336120295</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.092862567016923</v>
+        <v>-1.812555609663754</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.637906461430715</v>
+        <v>2.750029244371983</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.171692083763044</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.178423162809058</v>
+        <v>4.226690468265256</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.115270684821795</v>
+        <v>-1.834963727468626</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.62105990921176</v>
+        <v>2.733182692153027</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.171692083763044</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.170539857712051</v>
+        <v>4.218807163168249</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.263276452301194</v>
+        <v>-1.982969494948025</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.563911601769637</v>
+        <v>2.676034384710905</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.084965074899503</v>
+        <v>1.165410583993165</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.120557651943564</v>
+        <v>4.168824957399761</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.272717378189724</v>
+        <v>-1.992410420836555</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.616388949136073</v>
+        <v>2.72851173207734</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.207392192442894</v>
+        <v>1.287837701536556</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.250267640191446</v>
+        <v>4.298534945647643</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.324990985525365</v>
+        <v>-2.044684028172196</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.598370600747117</v>
+        <v>2.710493383688385</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.155118585107253</v>
+        <v>1.235564094200915</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.221794570335362</v>
+        <v>4.270061875791559</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.401320963126271</v>
+        <v>-2.121014005773102</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.56595042260053</v>
+        <v>2.678073205541797</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.155118585107253</v>
+        <v>1.235564094200915</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.219906383229137</v>
+        <v>4.268173688685335</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.513077915741572</v>
+        <v>-2.232770958388403</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.516067871157271</v>
+        <v>2.628190654098539</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.043361632491952</v>
+        <v>1.123807141585614</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.147672441262819</v>
+        <v>4.195939746719016</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.511236896683321</v>
+        <v>-2.230929939330152</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.515238288990724</v>
+        <v>2.627361071931992</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.04462985916342</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.146867387475853</v>
+        <v>4.195134692932049</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.643538188780874</v>
+        <v>-2.363231231427705</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.475391179017621</v>
+        <v>2.587513961958889</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.04462985916342</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.159940794341771</v>
+        <v>4.208208099797968</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.645099831595735</v>
+        <v>-2.364792874242565</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.474766521891677</v>
+        <v>2.586889304832945</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.04462985916342</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.159940794341771</v>
+        <v>4.208208099797968</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.673000618705208</v>
+        <v>-2.392693661352038</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.462130248174891</v>
+        <v>2.574253031116158</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.010032935020485</v>
+        <v>1.090478444114147</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.137706680983012</v>
+        <v>4.185973986439209</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.795526721408101</v>
+        <v>-2.515219764054932</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.409884251070932</v>
+        <v>2.5220070340122</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8875068323175914</v>
+        <v>0.9679523414112534</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.060955463338474</v>
+        <v>4.109222768794671</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.815588042684608</v>
+        <v>-2.535281085331439</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.468565682150833</v>
+        <v>2.5806884650921</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8674455110410844</v>
+        <v>0.9478910201347464</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.115624630163074</v>
+        <v>4.163891935619271</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.072308860679432</v>
+        <v>-2.792001903326263</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.50618907395475</v>
+        <v>2.618311856896018</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.7590309368972695</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.190887604678633</v>
+        <v>4.239154910134829</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.226295278455573</v>
+        <v>-2.945988321102403</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.513574775989934</v>
+        <v>2.625697558931201</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.7590309368972695</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.259867873824271</v>
+        <v>4.308135179280469</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.175773374627907</v>
+        <v>-2.895466417274737</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.519834739641121</v>
+        <v>2.631957522582389</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.7590309368972695</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.245919075944393</v>
+        <v>4.29418638140059</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.428248528635631</v>
+        <v>-3.147941571282462</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.430715167093445</v>
+        <v>2.542837950034713</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.7590309368972695</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.257789564999807</v>
+        <v>4.306056870456004</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.697721330557339</v>
+        <v>-3.41741437320417</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.324136580843706</v>
+        <v>2.436259363784973</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.7590309368972695</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.259000099518751</v>
+        <v>4.307267404974947</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.85526540228678</v>
+        <v>-3.574958444933611</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.26524069437925</v>
+        <v>2.377363477320518</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6921291317569951</v>
+        <v>0.7725746408506571</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.222980758661907</v>
+        <v>4.271248064118105</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.984115952988827</v>
+        <v>-3.703808995635657</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.208778326834621</v>
+        <v>2.320901109775889</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6511357229062735</v>
+        <v>0.7315812319999355</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.193462566087664</v>
+        <v>4.24172987154386</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.101083645627718</v>
+        <v>-3.820776688274548</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.324195306478109</v>
+        <v>2.436318089419377</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6511357229062735</v>
+        <v>0.7315812319999355</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.355666622786708</v>
+        <v>4.403933928242905</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.185801587848672</v>
+        <v>-3.905494630495502</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.285154767553542</v>
+        <v>2.39727755049481</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5660196939782272</v>
+        <v>0.6464652030718891</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.299443643393694</v>
+        <v>4.347710948849891</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.267736406117555</v>
+        <v>-3.987429448764386</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.26261025781448</v>
+        <v>2.374733040755748</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.556084948391147</v>
+        <v>0.636530457484809</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.303712213609938</v>
+        <v>4.351979519066135</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.213998232717293</v>
+        <v>-3.933691275364124</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.293031165630487</v>
+        <v>2.405153948571755</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6098231217914091</v>
+        <v>0.6902686308850711</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.344880756105997</v>
+        <v>4.393148061562195</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.103991949240071</v>
+        <v>-3.823684991886902</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.329186566265551</v>
+        <v>2.441309349206819</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.6330276937086843</v>
+        <v>0.7134732028023463</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.350956386500538</v>
+        <v>4.399223691956735</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.960932373499146</v>
+        <v>-3.680625416145976</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.390660407283896</v>
+        <v>2.502783190225164</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.6410411202986636</v>
+        <v>0.7214866293923256</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.360014453176499</v>
+        <v>4.408281758632697</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.659485648027308</v>
+        <v>-3.379178690674139</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.518499980355167</v>
+        <v>2.630622763296435</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.9424878457705008</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.548143371342139</v>
+        <v>4.596410676798335</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.714440844470377</v>
+        <v>-3.434133887117208</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.497489079530649</v>
+        <v>2.609611862471918</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.9424878457705008</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.549114549094849</v>
+        <v>4.597381854551045</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.663402468463857</v>
+        <v>-3.383095511110688</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.518747334313013</v>
+        <v>2.630870117254281</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.9424878457705008</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.549957453474605</v>
+        <v>4.598224758930801</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,45 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.464573276778279</v>
+        <v>3.831748677354685</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.355082983833149</v>
+        <v>-3.380714357235552</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.661113227039442</v>
+        <v>2.650860677678481</v>
       </c>
       <c r="F2032" t="n">
-        <v>1.25080733040121</v>
+        <v>1.025314508739298</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.753987243127175</v>
+        <v>4.618691550130028</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" s="2" t="n">
+        <v>45495</v>
+      </c>
+      <c r="B2033" t="n">
+        <v>3.77052299397603</v>
+      </c>
+      <c r="C2033" t="n">
+        <v>3.980133892981399</v>
+      </c>
+      <c r="D2033" t="n">
+        <v>-3.380714357235552</v>
+      </c>
+      <c r="E2033" t="n">
+        <v>2.650860677678481</v>
+      </c>
+      <c r="F2033" t="n">
+        <v>1.025314508739298</v>
+      </c>
+      <c r="G2033" t="n">
+        <v>3.973197689967766</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240722.xlsx
+++ b/tame_output/ON/bt/strategyON_20240722.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>91.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>122.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.9%</t>
+          <t>-67.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.5%</t>
+          <t>456.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-499.6%</t>
+          <t>-507.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-111.1%</t>
+          <t>-114.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.8%</t>
+          <t>-126.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-121.5%</t>
+          <t>-125.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-43.9%</t>
         </is>
       </c>
     </row>
@@ -44383,10 +44383,10 @@
         <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3846419795235408</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>2.83837196775276</v>
       </c>
     </row>
     <row r="1863">
@@ -44406,10 +44406,10 @@
         <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.7613982729162152</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.659840012179184</v>
       </c>
     </row>
     <row r="1864">
@@ -44429,10 +44429,10 @@
         <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.169987050096894</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.413448289885536</v>
       </c>
     </row>
     <row r="1865">
@@ -44452,10 +44452,10 @@
         <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.169987050096894</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.408633722356996</v>
       </c>
     </row>
     <row r="1866">
@@ -44475,10 +44475,10 @@
         <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.169987050096894</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.406627772965874</v>
       </c>
     </row>
     <row r="1867">
@@ -44498,10 +44498,10 @@
         <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.169987050096894</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.416886463634553</v>
       </c>
     </row>
     <row r="1868">
@@ -44521,10 +44521,10 @@
         <v>0.3165746066023623</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.169987050096894</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.412986028780248</v>
       </c>
     </row>
     <row r="1869">
@@ -44544,10 +44544,10 @@
         <v>0.2956983997604259</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.169987050096894</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.411390948835249</v>
       </c>
     </row>
     <row r="1870">
@@ -44567,10 +44567,10 @@
         <v>0.1808128389655548</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.238730185830772</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.37392404332413</v>
       </c>
     </row>
     <row r="1871">
@@ -44590,10 +44590,10 @@
         <v>0.1020986511074309</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.238730185830772</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.369897738789727</v>
       </c>
     </row>
     <row r="1872">
@@ -44613,10 +44613,10 @@
         <v>-0.05120400571120598</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.238730185830772</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.369795637468143</v>
       </c>
     </row>
     <row r="1873">
@@ -44636,10 +44636,10 @@
         <v>-0.05042706782033113</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.243216631032161</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.36967528631874</v>
       </c>
     </row>
     <row r="1874">
@@ -44659,10 +44659,10 @@
         <v>-0.1888888935238819</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.243216631032161</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.37502558961679</v>
       </c>
     </row>
     <row r="1875">
@@ -44682,10 +44682,10 @@
         <v>-0.2011124989483934</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.293565694486383</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.352732171501434</v>
       </c>
     </row>
     <row r="1876">
@@ -44705,10 +44705,10 @@
         <v>-0.2371184592951829</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.39118497190778</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.297202355670365</v>
       </c>
     </row>
     <row r="1877">
@@ -44728,10 +44728,10 @@
         <v>-0.255853502776954</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.445256471416139</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.267653012286921</v>
       </c>
     </row>
     <row r="1878">
@@ -44751,10 +44751,10 @@
         <v>-0.3320435757902573</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.572895416030128</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.196582842637171</v>
       </c>
     </row>
     <row r="1879">
@@ -44774,10 +44774,10 @@
         <v>-0.3410221567092107</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.673308783947165</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.140817376371384</v>
       </c>
     </row>
     <row r="1880">
@@ -44797,10 +44797,10 @@
         <v>-0.29626252254881</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.599838952279717</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.200270976865274</v>
       </c>
     </row>
     <row r="1881">
@@ -44820,10 +44820,10 @@
         <v>-0.3517570687559104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.774963369666261</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.109751547180865</v>
       </c>
     </row>
     <row r="1882">
@@ -44843,10 +44843,10 @@
         <v>-0.4527570712633024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.774963369666261</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.102532382279269</v>
       </c>
     </row>
     <row r="1883">
@@ -44866,10 +44866,10 @@
         <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.879338100692707</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.033235352889425</v>
       </c>
     </row>
     <row r="1884">
@@ -44889,10 +44889,10 @@
         <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.975013587275104</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>1.976945850778543</v>
       </c>
     </row>
     <row r="1885">
@@ -44912,10 +44912,10 @@
         <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.949761964465361</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>1.994790553093504</v>
       </c>
     </row>
     <row r="1886">
@@ -44935,10 +44935,10 @@
         <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.949761964465361</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>1.998780888779904</v>
       </c>
     </row>
     <row r="1887">
@@ -44958,10 +44958,10 @@
         <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.949761964465361</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>1.997305661881162</v>
       </c>
     </row>
     <row r="1888">
@@ -44981,10 +44981,10 @@
         <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.900171120040528</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.042113578700935</v>
       </c>
     </row>
     <row r="1889">
@@ -45004,10 +45004,10 @@
         <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.868921529305354</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.047812199495356</v>
       </c>
     </row>
     <row r="1890">
@@ -45027,10 +45027,10 @@
         <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.826994853718191</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.082547277883863</v>
       </c>
     </row>
     <row r="1891">
@@ -45050,10 +45050,10 @@
         <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.826994853718191</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.083686422439921</v>
       </c>
     </row>
     <row r="1892">
@@ -45073,10 +45073,10 @@
         <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.822039507629745</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.089293404255097</v>
       </c>
     </row>
     <row r="1893">
@@ -45096,10 +45096,10 @@
         <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.822039507629745</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.095027108493733</v>
       </c>
     </row>
     <row r="1894">
@@ -45119,10 +45119,10 @@
         <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.750673115020097</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.128109681665657</v>
       </c>
     </row>
     <row r="1895">
@@ -45142,10 +45142,10 @@
         <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.750673115020097</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.118226200352749</v>
       </c>
     </row>
     <row r="1896">
@@ -45165,10 +45165,10 @@
         <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.750673115020097</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.116391639853376</v>
       </c>
     </row>
     <row r="1897">
@@ -45188,10 +45188,10 @@
         <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.68268736515954</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.156882774796249</v>
       </c>
     </row>
     <row r="1898">
@@ -45211,10 +45211,10 @@
         <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.658733824183583</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.171923405527317</v>
       </c>
     </row>
     <row r="1899">
@@ -45234,10 +45234,10 @@
         <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.394673885860787</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.317099052359243</v>
       </c>
     </row>
     <row r="1900">
@@ -45257,10 +45257,10 @@
         <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.394673885860787</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.314312018698942</v>
       </c>
     </row>
     <row r="1901">
@@ -45280,10 +45280,10 @@
         <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.354489587494596</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.338766221606497</v>
       </c>
     </row>
     <row r="1902">
@@ -45303,10 +45303,10 @@
         <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.191089716555233</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.436172965390872</v>
       </c>
     </row>
     <row r="1903">
@@ -45326,10 +45326,10 @@
         <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.9576084943256347</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.584186127566483</v>
       </c>
     </row>
     <row r="1904">
@@ -45349,10 +45349,10 @@
         <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.8647050030830987</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.637036011999045</v>
       </c>
     </row>
     <row r="1905">
@@ -45372,10 +45372,10 @@
         <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.7324295294522121</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.711768782924605</v>
       </c>
     </row>
     <row r="1906">
@@ -45395,10 +45395,10 @@
         <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5766911968924705</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.808026843148086</v>
       </c>
     </row>
     <row r="1907">
@@ -45418,10 +45418,10 @@
         <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5766911968924705</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.820933184371745</v>
       </c>
     </row>
     <row r="1908">
@@ -45441,10 +45441,10 @@
         <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.6822811866655749</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.629603260908664</v>
       </c>
     </row>
     <row r="1909">
@@ -45464,10 +45464,10 @@
         <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.6878771963257062</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.674789996989671</v>
       </c>
     </row>
     <row r="1910">
@@ -45487,10 +45487,10 @@
         <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.6675562804171487</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.567103623846638</v>
       </c>
     </row>
     <row r="1911">
@@ -45510,10 +45510,10 @@
         <v>0.5089641519027821</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6145867581631598</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.590171350945553</v>
       </c>
     </row>
     <row r="1912">
@@ -45533,10 +45533,10 @@
         <v>0.5194229025159651</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6145867581631598</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.58321073885046</v>
       </c>
     </row>
     <row r="1913">
@@ -45556,10 +45556,10 @@
         <v>0.5472305394886159</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6145867581631598</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.597673093231603</v>
       </c>
     </row>
     <row r="1914">
@@ -45579,10 +45579,10 @@
         <v>0.5850663147968196</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6145867581631598</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.592205213690798</v>
       </c>
     </row>
     <row r="1915">
@@ -45602,10 +45602,10 @@
         <v>0.6318808627342487</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.4912956233460293</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.663677988591654</v>
       </c>
     </row>
     <row r="1916">
@@ -45625,10 +45625,10 @@
         <v>0.6480415205329515</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4701464244425859</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.684068486171045</v>
       </c>
     </row>
     <row r="1917">
@@ -45648,10 +45648,10 @@
         <v>0.7413284056733795</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4701464244425859</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.679849194518095</v>
       </c>
     </row>
     <row r="1918">
@@ -45671,10 +45671,10 @@
         <v>0.7841578477043138</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4569273560501572</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.689904949473569</v>
       </c>
     </row>
     <row r="1919">
@@ -45694,10 +45694,10 @@
         <v>0.8768400802676455</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4569273560501572</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.682647024457271</v>
       </c>
     </row>
     <row r="1920">
@@ -45717,10 +45717,10 @@
         <v>0.9507960407752671</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4569273560501572</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.686246147977919</v>
       </c>
     </row>
     <row r="1921">
@@ -45740,10 +45740,10 @@
         <v>1.032702132038806</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.2854808930276941</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.802441531845951</v>
       </c>
     </row>
     <row r="1922">
@@ -45763,10 +45763,10 @@
         <v>1.061438435950439</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.2111913272893548</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.846035748905252</v>
       </c>
     </row>
     <row r="1923">
@@ -45786,10 +45786,10 @@
         <v>1.09158753389833</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1475555850554203</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.88891199529993</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.710602780646815</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.117352496412494</v>
+        <v>1.074042068544504</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1475555850554203</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.870106254083725</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.36189621417198</v>
+        <v>-4.470172283841955</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.215267771759315</v>
+        <v>1.171957343891325</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.09287491174944001</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>3.016107628791519</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.289653646000786</v>
+        <v>-4.39792971567076</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.248094112862613</v>
+        <v>1.204783684994623</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.09287491174944001</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>3.020036942626339</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.236655323719398</v>
+        <v>-4.344931393389373</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.269972025692508</v>
+        <v>1.226661597824519</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1482111707513789</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>3.053917281944842</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.127850438239671</v>
+        <v>-4.236126507909646</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.310492051104393</v>
+        <v>1.267181623236403</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1482111707513789</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>3.050915353164836</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.90782964020266</v>
+        <v>-4.016105709872635</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.400079407329811</v>
+        <v>1.356768979461821</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.2894310158193591</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.137226297216238</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.774961951139382</v>
+        <v>-3.883238020809357</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.469120665756946</v>
+        <v>1.425810237888956</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.2894310158193591</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.153120480018061</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.654788867774883</v>
+        <v>-3.763064937444858</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518335743543047</v>
+        <v>1.475025315675057</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.409604099183858</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.226370174477063</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.510116722675146</v>
+        <v>-3.61839279234512</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586292704144382</v>
+        <v>1.542982276276392</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.5542762442835955</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.323261564098345</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.569991550032838</v>
+        <v>-3.678267619702813</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.548380264602731</v>
+        <v>1.505069836734741</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.4944014169259033</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.273374159085156</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.450171319122</v>
+        <v>-3.558447388791975</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.611597526201274</v>
+        <v>1.568287098333284</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.4944014169259033</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.288663328319364</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.452641025583806</v>
+        <v>-3.560917095253781</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.518253842938994</v>
+        <v>1.474943415071004</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.4919317104640972</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.194825703764722</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.521011211907816</v>
+        <v>-3.629287281577791</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.410167629894691</v>
+        <v>1.366857202026701</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5012074095003122</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.119652984671752</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.534799264754863</v>
+        <v>-3.643075334424838</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.395089117387764</v>
+        <v>1.351778689519774</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5012074095003122</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.110089693303644</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.590319340647453</v>
+        <v>-3.698595410317427</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.50991192372293</v>
+        <v>1.46660149585494</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5012074095003122</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.295387835452043</v>
+        <v>3.247120529995846</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.414845080854983</v>
+        <v>-3.523121150524958</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.584668859631706</v>
+        <v>1.541358431763716</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5012074095003122</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.299955067443831</v>
+        <v>3.251687761987634</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.525781333496232</v>
+        <v>-3.634057403166207</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.516036387336413</v>
+        <v>1.472725959468423</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5012074095003122</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.275697096205038</v>
+        <v>3.227429790748841</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.49211778802395</v>
+        <v>-3.600393857693925</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.458040118926776</v>
+        <v>1.414729691058786</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5348709549725941</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.224433536889857</v>
+        <v>3.17616623143366</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.432265168820227</v>
+        <v>-3.540541238490202</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.492153553040398</v>
+        <v>1.448843125172408</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5348709549725941</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.234605923321989</v>
+        <v>3.186338617865792</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.346021705793849</v>
+        <v>-3.454297775463824</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.521597208824809</v>
+        <v>1.478286780956819</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5348709549725941</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.22955219389585</v>
+        <v>3.181284888439652</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.391328525192829</v>
+        <v>-3.499604594862804</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.495250256509742</v>
+        <v>1.451939828641752</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.4940607919633633</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.196841871534837</v>
+        <v>3.14857456607864</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.420361629895131</v>
+        <v>-3.528637699565106</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.484188887661923</v>
+        <v>1.440878459793933</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.4940607919633633</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.197393744567938</v>
+        <v>3.149126439111741</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.327551148444272</v>
+        <v>-3.435827218114246</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.450585772133633</v>
+        <v>1.407275344265643</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6673167825078846</v>
+        <v>0.5868712734142226</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.18235272532982</v>
+        <v>3.134085419873622</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.371940617773699</v>
+        <v>-3.480216687443674</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.434703460326462</v>
+        <v>1.391393032458472</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.622927313178457</v>
+        <v>0.542481804084795</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.157592519656764</v>
+        <v>3.109325214200567</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.259269399537449</v>
+        <v>-3.367545469207424</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.474847656132686</v>
+        <v>1.431537228264696</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.6551530223210451</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.220270959110237</v>
+        <v>3.172003653654039</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.146892398354777</v>
+        <v>-3.255168468024751</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.525289752436422</v>
+        <v>1.481979324568432</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.6551530223210451</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.225762254940904</v>
+        <v>3.177494949484707</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.17467279625613</v>
+        <v>-3.282948865926104</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.52567479504442</v>
+        <v>1.48236436717643</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.707818133513354</v>
+        <v>0.627372624419692</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.220591217968631</v>
+        <v>3.172323912512434</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.293053468986268</v>
+        <v>-3.401329538656243</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.316678245953018</v>
+        <v>1.273367818085028</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.5601547722687158</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.018616226678699</v>
+        <v>2.970348921222502</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.401667547429599</v>
+        <v>-3.509943617099574</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.393382275294891</v>
+        <v>1.350071847426901</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.5601547722687158</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.138765887397904</v>
+        <v>3.090498581941707</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.366258509181456</v>
+        <v>-3.474534578851431</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.422058916696471</v>
+        <v>1.378748488828481</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.5601547722687158</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.153278913500227</v>
+        <v>3.10501160804403</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.327874846623305</v>
+        <v>-3.43615091629328</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.4348318230621</v>
+        <v>1.39152139519411</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.678983943920529</v>
+        <v>0.598538434826867</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.173728552377487</v>
+        <v>3.12546124692129</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.150758516588139</v>
+        <v>-3.259034586258114</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.502407383921468</v>
+        <v>1.459096956053478</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.678983943920529</v>
+        <v>0.598538434826867</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.170457581222789</v>
+        <v>3.122190275766592</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.195850761421685</v>
+        <v>-3.30412683109166</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.485053877749963</v>
+        <v>1.441743449881973</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6170879007511392</v>
+        <v>0.5366423916574772</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.134003347083068</v>
+        <v>3.085736041626871</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.016475340182917</v>
+        <v>-3.124751409852892</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.550591021551885</v>
+        <v>1.507280593683895</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7738646589218579</v>
+        <v>0.6934191498281959</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.221856377291914</v>
+        <v>3.173589071835716</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.061489553703523</v>
+        <v>-3.169765623373498</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.513392791475232</v>
+        <v>1.470082363607242</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7435157636072532</v>
+        <v>0.6630702545135913</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.18445449543474</v>
+        <v>3.136187189978543</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.328494063975959</v>
+        <v>-3.436770133645934</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.412282549705203</v>
+        <v>1.368972121837214</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5491527255643047</v>
+        <v>0.4687072164706427</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.073528234947917</v>
+        <v>3.02526092949172</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.429691845413132</v>
+        <v>-3.537967915083106</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.371007359026836</v>
+        <v>1.327696931158846</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.4002984029253235</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.031686868717227</v>
+        <v>2.98341956326103</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.423180878798819</v>
+        <v>-3.531456948468794</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.371211707226877</v>
+        <v>1.327901279358888</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.4002984029253235</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.029286830271544</v>
+        <v>2.981019524815347</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.404142751091522</v>
+        <v>-3.512418820761496</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.375351677518041</v>
+        <v>1.332041249650051</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.422560300687791</v>
+        <v>0.3421147915941289</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.990901382681072</v>
+        <v>2.942634077224875</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.43526938224214</v>
+        <v>-3.543545451912114</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.540482893996475</v>
+        <v>1.497172466128485</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.422560300687791</v>
+        <v>0.3421147915941289</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.168483251619753</v>
+        <v>3.120215946163555</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.449136143576057</v>
+        <v>-3.557412213246032</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.535769518449041</v>
+        <v>1.492459090581051</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.304256874860306</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.146601830565592</v>
+        <v>3.098334525109395</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.404331972036127</v>
+        <v>-3.512608041706102</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.559699717461939</v>
+        <v>1.516389289593949</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.304256874860306</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.152610360962518</v>
+        <v>3.104343055506321</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.256589001801125</v>
+        <v>-3.3648650714711</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.516747126833139</v>
+        <v>1.47343669896515</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.4720642320951892</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.151244996580647</v>
+        <v>3.10297769112445</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.358603684332346</v>
+        <v>-3.466879754002321</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.478734875352132</v>
+        <v>1.435424447484142</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.4720642320951892</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.154038618112128</v>
+        <v>3.105771312655931</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.352450978279562</v>
+        <v>-3.460727047949536</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.481858306164904</v>
+        <v>1.438547878296914</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5586624472416355</v>
+        <v>0.4782169381479734</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.158392590135457</v>
+        <v>3.11012528467926</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.369260276430063</v>
+        <v>-3.477536346100038</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.474215063644814</v>
+        <v>1.430904635776824</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.4614076399974718</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.147387487985267</v>
+        <v>3.09912018252907</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.306962277653941</v>
+        <v>-3.415238347323916</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.565469816952084</v>
+        <v>1.522159389084094</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.4614076399974718</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.213723041782088</v>
+        <v>3.165455736325891</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.105172079988783</v>
+        <v>-3.213448149658758</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.448477897732274</v>
+        <v>1.405167469864284</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7398713412602882</v>
+        <v>0.6594258321666262</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.134825958797707</v>
+        <v>3.08655865334151</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.940359076909936</v>
+        <v>-3.048635146579911</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.584693331285988</v>
+        <v>1.541382903417998</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9046843443391351</v>
+        <v>0.8242388352454731</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.304003992967191</v>
+        <v>3.255736687510994</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.038099621534911</v>
+        <v>-3.146375691204885</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.560224849552042</v>
+        <v>1.516914421684052</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.888795066206155</v>
+        <v>0.808349557112493</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.309098162203446</v>
+        <v>3.260830856747249</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.21443738165784</v>
+        <v>-3.322713451327814</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.488225726327542</v>
+        <v>1.444915298459552</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.6320117969895636</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.20183148695436</v>
+        <v>3.153564181498163</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.138015335225913</v>
+        <v>-3.246291404895888</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.517286162940241</v>
+        <v>1.473975735072251</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.6320117969895636</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.200323104994289</v>
+        <v>3.152055799538092</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.093642203587344</v>
+        <v>-3.201918273257319</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.534898283031104</v>
+        <v>1.491587855163115</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.6763849286281322</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.226809851412866</v>
+        <v>3.178542545956669</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.970807982700177</v>
+        <v>-3.079084052370152</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.578425765524562</v>
+        <v>1.535115337656572</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.6763849286281322</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.221203645551457</v>
+        <v>3.172936340095259</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.923152252139121</v>
+        <v>-3.031428321809096</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.603869814776789</v>
+        <v>1.560559386908799</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8044861682828498</v>
+        <v>0.7240406591891878</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.256178840915895</v>
+        <v>3.207911535459698</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.822634093640366</v>
+        <v>-2.930910163310341</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.648969451551016</v>
+        <v>1.605659023683026</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9050043267816044</v>
+        <v>0.8245588176879424</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.321382109389872</v>
+        <v>3.273114803933675</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.883300684042756</v>
+        <v>-2.99157675371273</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.611457487865932</v>
+        <v>1.568147059997942</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8233060100630707</v>
+        <v>0.7428605009694087</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.259117791834624</v>
+        <v>3.210850486378427</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.838462282434357</v>
+        <v>-2.946738352104332</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.63349055111992</v>
+        <v>1.59018012325193</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8278494430079402</v>
+        <v>0.7474039339142782</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.265941554212175</v>
+        <v>3.217674248755977</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.857960738676366</v>
+        <v>-2.96623680834634</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.629852108254195</v>
+        <v>1.586541680386205</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7797648017280359</v>
+        <v>0.6993192926343739</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.24125170907531</v>
+        <v>3.192984403619113</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.813757901590465</v>
+        <v>-2.92203397126044</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.653412845616392</v>
+        <v>1.610102417748402</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8239676388139363</v>
+        <v>0.7435221297202743</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.273653013854688</v>
+        <v>3.22538570839849</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.850736929253908</v>
+        <v>-2.959012998923883</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.637031235020262</v>
+        <v>1.593720807152273</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.7804960315116048</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.294247355398733</v>
+        <v>3.245980049942536</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.692445511714636</v>
+        <v>-2.800721581384611</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.751595567219011</v>
+        <v>1.708285139351021</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.7804960315116048</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.345495120581773</v>
+        <v>3.297227815125576</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.48480350808016</v>
+        <v>-2.593079577750135</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.833093073267055</v>
+        <v>1.789782645399065</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.068583544239743</v>
+        <v>0.988138035146081</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.468521027356712</v>
+        <v>3.420253721900515</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.433771415357632</v>
+        <v>-2.542047485027607</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.848454138594336</v>
+        <v>1.805143710726346</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.119615636962271</v>
+        <v>1.039170127868609</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.494088511228499</v>
+        <v>3.445821205772301</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.368547234230427</v>
+        <v>-2.476823303900401</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.891731215137923</v>
+        <v>1.848420787269933</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.184839818089477</v>
+        <v>1.104394308995815</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.550410423997527</v>
+        <v>3.50214311854133</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.331120214159293</v>
+        <v>-2.439396283829268</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.902662995465657</v>
+        <v>1.859352567597667</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.190091356118658</v>
+        <v>1.109645847024996</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.549522319114316</v>
+        <v>3.501255013658119</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.351231870194001</v>
+        <v>-2.459507939863976</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.895875125383014</v>
+        <v>1.852564697515024</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.201118701116078</v>
+        <v>1.120673192022416</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.557395518444008</v>
+        <v>3.509128212987811</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.297487055766796</v>
+        <v>-2.405763125436771</v>
       </c>
       <c r="E1991" t="n">
-        <v>2.077930822175106</v>
+        <v>2.034620394307117</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.21118201055654</v>
+        <v>1.130736501462878</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.723991275129496</v>
+        <v>3.675723969673299</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.222704794741784</v>
+        <v>-2.330980864411758</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.227956635802929</v>
+        <v>2.184646207934939</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.285964271581552</v>
+        <v>1.20551876248789</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.888973540962321</v>
+        <v>3.840706235506124</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.196620710477976</v>
+        <v>-2.304896780147951</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.230098245522311</v>
+        <v>2.186787817654321</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.285964271581552</v>
+        <v>1.20551876248789</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.88068151697618</v>
+        <v>3.832414211519983</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.118489529629029</v>
+        <v>-2.226765599299004</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.259543913445669</v>
+        <v>2.216233485577679</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.360141082465237</v>
+        <v>1.279695573371575</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.92338079909017</v>
+        <v>3.875113493633973</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.109597068235746</v>
+        <v>-2.217873137905721</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.280655303729774</v>
+        <v>2.237344875861784</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.360141082465237</v>
+        <v>1.279695573371575</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.940935204816961</v>
+        <v>3.892667899360764</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.278073185205624</v>
+        <v>-2.386349254875598</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.205119904346406</v>
+        <v>2.161809476478417</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.332193246748656</v>
+        <v>1.251747737654994</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.916021550791597</v>
+        <v>3.8677542453354</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.58027365634404</v>
+        <v>-1.688549726014015</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.465509413078902</v>
+        <v>2.422198985210912</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.261845187378245</v>
+        <v>1.181399678284583</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.855082412357213</v>
+        <v>3.806815106901015</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.557552552660888</v>
+        <v>-1.665828622330863</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.465261877049067</v>
+        <v>2.421951449181077</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.261845187378245</v>
+        <v>1.181399678284583</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.845746434854117</v>
+        <v>3.79747912939792</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.555827509370844</v>
+        <v>-1.664103579040819</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.624858020216254</v>
+        <v>2.581547592348264</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.263570230668289</v>
+        <v>1.183124721574627</v>
       </c>
       <c r="G1999" t="n">
-        <v>4.005687586679312</v>
+        <v>3.957420281223115</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.7106085161491</v>
+        <v>-1.818884585819074</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.600023439998598</v>
+        <v>2.556713012130608</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.230202556613813</v>
+        <v>1.149757047520151</v>
       </c>
       <c r="G2000" t="n">
-        <v>4.022744804740273</v>
+        <v>3.974477499284076</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.703553825933926</v>
+        <v>-1.811829895603901</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.599520672074213</v>
+        <v>2.556210244206223</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.237257246828987</v>
+        <v>1.156811737735325</v>
       </c>
       <c r="G2001" t="n">
-        <v>4.023652974858923</v>
+        <v>3.975385669402725</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.676602601607438</v>
+        <v>-1.784878671277413</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.62030731544955</v>
+        <v>2.57699688758156</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.252137592856706</v>
+        <v>1.171692083763044</v>
       </c>
       <c r="G2002" t="n">
-        <v>4.042587336120295</v>
+        <v>3.994320030664099</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.812555609663754</v>
+        <v>-1.920831679333729</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.750029244371983</v>
+        <v>2.706718816503993</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.252137592856706</v>
+        <v>1.171692083763044</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.226690468265256</v>
+        <v>4.178423162809058</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.834963727468626</v>
+        <v>-1.943239797138601</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.733182692153027</v>
+        <v>2.689872264285037</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.252137592856706</v>
+        <v>1.171692083763044</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.218807163168249</v>
+        <v>4.170539857712051</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.982969494948025</v>
+        <v>-2.091245564618</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.676034384710905</v>
+        <v>2.632723956842915</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.165410583993165</v>
+        <v>1.084965074899503</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.168824957399761</v>
+        <v>4.120557651943564</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.992410420836555</v>
+        <v>-2.10068649050653</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.72851173207734</v>
+        <v>2.68520130420935</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.287837701536556</v>
+        <v>1.207392192442894</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.298534945647643</v>
+        <v>4.250267640191446</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.044684028172196</v>
+        <v>-2.152960097842171</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.710493383688385</v>
+        <v>2.667182955820394</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.235564094200915</v>
+        <v>1.155118585107253</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.270061875791559</v>
+        <v>4.221794570335362</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.121014005773102</v>
+        <v>-2.229290075443077</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.678073205541797</v>
+        <v>2.634762777673807</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.235564094200915</v>
+        <v>1.155118585107253</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.268173688685335</v>
+        <v>4.219906383229137</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.232770958388403</v>
+        <v>-2.341047028058378</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.628190654098539</v>
+        <v>2.584880226230549</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.123807141585614</v>
+        <v>1.043361632491952</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.195939746719016</v>
+        <v>4.147672441262819</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.230929939330152</v>
+        <v>-2.339206009000127</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.627361071931992</v>
+        <v>2.584050644064002</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.125075368257082</v>
+        <v>1.04462985916342</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.195134692932049</v>
+        <v>4.146867387475853</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.363231231427705</v>
+        <v>-2.47150730109768</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.587513961958889</v>
+        <v>2.544203534090899</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.125075368257082</v>
+        <v>1.04462985916342</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.208208099797968</v>
+        <v>4.159940794341771</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.364792874242565</v>
+        <v>-2.473068943912541</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.586889304832945</v>
+        <v>2.543578876964955</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.125075368257082</v>
+        <v>1.04462985916342</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.208208099797968</v>
+        <v>4.159940794341771</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.392693661352038</v>
+        <v>-2.500969731022014</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.574253031116158</v>
+        <v>2.530942603248168</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.090478444114147</v>
+        <v>1.010032935020485</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.185973986439209</v>
+        <v>4.137706680983012</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.515219764054932</v>
+        <v>-2.623495833724907</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.5220070340122</v>
+        <v>2.478696606144209</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9679523414112534</v>
+        <v>0.8875068323175914</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.109222768794671</v>
+        <v>4.060955463338474</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.535281085331439</v>
+        <v>-2.643557155001414</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.5806884650921</v>
+        <v>2.53737803722411</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9478910201347464</v>
+        <v>0.8674455110410844</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.163891935619271</v>
+        <v>4.115624630163074</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.792001903326263</v>
+        <v>-2.900277972996238</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.618311856896018</v>
+        <v>2.575001429028028</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7590309368972695</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.239154910134829</v>
+        <v>4.190887604678633</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622233</v>
       </c>
       <c r="C2017" t="n">
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.945988321102403</v>
+        <v>-3.054264390772379</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.625697558931201</v>
+        <v>2.582387131063211</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7590309368972695</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.308135179280469</v>
+        <v>4.259867873824271</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.895466417274737</v>
+        <v>-3.003742486944713</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.631957522582389</v>
+        <v>2.588647094714398</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7590309368972695</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.29418638140059</v>
+        <v>4.245919075944393</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994891</v>
       </c>
       <c r="C2019" t="n">
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.147941571282462</v>
+        <v>-3.256217640952437</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.542837950034713</v>
+        <v>2.499527522166723</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7590309368972695</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.306056870456004</v>
+        <v>4.257789564999807</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358295</v>
       </c>
       <c r="C2020" t="n">
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.41741437320417</v>
+        <v>-3.532707121872057</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.436259363784973</v>
+        <v>2.390142264317818</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7590309368972695</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.307267404974947</v>
+        <v>4.259000099518751</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.574958444933611</v>
+        <v>-3.690251193601498</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.377363477320518</v>
+        <v>2.331246377853363</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7725746408506571</v>
+        <v>0.6921291317569951</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.271248064118105</v>
+        <v>4.222980758661907</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.65216331330134</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.703808995635657</v>
+        <v>-3.819101744303544</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.320901109775889</v>
+        <v>2.274784010308734</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.6511357229062735</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.24172987154386</v>
+        <v>4.193462566087664</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.820776688274548</v>
+        <v>-3.936069436942435</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.436318089419377</v>
+        <v>2.390200989952222</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.6511357229062735</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.403933928242905</v>
+        <v>4.355666622786708</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456689</v>
       </c>
       <c r="C2024" t="n">
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.905494630495502</v>
+        <v>-4.020787379163389</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.39727755049481</v>
+        <v>2.351160451027654</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6464652030718891</v>
+        <v>0.5660196939782272</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.347710948849891</v>
+        <v>4.299443643393694</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.987429448764386</v>
+        <v>-4.102722197432272</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.374733040755748</v>
+        <v>2.328615941288593</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.636530457484809</v>
+        <v>0.556084948391147</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.351979519066135</v>
+        <v>4.303712213609938</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.933691275364124</v>
+        <v>-4.04898402403201</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.405153948571755</v>
+        <v>2.3590368491046</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6902686308850711</v>
+        <v>0.6098231217914091</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.393148061562195</v>
+        <v>4.344880756105997</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.823684991886902</v>
+        <v>-3.938977740554789</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.441309349206819</v>
+        <v>2.395192249739664</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7134732028023463</v>
+        <v>0.6330276937086843</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.399223691956735</v>
+        <v>4.350956386500538</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.680625416145976</v>
+        <v>-3.795918164813863</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.502783190225164</v>
+        <v>2.456666090758009</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7214866293923256</v>
+        <v>0.6410411202986636</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.408281758632697</v>
+        <v>4.360014453176499</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.379178690674139</v>
+        <v>-3.494471439342026</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.630622763296435</v>
+        <v>2.58450566382928</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9424878457705008</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.596410676798335</v>
+        <v>4.548143371342139</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.434133887117208</v>
+        <v>-3.549426635785095</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.609611862471918</v>
+        <v>2.563494763004763</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9424878457705008</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.597381854551045</v>
+        <v>4.549114549094849</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.383095511110688</v>
+        <v>-3.498388259778574</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.630870117254281</v>
+        <v>2.584753017787127</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9424878457705008</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.598224758930801</v>
+        <v>4.549957453474605</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354685</v>
+        <v>3.831748677354682</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.380714357235552</v>
+        <v>-3.457248964911944</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.650860677678481</v>
+        <v>2.620246834607924</v>
       </c>
       <c r="F2032" t="n">
-        <v>1.025314508739298</v>
+        <v>0.9836271406371316</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.618691550130028</v>
+        <v>4.593679129268728</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.77052299397603</v>
+        <v>3.805143348333665</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.980133892981399</v>
+        <v>4.028475469687634</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.380714357235552</v>
+        <v>-3.457248964911944</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.650860677678481</v>
+        <v>2.620246834607924</v>
       </c>
       <c r="F2033" t="n">
-        <v>1.025314508739298</v>
+        <v>0.9836271406371316</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.973197689967766</v>
+        <v>4.021539266674002</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240722.xlsx
+++ b/tame_output/ON/bt/strategyON_20240722.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>79.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,32 +844,32 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>59.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.4%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.2%</t>
+          <t>-68.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.7%</t>
+          <t>452.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-507.3%</t>
+          <t>-521.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-114.2%</t>
+          <t>-119.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-126.9%</t>
+          <t>-131.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-125.6%</t>
+          <t>-117.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1471,42 +1471,42 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-43.9%</t>
+          <t>-75.2%</t>
         </is>
       </c>
     </row>
@@ -44383,10 +44383,10 @@
         <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.3846419795235408</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.83837196775276</v>
+        <v>2.886639273208957</v>
       </c>
     </row>
     <row r="1863">
@@ -44406,10 +44406,10 @@
         <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7613982729162152</v>
+        <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.659840012179184</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44429,10 +44429,10 @@
         <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.169987050096894</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.413448289885536</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44452,10 +44452,10 @@
         <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.169987050096894</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.408633722356996</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44475,10 +44475,10 @@
         <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.169987050096894</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.406627772965874</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44498,10 +44498,10 @@
         <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.169987050096894</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.416886463634553</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44521,10 +44521,10 @@
         <v>0.3165746066023623</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.169987050096894</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.412986028780248</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44544,10 +44544,10 @@
         <v>0.2956983997604259</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.169987050096894</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.411390948835249</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44567,10 +44567,10 @@
         <v>0.1808128389655548</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.238730185830772</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.37392404332413</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44590,10 +44590,10 @@
         <v>0.1020986511074309</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.238730185830772</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.369897738789727</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44613,10 +44613,10 @@
         <v>-0.05120400571120598</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.238730185830772</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.369795637468143</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44636,10 +44636,10 @@
         <v>-0.05042706782033113</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.243216631032161</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.36967528631874</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44659,10 +44659,10 @@
         <v>-0.1888888935238819</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.243216631032161</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.37502558961679</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44682,10 +44682,10 @@
         <v>-0.2011124989483934</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.293565694486383</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.352732171501434</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44705,10 +44705,10 @@
         <v>-0.2371184592951829</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.39118497190778</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.297202355670365</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44728,10 +44728,10 @@
         <v>-0.255853502776954</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.445256471416139</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.267653012286921</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44751,10 +44751,10 @@
         <v>-0.3320435757902573</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.572895416030128</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.196582842637171</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44774,10 +44774,10 @@
         <v>-0.3410221567092107</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.673308783947165</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.140817376371384</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44797,10 +44797,10 @@
         <v>-0.29626252254881</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.599838952279717</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.200270976865274</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44820,10 +44820,10 @@
         <v>-0.3517570687559104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.774963369666261</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.109751547180865</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44843,10 +44843,10 @@
         <v>-0.4527570712633024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.774963369666261</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.102532382279269</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44866,10 +44866,10 @@
         <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.879338100692707</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.033235352889425</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44889,10 +44889,10 @@
         <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.975013587275104</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.976945850778543</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44912,10 +44912,10 @@
         <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.949761964465361</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.994790553093504</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44935,10 +44935,10 @@
         <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.949761964465361</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.998780888779904</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44958,10 +44958,10 @@
         <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.949761964465361</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.997305661881162</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44981,10 +44981,10 @@
         <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.900171120040528</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.042113578700935</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45004,10 +45004,10 @@
         <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.868921529305354</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.047812199495356</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45027,10 +45027,10 @@
         <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.826994853718191</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.082547277883863</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45050,10 +45050,10 @@
         <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.826994853718191</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.083686422439921</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45073,10 +45073,10 @@
         <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.822039507629745</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.089293404255097</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45096,10 +45096,10 @@
         <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.822039507629745</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.095027108493733</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45119,10 +45119,10 @@
         <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.750673115020097</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.128109681665657</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45142,10 +45142,10 @@
         <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.750673115020097</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.118226200352749</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.672030763858595</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.3023732209917522</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.750673115020097</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.116391639853376</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.574123725182105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.2635107204946165</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.68268736515954</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.156882774796249</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.550170184206147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.25326079795874</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.658733824183583</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.171923405527317</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-8.28611024588335</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.1608971387913734</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.394673885860787</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.317099052359243</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.579030622378512</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.1191476769502611</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.394673885860787</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.314312018698942</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.538846324012321</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.1355650201845786</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.354489587494596</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.338766221606497</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.375446453072959</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.2002917897810805</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.191089716555233</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.436172965390872</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-7.14196523084336</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.3016087075107725</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9576084943256347</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.584186127566483</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-6.992298839835845</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.3585830536008192</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8647050030830987</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.637036011999045</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.860023366204959</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.4068607298002007</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7324295294522121</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.711768782924605</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.704285033645217</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.4719711235117341</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5766911968924705</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.808026843148086</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.455285234961636</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.5844773842088253</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5766911968924705</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.820933184371745</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.56087522473474</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.4142654587003651</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6822811866655749</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.629603260908664</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.579610126853337</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.4553158397300123</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6878771963257062</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.674789996989671</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.431670085445738</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.3946129336048845</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6675562804171487</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.567103623846638</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.378700563191749</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5089641519027821</v>
+        <v>0.4070867562530021</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.6145867581631598</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.590171350945553</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.335152156421059</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5194229025159651</v>
+        <v>0.4175455068661851</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.6145867581631598</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.58321073885046</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.04709546081784</v>
+        <v>-6.30178894994229</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5472305394886159</v>
+        <v>0.4453531438388354</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.6145867581631598</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.597673093231603</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.938836323695318</v>
+        <v>-6.193529812819769</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5850663147968196</v>
+        <v>0.4831889191470391</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.6145867581631598</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.592205213690798</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.815545188878187</v>
+        <v>-6.070238678002638</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6318808627342487</v>
+        <v>0.5300034670844682</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4912956233460293</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.663677988591654</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.794395989974744</v>
+        <v>-6.049089479099194</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6480415205329515</v>
+        <v>0.546164124883171</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.4701464244425859</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.684068486171045</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.550630547991299</v>
+        <v>-5.80532403711575</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7413284056733795</v>
+        <v>0.6394510100235995</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.4701464244425859</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.679849194518095</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.448867727714005</v>
+        <v>-5.703561216838455</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7841578477043138</v>
+        <v>0.6822804520545334</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4569273560501572</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.689904949473569</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.19901733376493</v>
+        <v>-5.453710822889381</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8768400802676455</v>
+        <v>0.7749626846178654</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4569273560501572</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.682647024457271</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.023125241297498</v>
+        <v>-5.277818730421949</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9507960407752671</v>
+        <v>0.8489186451254871</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4569273560501572</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.686246147977919</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.851678778275034</v>
+        <v>-5.106372267399485</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.032702132038806</v>
+        <v>0.9308247363890261</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2854808930276941</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.802441531845951</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.777389212536695</v>
+        <v>-5.032082701661146</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.061438435950439</v>
+        <v>0.9595610403006587</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.2111913272893548</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.846035748905252</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.713753470302761</v>
+        <v>-4.968446959427212</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.09158753389833</v>
+        <v>0.9897101382485496</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1475555850554203</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.88891199529993</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.710602780646815</v>
+        <v>-4.857020200101291</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.074042068544504</v>
+        <v>1.015475100762713</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1475555850554203</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.870106254083725</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.470172283841955</v>
+        <v>-4.616589703296431</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.171957343891325</v>
+        <v>1.113390376109535</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.09287491174944001</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.016107628791519</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367683</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.39792971567076</v>
+        <v>-4.544347135125236</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.204783684994623</v>
+        <v>1.146216717212833</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.09287491174944001</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.020036942626339</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.344931393389373</v>
+        <v>-4.491348812843849</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.226661597824519</v>
+        <v>1.168094630042728</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1482111707513789</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.053917281944842</v>
+        <v>3.10218458740104</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.236126507909646</v>
+        <v>-4.382543927364122</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.267181623236403</v>
+        <v>1.208614655454612</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1482111707513789</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.050915353164836</v>
+        <v>3.099182658621033</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.016105709872635</v>
+        <v>-4.162523129327111</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.356768979461821</v>
+        <v>1.298202011680031</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2894310158193591</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.137226297216238</v>
+        <v>3.185493602672435</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.883238020809357</v>
+        <v>-4.029655440263833</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.425810237888956</v>
+        <v>1.367243270107165</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2894310158193591</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.153120480018061</v>
+        <v>3.201387785474259</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.763064937444858</v>
+        <v>-3.909482356899335</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.475025315675057</v>
+        <v>1.416458347893266</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.409604099183858</v>
+        <v>0.4900496082775201</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.226370174477063</v>
+        <v>3.27463747993326</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.61839279234512</v>
+        <v>-3.764810211799597</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.542982276276392</v>
+        <v>1.484415308494601</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5542762442835955</v>
+        <v>0.6347217533772576</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.323261564098345</v>
+        <v>3.371528869554542</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.678267619702813</v>
+        <v>-3.82468503915729</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.505069836734741</v>
+        <v>1.44650286895295</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4944014169259033</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.273374159085156</v>
+        <v>3.321641464541353</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.558447388791975</v>
+        <v>-3.704864808246452</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.568287098333284</v>
+        <v>1.509720130551494</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4944014169259033</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.288663328319364</v>
+        <v>3.336930633775562</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.560917095253781</v>
+        <v>-3.707334514708258</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.474943415071004</v>
+        <v>1.416376447289213</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4919317104640972</v>
+        <v>0.5723772195577592</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.194825703764722</v>
+        <v>3.243093009220919</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.629287281577791</v>
+        <v>-3.775704701032268</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.366857202026701</v>
+        <v>1.30829023424491</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5012074095003122</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.119652984671752</v>
+        <v>3.16792029012795</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.643075334424838</v>
+        <v>-3.789492753879315</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.351778689519774</v>
+        <v>1.293211721737983</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5012074095003122</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.110089693303644</v>
+        <v>3.158356998759841</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.698595410317427</v>
+        <v>-3.845012829771904</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.46660149585494</v>
+        <v>1.408034528073149</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5012074095003122</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.247120529995846</v>
+        <v>3.295387835452043</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.523121150524958</v>
+        <v>-3.669538569979435</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.541358431763716</v>
+        <v>1.482791463981925</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5012074095003122</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.251687761987634</v>
+        <v>3.299955067443831</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.634057403166207</v>
+        <v>-3.780474822620683</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.472725959468423</v>
+        <v>1.414158991686633</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5012074095003122</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.227429790748841</v>
+        <v>3.275697096205038</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.600393857693925</v>
+        <v>-3.746811277148402</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.414729691058786</v>
+        <v>1.356162723276995</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5348709549725941</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.17616623143366</v>
+        <v>3.224433536889857</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.540541238490202</v>
+        <v>-3.686958657944678</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.448843125172408</v>
+        <v>1.390276157390617</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5348709549725941</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.186338617865792</v>
+        <v>3.234605923321989</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.454297775463824</v>
+        <v>-3.600715194918301</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.478286780956819</v>
+        <v>1.419719813175028</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5348709549725941</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.181284888439652</v>
+        <v>3.22955219389585</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.499604594862804</v>
+        <v>-3.646022014317281</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.451939828641752</v>
+        <v>1.393372860859962</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4940607919633633</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.14857456607864</v>
+        <v>3.196841871534837</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.528637699565106</v>
+        <v>-3.675055119019583</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.440878459793933</v>
+        <v>1.382311492012143</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4940607919633633</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.149126439111741</v>
+        <v>3.197393744567938</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.435827218114246</v>
+        <v>-3.582244637568723</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.407275344265643</v>
+        <v>1.348708376483852</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5868712734142226</v>
+        <v>0.6673167825078846</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.134085419873622</v>
+        <v>3.18235272532982</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.480216687443674</v>
+        <v>-3.626634106898151</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.391393032458472</v>
+        <v>1.332826064676682</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.542481804084795</v>
+        <v>0.622927313178457</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.109325214200567</v>
+        <v>3.157592519656764</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.367545469207424</v>
+        <v>-3.513962888661901</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.431537228264696</v>
+        <v>1.372970260482905</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6551530223210451</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.172003653654039</v>
+        <v>3.220270959110237</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.255168468024751</v>
+        <v>-3.401585887479228</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.481979324568432</v>
+        <v>1.423412356786641</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6551530223210451</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.177494949484707</v>
+        <v>3.225762254940904</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.282948865926104</v>
+        <v>-3.429366285380581</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.48236436717643</v>
+        <v>1.423797399394639</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.627372624419692</v>
+        <v>0.707818133513354</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.172323912512434</v>
+        <v>3.220591217968631</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.401329538656243</v>
+        <v>-3.54774695811072</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.273367818085028</v>
+        <v>1.214800850303237</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5601547722687158</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.970348921222502</v>
+        <v>3.018616226678699</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.509943617099574</v>
+        <v>-3.656361036554051</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.350071847426901</v>
+        <v>1.29150487964511</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5601547722687158</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.090498581941707</v>
+        <v>3.138765887397904</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.474534578851431</v>
+        <v>-3.620951998305908</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.378748488828481</v>
+        <v>1.32018152104669</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5601547722687158</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.10501160804403</v>
+        <v>3.153278913500227</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.43615091629328</v>
+        <v>-3.582568335747757</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.39152139519411</v>
+        <v>1.332954427412319</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.598538434826867</v>
+        <v>0.678983943920529</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.12546124692129</v>
+        <v>3.173728552377487</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.259034586258114</v>
+        <v>-3.405452005712591</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.459096956053478</v>
+        <v>1.400529988271688</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.598538434826867</v>
+        <v>0.678983943920529</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.122190275766592</v>
+        <v>3.170457581222789</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.30412683109166</v>
+        <v>-3.450544250546137</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.441743449881973</v>
+        <v>1.383176482100182</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5366423916574772</v>
+        <v>0.6170879007511392</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.085736041626871</v>
+        <v>3.134003347083068</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.124751409852892</v>
+        <v>-3.271168829307369</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.507280593683895</v>
+        <v>1.448713625902104</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6934191498281959</v>
+        <v>0.7738646589218579</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.173589071835716</v>
+        <v>3.221856377291914</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.169765623373498</v>
+        <v>-3.316183042827975</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.470082363607242</v>
+        <v>1.411515395825451</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6630702545135913</v>
+        <v>0.7435157636072532</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.136187189978543</v>
+        <v>3.18445449543474</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.436770133645934</v>
+        <v>-3.58318755310041</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.368972121837214</v>
+        <v>1.310405154055423</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4687072164706427</v>
+        <v>0.5491527255643047</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.02526092949172</v>
+        <v>3.073528234947917</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.537967915083106</v>
+        <v>-3.684385334537583</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.327696931158846</v>
+        <v>1.269129963377055</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4002984029253235</v>
+        <v>0.4807439120189855</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.98341956326103</v>
+        <v>3.031686868717227</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.531456948468794</v>
+        <v>-3.677874367923271</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.327901279358888</v>
+        <v>1.269334311577097</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4002984029253235</v>
+        <v>0.4807439120189855</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.981019524815347</v>
+        <v>3.029286830271544</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.512418820761496</v>
+        <v>-3.658836240215973</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.332041249650051</v>
+        <v>1.273474281868261</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3421147915941289</v>
+        <v>0.422560300687791</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.942634077224875</v>
+        <v>2.990901382681072</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.543545451912114</v>
+        <v>-3.689962871366591</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.497172466128485</v>
+        <v>1.438605498346694</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3421147915941289</v>
+        <v>0.422560300687791</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.120215946163555</v>
+        <v>3.168483251619753</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.557412213246032</v>
+        <v>-3.703829632700509</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.492459090581051</v>
+        <v>1.43389212279926</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.304256874860306</v>
+        <v>0.3847023839539681</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.098334525109395</v>
+        <v>3.146601830565592</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.512608041706102</v>
+        <v>-3.659025461160579</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.516389289593949</v>
+        <v>1.457822321812158</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.304256874860306</v>
+        <v>0.3847023839539681</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.104343055506321</v>
+        <v>3.152610360962518</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.3648650714711</v>
+        <v>-3.511282490925577</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.47343669896515</v>
+        <v>1.414869731183359</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4720642320951892</v>
+        <v>0.5525097411888512</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.10297769112445</v>
+        <v>3.151244996580647</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.466879754002321</v>
+        <v>-3.613297173456798</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.435424447484142</v>
+        <v>1.376857479702351</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4720642320951892</v>
+        <v>0.5525097411888512</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.105771312655931</v>
+        <v>3.154038618112128</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.460727047949536</v>
+        <v>-3.607144467404013</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.438547878296914</v>
+        <v>1.379980910515124</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4782169381479734</v>
+        <v>0.5586624472416355</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.11012528467926</v>
+        <v>3.158392590135457</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.477536346100038</v>
+        <v>-3.623953765554515</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.430904635776824</v>
+        <v>1.372337667995033</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4614076399974718</v>
+        <v>0.5418531490911338</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.09912018252907</v>
+        <v>3.147387487985267</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.415238347323916</v>
+        <v>-3.561655766778393</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.522159389084094</v>
+        <v>1.463592421302303</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4614076399974718</v>
+        <v>0.5418531490911338</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.165455736325891</v>
+        <v>3.213723041782088</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.213448149658758</v>
+        <v>-3.359865569113235</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.405167469864284</v>
+        <v>1.346600502082493</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6594258321666262</v>
+        <v>0.7398713412602882</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.08655865334151</v>
+        <v>3.134825958797707</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.048635146579911</v>
+        <v>-3.195052566034388</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.541382903417998</v>
+        <v>1.482815935636207</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8242388352454731</v>
+        <v>0.9046843443391351</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.255736687510994</v>
+        <v>3.304003992967191</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.146375691204885</v>
+        <v>-3.292793110659362</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.516914421684052</v>
+        <v>1.458347453902261</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.808349557112493</v>
+        <v>0.888795066206155</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.260830856747249</v>
+        <v>3.309098162203446</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.322713451327814</v>
+        <v>-3.469130870782291</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.444915298459552</v>
+        <v>1.386348330677761</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6320117969895636</v>
+        <v>0.7124573060832255</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.153564181498163</v>
+        <v>3.20183148695436</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397797</v>
       </c>
       <c r="C1975" t="n">
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.246291404895888</v>
+        <v>-3.392708824350365</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.473975735072251</v>
+        <v>1.41540876729046</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6320117969895636</v>
+        <v>0.7124573060832255</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.152055799538092</v>
+        <v>3.200323104994289</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.201918273257319</v>
+        <v>-3.348335692711796</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.491587855163115</v>
+        <v>1.433020887381324</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6763849286281322</v>
+        <v>0.7568304377217941</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.178542545956669</v>
+        <v>3.226809851412866</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.079084052370152</v>
+        <v>-3.225501471824629</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.535115337656572</v>
+        <v>1.476548369874781</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6763849286281322</v>
+        <v>0.7568304377217941</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.172936340095259</v>
+        <v>3.221203645551457</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.031428321809096</v>
+        <v>-3.177845741263573</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.560559386908799</v>
+        <v>1.501992419127008</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7240406591891878</v>
+        <v>0.8044861682828498</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.207911535459698</v>
+        <v>3.256178840915895</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.930910163310341</v>
+        <v>-3.077327582764818</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.605659023683026</v>
+        <v>1.547092055901235</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8245588176879424</v>
+        <v>0.9050043267816044</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.273114803933675</v>
+        <v>3.321382109389872</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557296</v>
       </c>
       <c r="C1980" t="n">
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.99157675371273</v>
+        <v>-3.137994173167207</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.568147059997942</v>
+        <v>1.509580092216152</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7428605009694087</v>
+        <v>0.8233060100630707</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.210850486378427</v>
+        <v>3.259117791834624</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932771</v>
       </c>
       <c r="C1981" t="n">
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.946738352104332</v>
+        <v>-3.093155771558809</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.59018012325193</v>
+        <v>1.531613155470139</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7474039339142782</v>
+        <v>0.8278494430079402</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.217674248755977</v>
+        <v>3.265941554212175</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.96623680834634</v>
+        <v>-3.112654227800817</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.586541680386205</v>
+        <v>1.527974712604414</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6993192926343739</v>
+        <v>0.7797648017280359</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.192984403619113</v>
+        <v>3.24125170907531</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.92203397126044</v>
+        <v>-3.068451390714917</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.610102417748402</v>
+        <v>1.551535449966611</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7435221297202743</v>
+        <v>0.8239676388139363</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.22538570839849</v>
+        <v>3.273653013854688</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.959012998923883</v>
+        <v>-3.10543041837836</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.593720807152273</v>
+        <v>1.535153839370482</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7804960315116048</v>
+        <v>0.8609415406052668</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.245980049942536</v>
+        <v>3.294247355398733</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.800721581384611</v>
+        <v>-2.947139000839088</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.708285139351021</v>
+        <v>1.64971817156923</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7804960315116048</v>
+        <v>0.8609415406052668</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.297227815125576</v>
+        <v>3.345495120581773</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.593079577750135</v>
+        <v>-2.739496997204612</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.789782645399065</v>
+        <v>1.731215677617274</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.988138035146081</v>
+        <v>1.068583544239743</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.420253721900515</v>
+        <v>3.468521027356712</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.86448984247514</v>
       </c>
       <c r="C1987" t="n">
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.542047485027607</v>
+        <v>-2.688464904482084</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.805143710726346</v>
+        <v>1.746576742944555</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.039170127868609</v>
+        <v>1.119615636962271</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.445821205772301</v>
+        <v>3.494088511228499</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.476823303900401</v>
+        <v>-2.623240723354878</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.848420787269933</v>
+        <v>1.789853819488142</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.104394308995815</v>
+        <v>1.184839818089477</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.50214311854133</v>
+        <v>3.550410423997527</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.439396283829268</v>
+        <v>-2.585813703283744</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.859352567597667</v>
+        <v>1.800785599815876</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.109645847024996</v>
+        <v>1.190091356118658</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.501255013658119</v>
+        <v>3.549522319114316</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.459507939863976</v>
+        <v>-2.605925359318453</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.852564697515024</v>
+        <v>1.793997729733233</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.120673192022416</v>
+        <v>1.201118701116078</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.509128212987811</v>
+        <v>3.557395518444008</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.405763125436771</v>
+        <v>-2.552180544891248</v>
       </c>
       <c r="E1991" t="n">
-        <v>2.034620394307117</v>
+        <v>1.976053426525326</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.130736501462878</v>
+        <v>1.21118201055654</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.675723969673299</v>
+        <v>3.723991275129496</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.330980864411758</v>
+        <v>-2.477398283866235</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.184646207934939</v>
+        <v>2.126079240153148</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.20551876248789</v>
+        <v>1.285964271581552</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.840706235506124</v>
+        <v>3.888973540962321</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.304896780147951</v>
+        <v>-2.451314199602427</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.186787817654321</v>
+        <v>2.12822084987253</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.20551876248789</v>
+        <v>1.285964271581552</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.832414211519983</v>
+        <v>3.88068151697618</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.226765599299004</v>
+        <v>-2.373183018753481</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.216233485577679</v>
+        <v>2.157666517795888</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.279695573371575</v>
+        <v>1.360141082465237</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.875113493633973</v>
+        <v>3.92338079909017</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.217873137905721</v>
+        <v>-2.364290557360198</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.237344875861784</v>
+        <v>2.178777908079993</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.279695573371575</v>
+        <v>1.360141082465237</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.892667899360764</v>
+        <v>3.940935204816961</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.386349254875598</v>
+        <v>-2.532766674330075</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.161809476478417</v>
+        <v>2.103242508696626</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.251747737654994</v>
+        <v>1.332193246748656</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.8677542453354</v>
+        <v>3.916021550791597</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.688549726014015</v>
+        <v>-1.834967145468492</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.422198985210912</v>
+        <v>2.363632017429121</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.181399678284583</v>
+        <v>1.261845187378245</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.806815106901015</v>
+        <v>3.855082412357213</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.665828622330863</v>
+        <v>-1.81224604178534</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.421951449181077</v>
+        <v>2.363384481399287</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.181399678284583</v>
+        <v>1.261845187378245</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.79747912939792</v>
+        <v>3.845746434854117</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.664103579040819</v>
+        <v>-1.810520998495296</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.581547592348264</v>
+        <v>2.522980624566473</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.183124721574627</v>
+        <v>1.263570230668289</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.957420281223115</v>
+        <v>4.005687586679312</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.818884585819074</v>
+        <v>-1.965302005273551</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.556713012130608</v>
+        <v>2.498146044348817</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.149757047520151</v>
+        <v>1.230202556613813</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.974477499284076</v>
+        <v>4.022744804740273</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.811829895603901</v>
+        <v>-1.958247315058377</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.556210244206223</v>
+        <v>2.497643276424432</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.156811737735325</v>
+        <v>1.237257246828987</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.975385669402725</v>
+        <v>4.023652974858923</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.784878671277413</v>
+        <v>-1.931296090731889</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.57699688758156</v>
+        <v>2.518429919799769</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.171692083763044</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.994320030664099</v>
+        <v>4.042587336120295</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.920831679333729</v>
+        <v>-2.067249098788206</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.706718816503993</v>
+        <v>2.648151848722202</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.171692083763044</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.178423162809058</v>
+        <v>4.226690468265256</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.943239797138601</v>
+        <v>-2.089657216593078</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.689872264285037</v>
+        <v>2.631305296503247</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.171692083763044</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.170539857712051</v>
+        <v>4.218807163168249</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.091245564618</v>
+        <v>-2.237662984072477</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.632723956842915</v>
+        <v>2.574156989061124</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.084965074899503</v>
+        <v>1.165410583993165</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.120557651943564</v>
+        <v>4.168824957399761</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.10068649050653</v>
+        <v>-2.247103909961007</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.68520130420935</v>
+        <v>2.626634336427559</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.207392192442894</v>
+        <v>1.287837701536556</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.250267640191446</v>
+        <v>4.298534945647643</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.152960097842171</v>
+        <v>-2.299377517296648</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.667182955820394</v>
+        <v>2.608615988038604</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.155118585107253</v>
+        <v>1.235564094200915</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.221794570335362</v>
+        <v>4.270061875791559</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.229290075443077</v>
+        <v>-2.375707494897554</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.634762777673807</v>
+        <v>2.576195809892016</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.155118585107253</v>
+        <v>1.235564094200915</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.219906383229137</v>
+        <v>4.268173688685335</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887749</v>
       </c>
       <c r="C2009" t="n">
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.341047028058378</v>
+        <v>-2.487464447512855</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.584880226230549</v>
+        <v>2.526313258448758</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.043361632491952</v>
+        <v>1.123807141585614</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.147672441262819</v>
+        <v>4.195939746719016</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.339206009000127</v>
+        <v>-2.485623428454604</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.584050644064002</v>
+        <v>2.525483676282211</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.04462985916342</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.146867387475853</v>
+        <v>4.195134692932049</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647107</v>
       </c>
       <c r="C2011" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.47150730109768</v>
+        <v>-2.617924720552157</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.544203534090899</v>
+        <v>2.485636566309108</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.04462985916342</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.159940794341771</v>
+        <v>4.208208099797968</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.473068943912541</v>
+        <v>-2.619486363367018</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.543578876964955</v>
+        <v>2.485011909183164</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.04462985916342</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.159940794341771</v>
+        <v>4.208208099797968</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.500969731022014</v>
+        <v>-2.647387150476491</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.530942603248168</v>
+        <v>2.472375635466377</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.010032935020485</v>
+        <v>1.090478444114147</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.137706680983012</v>
+        <v>4.185973986439209</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.623495833724907</v>
+        <v>-2.769913253179384</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.478696606144209</v>
+        <v>2.420129638362418</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8875068323175914</v>
+        <v>0.9679523414112534</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.060955463338474</v>
+        <v>4.109222768794671</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.643557155001414</v>
+        <v>-2.789974574455891</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.53737803722411</v>
+        <v>2.478811069442319</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8674455110410844</v>
+        <v>0.9478910201347464</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.115624630163074</v>
+        <v>4.163891935619271</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199803</v>
+        <v>3.640764248199806</v>
       </c>
       <c r="C2016" t="n">
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.900277972996238</v>
+        <v>-3.046695392450715</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.575001429028028</v>
+        <v>2.516434461246237</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.7590309368972695</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.190887604678633</v>
+        <v>4.239154910134829</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622233</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.054264390772379</v>
+        <v>-3.200681810226856</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.582387131063211</v>
+        <v>2.52382016328142</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.7590309368972695</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.259867873824271</v>
+        <v>4.308135179280469</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808525</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.003742486944713</v>
+        <v>-3.15015990639919</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.588647094714398</v>
+        <v>2.530080126932607</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.7590309368972695</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.245919075944393</v>
+        <v>4.29418638140059</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994891</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.256217640952437</v>
+        <v>-3.402635060406914</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.499527522166723</v>
+        <v>2.440960554384932</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.7590309368972695</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.257789564999807</v>
+        <v>4.306056870456004</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358295</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.532707121872057</v>
+        <v>-3.672107862328622</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.390142264317818</v>
+        <v>2.334381968135192</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.7590309368972695</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.259000099518751</v>
+        <v>4.307267404974947</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637083</v>
+        <v>3.663523617637087</v>
       </c>
       <c r="C2021" t="n">
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.690251193601498</v>
+        <v>-3.829651934058063</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.331246377853363</v>
+        <v>2.275486081670737</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6921291317569951</v>
+        <v>0.7725746408506571</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.222980758661907</v>
+        <v>4.271248064118105</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.65216331330134</v>
+        <v>3.652163313301344</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.819101744303544</v>
+        <v>-3.95850248476011</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.274784010308734</v>
+        <v>2.219023714126108</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6511357229062735</v>
+        <v>0.7315812319999355</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.193462566087664</v>
+        <v>4.24172987154386</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.66797646721547</v>
       </c>
       <c r="C2023" t="n">
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.936069436942435</v>
+        <v>-4.075470177399001</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.390200989952222</v>
+        <v>2.334440693769595</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6511357229062735</v>
+        <v>0.7315812319999355</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.355666622786708</v>
+        <v>4.403933928242905</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456689</v>
+        <v>3.696553628456693</v>
       </c>
       <c r="C2024" t="n">
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.020787379163389</v>
+        <v>-4.160188119619955</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.351160451027654</v>
+        <v>2.295400154845028</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5660196939782272</v>
+        <v>0.6464652030718891</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.299443643393694</v>
+        <v>4.347710948849891</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253289</v>
       </c>
       <c r="C2025" t="n">
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.102722197432272</v>
+        <v>-4.242122937888838</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.328615941288593</v>
+        <v>2.272855645105967</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.556084948391147</v>
+        <v>0.636530457484809</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.303712213609938</v>
+        <v>4.351979519066135</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717833</v>
       </c>
       <c r="C2026" t="n">
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.04898402403201</v>
+        <v>-4.188384764488576</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.3590368491046</v>
+        <v>2.303276552921973</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6098231217914091</v>
+        <v>0.6902686308850711</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.344880756105997</v>
+        <v>4.393148061562195</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616949</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.938977740554789</v>
+        <v>-4.078378481011354</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.395192249739664</v>
+        <v>2.339431953557038</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.6330276937086843</v>
+        <v>0.7134732028023463</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.350956386500538</v>
+        <v>4.399223691956735</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203663</v>
       </c>
       <c r="C2028" t="n">
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.795918164813863</v>
+        <v>-3.935318905270428</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.456666090758009</v>
+        <v>2.400905794575383</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.6410411202986636</v>
+        <v>0.7214866293923256</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.360014453176499</v>
+        <v>4.408281758632697</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.777251572436929</v>
       </c>
       <c r="C2029" t="n">
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.494471439342026</v>
+        <v>-3.633872179798591</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.58450566382928</v>
+        <v>2.528745367646654</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.9424878457705008</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.548143371342139</v>
+        <v>4.596410676798335</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064767</v>
       </c>
       <c r="C2030" t="n">
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.549426635785095</v>
+        <v>-3.68882737624166</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.563494763004763</v>
+        <v>2.507734466822137</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.9424878457705008</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.549114549094849</v>
+        <v>4.597381854551045</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859297</v>
+        <v>3.821198342859301</v>
       </c>
       <c r="C2031" t="n">
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.498388259778574</v>
+        <v>-3.63778900023514</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.584753017787127</v>
+        <v>2.5289927216045</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.9424878457705008</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.549957453474605</v>
+        <v>4.598224758930801</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354682</v>
+        <v>3.831748677354687</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.457248964911944</v>
+        <v>-3.596649705368509</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.620246834607924</v>
+        <v>2.564486538425298</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.9836271406371316</v>
+        <v>1.064072649730794</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.593679129268728</v>
+        <v>4.641946434724925</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.805143348333665</v>
+        <v>3.468165643115299</v>
       </c>
       <c r="C2033" t="n">
-        <v>4.028475469687634</v>
+        <v>3.715332477198171</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.457248964911944</v>
+        <v>-3.596649705368509</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.620246834607924</v>
+        <v>2.564486538425298</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9836271406371316</v>
+        <v>1.064072649730794</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.021539266674002</v>
+        <v>3.708396274184539</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240722.xlsx
+++ b/tame_output/ON/bt/strategyON_20240722.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.6%</t>
+          <t>-68.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.5%</t>
+          <t>452.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-521.2%</t>
+          <t>-522.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-119.8%</t>
+          <t>-120.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>166.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.3%</t>
+          <t>-121.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-117.6%</t>
+          <t>-143.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.607995237809813</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.8731244564912402</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.6772066700622352</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.710354973891572</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-6.016584014990491</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.7084504896337283</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.085795447242914</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.463963251597924</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.129203775554858</v>
+        <v>-6.130344427013355</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6585880178794419</v>
+        <v>0.6581317572960428</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.085795447242914</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.459148684069384</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.545595649841855</v>
+        <v>-6.546736301300353</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4900253187735202</v>
+        <v>0.4895690581901211</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.085795447242914</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.457142734678261</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-6.791007702027422</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.4021191885679722</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.085795447242914</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.467401425346941</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.995118069805685</v>
+        <v>-6.996258721264183</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3165746066023623</v>
+        <v>0.3161183460189636</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.085795447242914</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.463500990492636</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.043320887048029</v>
+        <v>-7.044461538506527</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2956983997604259</v>
+        <v>0.2952421391770268</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.085795447242914</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.461905910547637</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.339982228858227</v>
+        <v>-7.341122880316724</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1808128389655548</v>
+        <v>0.1803565783821561</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.154538582976792</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.424439005036518</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.526701937167529</v>
+        <v>-7.527842588626027</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1020986511074309</v>
+        <v>0.1016423905240318</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.154538582976792</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.420412700502115</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.909703325910161</v>
+        <v>-7.910843977368658</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.05120400571120598</v>
+        <v>-0.05166026629460463</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.154538582976792</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.420310599180531</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.914189771111549</v>
+        <v>-7.915330422570046</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05042706782033113</v>
+        <v>-0.05088332840373022</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.159025028178181</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.420190248031128</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.273720093615552</v>
+        <v>-8.274860745074049</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1888888935238819</v>
+        <v>-0.189345154107281</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.159025028178181</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.425540551329178</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.324069157069774</v>
+        <v>-8.325209808528271</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2011124989483934</v>
+        <v>-0.2015687595317921</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.209374091632403</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.403247133213822</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.42168843449117</v>
+        <v>-8.422829085949667</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2371184592951829</v>
+        <v>-0.2375747198785816</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.3069933690538</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.347717317382753</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.475759933999528</v>
+        <v>-8.476900585458026</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.255853502776954</v>
+        <v>-0.256309763360353</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.361064868562159</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.31816797399931</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.680018109329392</v>
+        <v>-8.68115876078789</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3320435757902573</v>
+        <v>-0.332499836373656</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.488703813176148</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.247097804349559</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.713670947837866</v>
+        <v>-8.714811599296363</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3410221567092107</v>
+        <v>-0.3414784172926093</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.589117181093185</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.191332338083772</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.640201116170417</v>
+        <v>-8.641341767628914</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.29626252254881</v>
+        <v>-0.2967187831322087</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.515647349425737</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.250785938577662</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.81532553355696</v>
+        <v>-8.816466185015457</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3517570687559104</v>
+        <v>-0.3522133293393095</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.690771766812281</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.160266508893253</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.04977762757145</v>
+        <v>-9.050918279029947</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4527570712633024</v>
+        <v>-0.4532133318467011</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.690771766812281</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.153047343991657</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.155293010056393</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5011791544478572</v>
+        <v>-0.5016354150312559</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.795146497838726</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.083750314601813</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.20807916565672</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5211778268494314</v>
+        <v>-0.5216340874328305</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.890821984421124</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>2.027460812490931</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.334115959025009</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5688988155676324</v>
+        <v>-0.5693550761510315</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.865570361611381</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.045305514805891</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.277044187129079</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5420797711228591</v>
+        <v>-0.5425360317062582</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.865570361611381</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.049295850492292</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.418716028853199</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6002237347112489</v>
+        <v>-0.600679995294648</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.865570361611381</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.047820623593551</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.369125184428365</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5653339867764431</v>
+        <v>-0.5657902473598422</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.815979517186547</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.092628540413323</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.220206849956508</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5188177866343833</v>
+        <v>-0.5192740472177824</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.784729926451374</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.098327161207744</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-8.994361697237096</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.4193569130938091</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.742803250864211</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.133062239596251</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-8.869783040899504</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.3683863060027135</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.742803250864211</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.13420138415231</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-8.922678328943791</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.3869106470583201</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.737847904775764</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.139808365967485</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-8.85054515365591</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.3523236727045314</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.737847904775764</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.145542070206122</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-8.779178761046262</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.3335143780545375</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.666481512166117</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.178624643378045</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.685719727061038</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.3060142457733552</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.666481512166117</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.168741162065138</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.672030763858595</v>
+        <v>-8.41847792619264</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3023732209917522</v>
+        <v>-0.2009520859253699</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.666481512166117</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.166906601565764</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.574123725182105</v>
+        <v>-8.320570887516149</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2635107204946165</v>
+        <v>-0.1620895854282347</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.59849576230556</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.207397736508637</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.550170184206147</v>
+        <v>-8.296617346540192</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.25326079795874</v>
+        <v>-0.1518396628923577</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.574542221329603</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.222438367239705</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.28611024588335</v>
+        <v>-8.032557408217395</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1608971387913734</v>
+        <v>-0.05947600372499107</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.310482283006806</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.367614014071631</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.579030622378512</v>
+        <v>-7.325477784712557</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1191476769502611</v>
+        <v>0.2205688120166434</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.310482283006806</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.36482698041133</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.538846324012321</v>
+        <v>-7.285293486346366</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1355650201845786</v>
+        <v>0.2369861552509609</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.270297984640615</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.389281183318885</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.375446453072959</v>
+        <v>-7.121893615407004</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2002917897810805</v>
+        <v>0.3017129248474628</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.106898113701253</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.48668792710326</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.14196523084336</v>
+        <v>-6.888412393177405</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3016087075107725</v>
+        <v>0.4030298425771544</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.8734168914716545</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.634701089278872</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.992298839835845</v>
+        <v>-6.73874600216989</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3585830536008192</v>
+        <v>0.4600041886672015</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.7805134002291185</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.687550973711434</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.860023366204959</v>
+        <v>-6.606470528539004</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4068607298002007</v>
+        <v>0.508281864866583</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.6482379265982319</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.762283744636993</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.704285033645217</v>
+        <v>-6.450732195979262</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4719711235117341</v>
+        <v>0.5733922585781164</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.4924995940384903</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.858541804860474</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.455285234961636</v>
+        <v>-6.201732397295681</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5844773842088253</v>
+        <v>0.6858985192752076</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.4924995940384903</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.871448146084133</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.56087522473474</v>
+        <v>-6.307322387068785</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4142654587003651</v>
+        <v>0.515686593766747</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.5980895838115947</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.680118222621052</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.579610126853337</v>
+        <v>-6.326057289187382</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4553158397300123</v>
+        <v>0.5567369747963946</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.603685593471726</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.725304958702059</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.431670085445738</v>
+        <v>-6.178117247779783</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3946129336048845</v>
+        <v>0.4960340686712668</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.5833646775631685</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.617618585559026</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.378700563191749</v>
+        <v>-6.125147725525794</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4070867562530021</v>
+        <v>0.5085078913193839</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5303951553091796</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.640686312657941</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.335152156421059</v>
+        <v>-6.081599318755104</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4175455068661851</v>
+        <v>0.5189666419325669</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5303951553091796</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.633725700562848</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.30178894994229</v>
+        <v>-6.048236112276335</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4453531438388354</v>
+        <v>0.5467742789052177</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5303951553091796</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.648188054943991</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.193529812819769</v>
+        <v>-5.939976975153813</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4831889191470391</v>
+        <v>0.5846100542134214</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5303951553091796</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.642720175403186</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.070238678002638</v>
+        <v>-5.816685840336683</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5300034670844682</v>
+        <v>0.6314246021508505</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.4071040204920491</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.714192950304042</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.049089479099194</v>
+        <v>-5.795536641433239</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.546164124883171</v>
+        <v>0.6475852599495533</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.3859548215886057</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.734583447883433</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.80532403711575</v>
+        <v>-5.551771199449795</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6394510100235995</v>
+        <v>0.7408721450899813</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.3859548215886057</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.730364156230483</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.703561216838455</v>
+        <v>-5.4500083791725</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6822804520545334</v>
+        <v>0.7837015871209156</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.372735753196177</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.740419911185957</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.453710822889381</v>
+        <v>-5.200157985223425</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7749626846178654</v>
+        <v>0.8763838196842473</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.372735753196177</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.733161986169659</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.277818730421949</v>
+        <v>-5.024265892755993</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8489186451254871</v>
+        <v>0.9503397801918689</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.372735753196177</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.736761109690308</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.106372267399485</v>
+        <v>-4.85281942973353</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9308247363890261</v>
+        <v>1.032245871455408</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.2012892901737139</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.852956493558339</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.032082701661146</v>
+        <v>-4.778529863995191</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9595610403006587</v>
+        <v>1.060982175367041</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.1269997244353746</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.89655071061764</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.968446959427212</v>
+        <v>-4.714894121761256</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9897101382485496</v>
+        <v>1.091131273314932</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.06336398220144007</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.939426957012318</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.857020200101291</v>
+        <v>-4.603467362435336</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.015475100762713</v>
+        <v>1.116896235829095</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.06336398220144007</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.920621215796114</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.616589703296431</v>
+        <v>-4.62400394128016</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.113390376109535</v>
+        <v>1.110424680916043</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>-0.08390056104626314</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>2.910042345114097</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.544347135125236</v>
+        <v>-4.551761373108965</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.146216717212833</v>
+        <v>1.143251022019341</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>-0.08390056104626314</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>2.913971658948917</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.491348812843849</v>
+        <v>-4.498763050827577</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.168094630042728</v>
+        <v>1.165128934849237</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>-0.02856430204432431</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>2.94785199826742</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.382543927364122</v>
+        <v>-4.38995816534785</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.208614655454612</v>
+        <v>1.205648960261121</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>-0.02856430204432431</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>2.944850069487414</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.162523129327111</v>
+        <v>-4.16993736731084</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.298202011680031</v>
+        <v>1.295236316486539</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.1126555430236559</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.031161013538816</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.029655440263833</v>
+        <v>-4.037069678247562</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.367243270107165</v>
+        <v>1.364277574913674</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.1126555430236559</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.04705519634064</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.909482356899335</v>
+        <v>-3.916896594883063</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.416458347893266</v>
+        <v>1.413492652699775</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.2328286263881549</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.120304890799641</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.764810211799597</v>
+        <v>-3.772224449783326</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.484415308494601</v>
+        <v>1.48144961330111</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.3775007714878923</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.217196280420923</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.82468503915729</v>
+        <v>-3.832099277141018</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.44650286895295</v>
+        <v>1.443537173759459</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.3176259441302002</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.167308875407734</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.704864808246452</v>
+        <v>-3.712279046230181</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.509720130551494</v>
+        <v>1.506754435358002</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.3176259441302002</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.182598044641942</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.707334514708258</v>
+        <v>-3.714748752691987</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.416376447289213</v>
+        <v>1.413410752095722</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.315156237668394</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.0887604200873</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.775704701032268</v>
+        <v>-3.783118939015996</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.30829023424491</v>
+        <v>1.305324539051419</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.324431936704609</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.01358770099433</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.789492753879315</v>
+        <v>-3.796906991863043</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.293211721737983</v>
+        <v>1.290246026544491</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.324431936704609</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.004024409626222</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.845012829771904</v>
+        <v>-3.852427067755633</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.408034528073149</v>
+        <v>1.405068832879658</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.324431936704609</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.295387835452043</v>
+        <v>3.141055246318424</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.669538569979435</v>
+        <v>-3.676952807963163</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.482791463981925</v>
+        <v>1.479825768788434</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.324431936704609</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.299955067443831</v>
+        <v>3.145622478310212</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.780474822620683</v>
+        <v>-3.787889060604412</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.414158991686633</v>
+        <v>1.411193296493141</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.324431936704609</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.275697096205038</v>
+        <v>3.121364507071419</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.746811277148402</v>
+        <v>-3.75422551513213</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.356162723276995</v>
+        <v>1.353197028083504</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.3580954821768908</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.224433536889857</v>
+        <v>3.070100947756238</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.686958657944678</v>
+        <v>-3.694372895928407</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.390276157390617</v>
+        <v>1.387310462197125</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.3580954821768908</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.234605923321989</v>
+        <v>3.08027333418837</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.600715194918301</v>
+        <v>-3.60812943290203</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.419719813175028</v>
+        <v>1.416754117981537</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.3580954821768908</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.22955219389585</v>
+        <v>3.075219604762231</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.646022014317281</v>
+        <v>-3.65343625230101</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.393372860859962</v>
+        <v>1.39040716566647</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.31728531916766</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.196841871534837</v>
+        <v>3.042509282401217</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.675055119019583</v>
+        <v>-3.682469357003311</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.382311492012143</v>
+        <v>1.379345796818651</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.31728531916766</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.197393744567938</v>
+        <v>3.043061155434319</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.582244637568723</v>
+        <v>-3.589658875552452</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.348708376483852</v>
+        <v>1.345742681290361</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6673167825078846</v>
+        <v>0.4100958006185194</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.18235272532982</v>
+        <v>3.0280201361962</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.626634106898151</v>
+        <v>-3.634048344881879</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.332826064676682</v>
+        <v>1.32986036948319</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.622927313178457</v>
+        <v>0.3657063312890917</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.157592519656764</v>
+        <v>3.003259930523145</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.513962888661901</v>
+        <v>-3.521377126645629</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.372970260482905</v>
+        <v>1.370004565289413</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.4783775495253419</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.220270959110237</v>
+        <v>3.065938369976618</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.401585887479228</v>
+        <v>-3.409000125462957</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.423412356786641</v>
+        <v>1.42044666159315</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.4783775495253419</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.225762254940904</v>
+        <v>3.071429665807285</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.429366285380581</v>
+        <v>-3.43678052336431</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.423797399394639</v>
+        <v>1.420831704201147</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.707818133513354</v>
+        <v>0.4505971516239888</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.220591217968631</v>
+        <v>3.066258628835012</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.54774695811072</v>
+        <v>-3.555161196094448</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.214800850303237</v>
+        <v>1.211835155109745</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.3833792994730126</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.018616226678699</v>
+        <v>2.86428363754508</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.656361036554051</v>
+        <v>-3.663775274537779</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.29150487964511</v>
+        <v>1.288539184451619</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.3833792994730126</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.138765887397904</v>
+        <v>2.984433298264285</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.620951998305908</v>
+        <v>-3.628366236289637</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.32018152104669</v>
+        <v>1.317215825853199</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.3833792994730126</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.153278913500227</v>
+        <v>2.998946324366608</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.582568335747757</v>
+        <v>-3.589982573731485</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.332954427412319</v>
+        <v>1.329988732218828</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.678983943920529</v>
+        <v>0.4217629620311638</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.173728552377487</v>
+        <v>3.019395963243868</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.405452005712591</v>
+        <v>-3.412866243696319</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.400529988271688</v>
+        <v>1.397564293078196</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.678983943920529</v>
+        <v>0.4217629620311638</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.170457581222789</v>
+        <v>3.01612499208917</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.450544250546137</v>
+        <v>-3.457958488529865</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.383176482100182</v>
+        <v>1.380210786906691</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6170879007511392</v>
+        <v>0.359866918861774</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.134003347083068</v>
+        <v>2.979670757949449</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.271168829307369</v>
+        <v>-3.278583067291097</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.448713625902104</v>
+        <v>1.445747930708612</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7738646589218579</v>
+        <v>0.5166436770324927</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.221856377291914</v>
+        <v>3.067523788158295</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.316183042827975</v>
+        <v>-3.323597280811704</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.411515395825451</v>
+        <v>1.40854970063196</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7435157636072532</v>
+        <v>0.4862947817178881</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.18445449543474</v>
+        <v>3.030121906301122</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.58318755310041</v>
+        <v>-3.590601791084139</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.310405154055423</v>
+        <v>1.307439458861931</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5491527255643047</v>
+        <v>0.2919317436749395</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.073528234947917</v>
+        <v>2.919195645814298</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.684385334537583</v>
+        <v>-3.691799572521312</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.269129963377055</v>
+        <v>1.266164268183564</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.2235229301296203</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.031686868717227</v>
+        <v>2.877354279583608</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.677874367923271</v>
+        <v>-3.685288605906999</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.269334311577097</v>
+        <v>1.266368616383605</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.2235229301296203</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.029286830271544</v>
+        <v>2.874954241137925</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.658836240215973</v>
+        <v>-3.666250478199702</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.273474281868261</v>
+        <v>1.270508586674769</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.422560300687791</v>
+        <v>0.1653393187984258</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.990901382681072</v>
+        <v>2.836568793547453</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.689962871366591</v>
+        <v>-3.69737710935032</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.438605498346694</v>
+        <v>1.435639803153202</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.422560300687791</v>
+        <v>0.1653393187984258</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.168483251619753</v>
+        <v>3.014150662486133</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.703829632700509</v>
+        <v>-3.711243870684237</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.43389212279926</v>
+        <v>1.430926427605769</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.1274814020646028</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.146601830565592</v>
+        <v>2.992269241431973</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.659025461160579</v>
+        <v>-3.666439699144307</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.457822321812158</v>
+        <v>1.454856626618667</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.1274814020646028</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.152610360962518</v>
+        <v>2.998277771828899</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.511282490925577</v>
+        <v>-3.518696728909305</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.414869731183359</v>
+        <v>1.411904035989867</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.295288759299486</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.151244996580647</v>
+        <v>2.996912407447029</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.613297173456798</v>
+        <v>-3.620711411440526</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.376857479702351</v>
+        <v>1.37389178450886</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.295288759299486</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.154038618112128</v>
+        <v>2.99970602897851</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.607144467404013</v>
+        <v>-3.614558705387742</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.379980910515124</v>
+        <v>1.377015215321632</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5586624472416355</v>
+        <v>0.3014414653522703</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.158392590135457</v>
+        <v>3.004060001001839</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.623953765554515</v>
+        <v>-3.631368003538243</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.372337667995033</v>
+        <v>1.369371972801542</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.2846321672017686</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.147387487985267</v>
+        <v>2.993054898851648</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.561655766778393</v>
+        <v>-3.569070004762121</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.463592421302303</v>
+        <v>1.460626726108811</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.2846321672017686</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.213723041782088</v>
+        <v>3.059390452648469</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.359865569113235</v>
+        <v>-3.367279807096963</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.346600502082493</v>
+        <v>1.343634806889002</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7398713412602882</v>
+        <v>0.482650359370923</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.134825958797707</v>
+        <v>2.980493369664088</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.195052566034388</v>
+        <v>-3.202466804018116</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.482815935636207</v>
+        <v>1.479850240442716</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9046843443391351</v>
+        <v>0.64746336244977</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.304003992967191</v>
+        <v>3.149671403833572</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.292793110659362</v>
+        <v>-3.300207348643091</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.458347453902261</v>
+        <v>1.45538175870877</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.888795066206155</v>
+        <v>0.6315740843167899</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.309098162203446</v>
+        <v>3.154765573069827</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.469130870782291</v>
+        <v>-3.47654510876602</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.386348330677761</v>
+        <v>1.38338263548427</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.4552363241938605</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.20183148695436</v>
+        <v>3.047498897820741</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.392708824350365</v>
+        <v>-3.400123062334093</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.41540876729046</v>
+        <v>1.412443072096969</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.4552363241938605</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.200323104994289</v>
+        <v>3.04599051586067</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.348335692711796</v>
+        <v>-3.355749930695525</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.433020887381324</v>
+        <v>1.430055192187832</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.4996094558324291</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.226809851412866</v>
+        <v>3.072477262279247</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.225501471824629</v>
+        <v>-3.232915709808357</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.476548369874781</v>
+        <v>1.47358267468129</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.4996094558324291</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.221203645551457</v>
+        <v>3.066871056417838</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.177845741263573</v>
+        <v>-3.185259979247301</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.501992419127008</v>
+        <v>1.499026723933517</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8044861682828498</v>
+        <v>0.5472651863934848</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.256178840915895</v>
+        <v>3.101846251782276</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.077327582764818</v>
+        <v>-3.084741820748547</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.547092055901235</v>
+        <v>1.544126360707744</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9050043267816044</v>
+        <v>0.6477833448922393</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.321382109389872</v>
+        <v>3.167049520256253</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.137994173167207</v>
+        <v>-3.145408411150936</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.509580092216152</v>
+        <v>1.50661439702266</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8233060100630707</v>
+        <v>0.5660850281737057</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.259117791834624</v>
+        <v>3.104785202701005</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.093155771558809</v>
+        <v>-3.100570009542538</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.531613155470139</v>
+        <v>1.528647460276648</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8278494430079402</v>
+        <v>0.5706284611185751</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.265941554212175</v>
+        <v>3.111608965078556</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.112654227800817</v>
+        <v>-3.120068465784546</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.527974712604414</v>
+        <v>1.525009017410923</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7797648017280359</v>
+        <v>0.5225438198386708</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.24125170907531</v>
+        <v>3.086919119941691</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.068451390714917</v>
+        <v>-3.075865628698645</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.551535449966611</v>
+        <v>1.54856975477312</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8239676388139363</v>
+        <v>0.5667466569245713</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.273653013854688</v>
+        <v>3.119320424721069</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.10543041837836</v>
+        <v>-3.112844656362089</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.535153839370482</v>
+        <v>1.53218814417699</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.6037205587159018</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.294247355398733</v>
+        <v>3.139914766265115</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.947139000839088</v>
+        <v>-2.954553238822816</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.64971817156923</v>
+        <v>1.646752476375739</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.6037205587159018</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.345495120581773</v>
+        <v>3.191162531448154</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.739496997204612</v>
+        <v>-2.74691123518834</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.731215677617274</v>
+        <v>1.728249982423782</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.068583544239743</v>
+        <v>0.811362562350378</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.468521027356712</v>
+        <v>3.314188438223093</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.688464904482084</v>
+        <v>-2.695879142465812</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.746576742944555</v>
+        <v>1.743611047751064</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.119615636962271</v>
+        <v>0.8623946550729059</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.494088511228499</v>
+        <v>3.33975592209488</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.623240723354878</v>
+        <v>-2.630654961338607</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.789853819488142</v>
+        <v>1.786888124294651</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.184839818089477</v>
+        <v>0.9276188362001115</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.550410423997527</v>
+        <v>3.396077834863908</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.585813703283744</v>
+        <v>-2.593227941267473</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.800785599815876</v>
+        <v>1.797819904622385</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.190091356118658</v>
+        <v>0.9328703742292932</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.549522319114316</v>
+        <v>3.395189729980697</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.605925359318453</v>
+        <v>-2.613339597302181</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.793997729733233</v>
+        <v>1.791032034539742</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.201118701116078</v>
+        <v>0.9438977192267124</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.557395518444008</v>
+        <v>3.403062929310389</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.552180544891248</v>
+        <v>-2.559594782874977</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.976053426525326</v>
+        <v>1.973087731331834</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.21118201055654</v>
+        <v>0.9539610286671744</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.723991275129496</v>
+        <v>3.569658685995877</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.477398283866235</v>
+        <v>-2.484812521849964</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.126079240153148</v>
+        <v>2.123113544959657</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.285964271581552</v>
+        <v>1.028743289692187</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.888973540962321</v>
+        <v>3.734640951828702</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.451314199602427</v>
+        <v>-2.458728437586156</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.12822084987253</v>
+        <v>2.125255154679039</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.285964271581552</v>
+        <v>1.028743289692187</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.88068151697618</v>
+        <v>3.726348927842561</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.373183018753481</v>
+        <v>-2.380597256737209</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.157666517795888</v>
+        <v>2.154700822602397</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.360141082465237</v>
+        <v>1.102920100575872</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.92338079909017</v>
+        <v>3.769048209956551</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.364290557360198</v>
+        <v>-2.371704795343926</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.178777908079993</v>
+        <v>2.175812212886501</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.360141082465237</v>
+        <v>1.102920100575872</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.940935204816961</v>
+        <v>3.786602615683342</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.532766674330075</v>
+        <v>-2.540180912313804</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.103242508696626</v>
+        <v>2.100276813503134</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.332193246748656</v>
+        <v>1.074972264859291</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.916021550791597</v>
+        <v>3.761688961657978</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.834967145468492</v>
+        <v>-1.842381383452221</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.363632017429121</v>
+        <v>2.360666322235629</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.261845187378245</v>
+        <v>1.00462420548888</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.855082412357213</v>
+        <v>3.700749823223593</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.81224604178534</v>
+        <v>-1.819660279769068</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.363384481399287</v>
+        <v>2.360418786205795</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.261845187378245</v>
+        <v>1.00462420548888</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.845746434854117</v>
+        <v>3.691413845720498</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.810520998495296</v>
+        <v>-1.817935236479024</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.522980624566473</v>
+        <v>2.520014929372981</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.263570230668289</v>
+        <v>1.006349248778924</v>
       </c>
       <c r="G1999" t="n">
-        <v>4.005687586679312</v>
+        <v>3.851354997545693</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.965302005273551</v>
+        <v>-1.97271624325728</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.498146044348817</v>
+        <v>2.495180349155326</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.230202556613813</v>
+        <v>0.9729815747244479</v>
       </c>
       <c r="G2000" t="n">
-        <v>4.022744804740273</v>
+        <v>3.868412215606654</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.958247315058377</v>
+        <v>-1.965661553042106</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.497643276424432</v>
+        <v>2.494677581230941</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.237257246828987</v>
+        <v>0.9800362649396217</v>
       </c>
       <c r="G2001" t="n">
-        <v>4.023652974858923</v>
+        <v>3.869320385725303</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.931296090731889</v>
+        <v>-1.938710328715618</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.518429919799769</v>
+        <v>2.515464224606277</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.252137592856706</v>
+        <v>0.9949166109673409</v>
       </c>
       <c r="G2002" t="n">
-        <v>4.042587336120295</v>
+        <v>3.888254746986677</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.067249098788206</v>
+        <v>-2.074663336771934</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.648151848722202</v>
+        <v>2.645186153528711</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.252137592856706</v>
+        <v>0.9949166109673409</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.226690468265256</v>
+        <v>4.072357879131636</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.089657216593078</v>
+        <v>-2.097071454576806</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.631305296503247</v>
+        <v>2.628339601309755</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.252137592856706</v>
+        <v>0.9949166109673409</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.218807163168249</v>
+        <v>4.064474574034629</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.237662984072477</v>
+        <v>-2.245077222056206</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.574156989061124</v>
+        <v>2.571191293867633</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.165410583993165</v>
+        <v>0.9081896021037994</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.168824957399761</v>
+        <v>4.014492368266142</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.247103909961007</v>
+        <v>-2.254518147944736</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.626634336427559</v>
+        <v>2.623668641234068</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.287837701536556</v>
+        <v>1.030616719647191</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.298534945647643</v>
+        <v>4.144202356514024</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.299377517296648</v>
+        <v>-2.306791755280377</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.608615988038604</v>
+        <v>2.605650292845112</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.235564094200915</v>
+        <v>0.9783431123115497</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.270061875791559</v>
+        <v>4.11572928665794</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.375707494897554</v>
+        <v>-2.383121732881283</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.576195809892016</v>
+        <v>2.573230114698525</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.235564094200915</v>
+        <v>0.9783431123115497</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.268173688685335</v>
+        <v>4.113841099551715</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.487464447512855</v>
+        <v>-2.494878685496584</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.526313258448758</v>
+        <v>2.523347563255267</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.123807141585614</v>
+        <v>0.8665861596962485</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.195939746719016</v>
+        <v>4.041607157585397</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.485623428454604</v>
+        <v>-2.493037666438333</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.525483676282211</v>
+        <v>2.52251798108872</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.125075368257082</v>
+        <v>0.8678543863677169</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.195134692932049</v>
+        <v>4.040802103798431</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.617924720552157</v>
+        <v>-2.625338958535886</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.485636566309108</v>
+        <v>2.482670871115617</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.125075368257082</v>
+        <v>0.8678543863677169</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.208208099797968</v>
+        <v>4.053875510664349</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.619486363367018</v>
+        <v>-2.626900601350746</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.485011909183164</v>
+        <v>2.482046213989673</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.125075368257082</v>
+        <v>0.8678543863677169</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.208208099797968</v>
+        <v>4.053875510664349</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.647387150476491</v>
+        <v>-2.654801388460219</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.472375635466377</v>
+        <v>2.469409940272886</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.090478444114147</v>
+        <v>0.8332574622247821</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.185973986439209</v>
+        <v>4.03164139730559</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.769913253179384</v>
+        <v>-2.777327491163113</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.420129638362418</v>
+        <v>2.417163943168927</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9679523414112534</v>
+        <v>0.7107313595218883</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.109222768794671</v>
+        <v>3.954890179661053</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.789974574455891</v>
+        <v>-2.79738881243962</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.478811069442319</v>
+        <v>2.475845374248828</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9478910201347464</v>
+        <v>0.6906700382453812</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.163891935619271</v>
+        <v>4.009559346485652</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.046695392450715</v>
+        <v>-3.054109630434444</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.516434461246237</v>
+        <v>2.513468766052745</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.5822554641015664</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.239154910134829</v>
+        <v>4.08482232100121</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.200681810226856</v>
+        <v>-3.208096048210584</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.52382016328142</v>
+        <v>2.520854468087929</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.5822554641015664</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.308135179280469</v>
+        <v>4.15380259014685</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.15015990639919</v>
+        <v>-3.157574144382918</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.530080126932607</v>
+        <v>2.527114431739116</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.5822554641015664</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.29418638140059</v>
+        <v>4.139853792266971</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.402635060406914</v>
+        <v>-3.410049298390643</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.440960554384932</v>
+        <v>2.43799485919144</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.5822554641015664</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.306056870456004</v>
+        <v>4.151724281322385</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.672107862328622</v>
+        <v>-3.679522100312351</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.334381968135192</v>
+        <v>2.331416272941701</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.5822554641015664</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.307267404974947</v>
+        <v>4.152934815841329</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.829651934058063</v>
+        <v>-3.837066172041792</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.275486081670737</v>
+        <v>2.272520386477246</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7725746408506571</v>
+        <v>0.5153536589612919</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.271248064118105</v>
+        <v>4.116915474984485</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.95850248476011</v>
+        <v>-3.965916722743839</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.219023714126108</v>
+        <v>2.216058018932617</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.4743602501105704</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.24172987154386</v>
+        <v>4.087397282410242</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.075470177399001</v>
+        <v>-4.08288441538273</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.334440693769595</v>
+        <v>2.331474998576105</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.4743602501105704</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.403933928242905</v>
+        <v>4.249601339109286</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.160188119619955</v>
+        <v>-4.167602357603683</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.295400154845028</v>
+        <v>2.292434459651537</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6464652030718891</v>
+        <v>0.389244221182524</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.347710948849891</v>
+        <v>4.193378359716272</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.242122937888838</v>
+        <v>-4.249537175872566</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.272855645105967</v>
+        <v>2.269889949912475</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.636530457484809</v>
+        <v>0.3793094755954438</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.351979519066135</v>
+        <v>4.197646929932516</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.188384764488576</v>
+        <v>-4.195799002472304</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.303276552921973</v>
+        <v>2.300310857728483</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6902686308850711</v>
+        <v>0.4330476489957059</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.393148061562195</v>
+        <v>4.238815472428575</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.078378481011354</v>
+        <v>-4.085792718995083</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.339431953557038</v>
+        <v>2.336466258363547</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7134732028023463</v>
+        <v>0.4562522209129811</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.399223691956735</v>
+        <v>4.244891102823116</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.935318905270428</v>
+        <v>-3.942733143254157</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.400905794575383</v>
+        <v>2.397940099381891</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7214866293923256</v>
+        <v>0.4642656475029604</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.408281758632697</v>
+        <v>4.253949169499077</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.633872179798591</v>
+        <v>-3.64128641778232</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.528745367646654</v>
+        <v>2.525779672453162</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.022933354864163</v>
+        <v>0.7657123729747977</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.596410676798335</v>
+        <v>4.442078087664717</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.68882737624166</v>
+        <v>-3.696241614225389</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.507734466822137</v>
+        <v>2.504768771628645</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.022933354864163</v>
+        <v>0.7657123729747977</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.597381854551045</v>
+        <v>4.443049265417427</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.63778900023514</v>
+        <v>-3.645203238218869</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.5289927216045</v>
+        <v>2.526027026411009</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.022933354864163</v>
+        <v>0.7657123729747977</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.598224758930801</v>
+        <v>4.443892169797182</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354687</v>
+        <v>3.831748677354686</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.596649705368509</v>
+        <v>-3.604063943352238</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.564486538425298</v>
+        <v>2.561520843231807</v>
       </c>
       <c r="F2032" t="n">
-        <v>1.064072649730794</v>
+        <v>0.8068516678414285</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.641946434724925</v>
+        <v>4.487613845591306</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.468165643115299</v>
+        <v>3.465382938752114</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.715332477198171</v>
+        <v>3.717571630186394</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.596649705368509</v>
+        <v>-3.604063943352238</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.564486538425298</v>
+        <v>2.561520843231807</v>
       </c>
       <c r="F2033" t="n">
-        <v>1.064072649730794</v>
+        <v>0.8068516678414285</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.708396274184539</v>
+        <v>3.710635427172762</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240722.xlsx
+++ b/tame_output/ON/bt/strategyON_20240722.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>55.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>103.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>86.2%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>34.1%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>62.9%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>31.6%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>131.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>102.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-46.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-67.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.1%</t>
+          <t>456.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-522.0%</t>
+          <t>-500.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-120.1%</t>
+          <t>-68.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>166.1%</t>
+          <t>188.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-121.2%</t>
+          <t>-108.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-143.3%</t>
+          <t>-85.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>119.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,57 +1456,57 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>80.5%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.607995237809813</v>
+        <v>-5.606854586351314</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8731244564912402</v>
+        <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6772066700622352</v>
+        <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.710354973891572</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44420,19 +44420,19 @@
         <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.549225793250327</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.016584014990491</v>
+        <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7084504896337283</v>
+        <v>1.142692023523782</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.085795447242914</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.463963251597924</v>
+        <v>2.895500868648388</v>
       </c>
     </row>
     <row r="1865">
@@ -44443,19 +44443,19 @@
         <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.544411225721787</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.130344427013355</v>
+        <v>-6.129203775554858</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6581317572960428</v>
+        <v>1.092373291186097</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.085795447242914</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.459148684069384</v>
+        <v>2.890686301119848</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.542405276330665</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.546736301300353</v>
+        <v>-6.545595649841855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4895690581901211</v>
+        <v>0.9238105920801751</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.085795447242914</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.457142734678261</v>
+        <v>2.888680351728726</v>
       </c>
     </row>
     <row r="1867">
@@ -44489,19 +44489,19 @@
         <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.552663966999344</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.791007702027422</v>
+        <v>-6.789867050568925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4021191885679722</v>
+        <v>0.8363607224580263</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.085795447242914</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.467401425346941</v>
+        <v>2.898939042397405</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.548763532145039</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.996258721264183</v>
+        <v>-6.995118069805685</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3161183460189636</v>
+        <v>0.7503598799090172</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.085795447242914</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.463500990492636</v>
+        <v>2.8950386075431</v>
       </c>
     </row>
     <row r="1869">
@@ -44535,19 +44535,19 @@
         <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.54716845220004</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.044461538506527</v>
+        <v>-7.043320887048029</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2952421391770268</v>
+        <v>0.7294836730670808</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.085795447242914</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.461905910547637</v>
+        <v>2.893443527598101</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.550947428129248</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.341122880316724</v>
+        <v>-7.339982228858227</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1803565783821561</v>
+        <v>0.6145981122722097</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.154538582976792</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.424439005036518</v>
+        <v>2.855976622086982</v>
       </c>
     </row>
     <row r="1871">
@@ -44581,19 +44581,19 @@
         <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.546921123594845</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.527842588626027</v>
+        <v>-7.526701937167529</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1016423905240318</v>
+        <v>0.5358839244140858</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.154538582976792</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.420412700502115</v>
+        <v>2.851950317552579</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.546819022273261</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.910843977368658</v>
+        <v>-7.909703325910161</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.05166026629460463</v>
+        <v>0.382581267595449</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.154538582976792</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.420310599180531</v>
+        <v>2.851848216230995</v>
       </c>
     </row>
     <row r="1873">
@@ -44627,19 +44627,19 @@
         <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.549390538244691</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.915330422570046</v>
+        <v>-7.914189771111549</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05088332840373022</v>
+        <v>0.3833582054863238</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.159025028178181</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.420190248031128</v>
+        <v>2.851727865081592</v>
       </c>
     </row>
     <row r="1874">
@@ -44650,19 +44650,19 @@
         <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.554740841542741</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.274860745074049</v>
+        <v>-8.273720093615552</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.189345154107281</v>
+        <v>0.244896379782773</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.159025028178181</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.425540551329178</v>
+        <v>2.857078168379642</v>
       </c>
     </row>
     <row r="1875">
@@ -44673,19 +44673,19 @@
         <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.562656861499919</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.325209808528271</v>
+        <v>-8.324069157069774</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2015687595317921</v>
+        <v>0.2326727743582615</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.209374091632403</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.403247133213822</v>
+        <v>2.834784750264286</v>
       </c>
     </row>
     <row r="1876">
@@ -44696,19 +44696,19 @@
         <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.565698612121687</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.422829085949667</v>
+        <v>-8.42168843449117</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2375747198785816</v>
+        <v>0.196666814011472</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.3069933690538</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.347717317382753</v>
+        <v>2.779254934433217</v>
       </c>
     </row>
     <row r="1877">
@@ -44719,19 +44719,19 @@
         <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.134806895136605</v>
+        <v>3.56859216844326</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.476900585458026</v>
+        <v>-8.475759933999528</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.256309763360353</v>
+        <v>0.177931770529701</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.361064868562159</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.31816797399931</v>
+        <v>2.749705591049774</v>
       </c>
     </row>
     <row r="1878">
@@ -44742,19 +44742,19 @@
         <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.140320092255247</v>
+        <v>3.574105365561902</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.68115876078789</v>
+        <v>-8.680018109329392</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.332499836373656</v>
+        <v>0.1017416975163976</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.488703813176148</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.247097804349559</v>
+        <v>2.678635421400023</v>
       </c>
     </row>
     <row r="1879">
@@ -44765,19 +44765,19 @@
         <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.144802646739683</v>
+        <v>3.578587920046338</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.714811599296363</v>
+        <v>-8.713670947837866</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3414784172926093</v>
+        <v>0.0927631165974443</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.589117181093185</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.191332338083772</v>
+        <v>2.622869955134236</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.160174348233104</v>
+        <v>3.593959621539759</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.641341767628914</v>
+        <v>-8.640201116170417</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2967187831322087</v>
+        <v>0.1375227507578449</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.515647349425737</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.250785938577662</v>
+        <v>2.682323555628126</v>
       </c>
     </row>
     <row r="1881">
@@ -44811,19 +44811,19 @@
         <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.174729568980621</v>
+        <v>3.608514842287276</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.816466185015457</v>
+        <v>-8.81532553355696</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3522133293393095</v>
+        <v>0.08202820455074455</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.690771766812281</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.160266508893253</v>
+        <v>2.591804125943717</v>
       </c>
     </row>
     <row r="1882">
@@ -44834,19 +44834,19 @@
         <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.167510404079025</v>
+        <v>3.60129567738568</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.050918279029947</v>
+        <v>-9.04977762757145</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4532133318467011</v>
+        <v>-0.0189717979566475</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.690771766812281</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.153047343991657</v>
+        <v>2.584584961042121</v>
       </c>
     </row>
     <row r="1883">
@@ -44857,19 +44857,19 @@
         <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.160838213305049</v>
+        <v>3.594623486611704</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.155293010056393</v>
+        <v>-9.154152358597896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5016354150312559</v>
+        <v>-0.06739388114120226</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.795146497838726</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.083750314601813</v>
+        <v>2.515287931652277</v>
       </c>
     </row>
     <row r="1884">
@@ -44880,19 +44880,19 @@
         <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.161954003143605</v>
+        <v>3.59573927645026</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.20807916565672</v>
+        <v>-9.206938514198223</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5216340874328305</v>
+        <v>-0.08739255354277642</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.890821984421124</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.027460812490931</v>
+        <v>2.458998429541396</v>
       </c>
     </row>
     <row r="1885">
@@ -44903,19 +44903,19 @@
         <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.16464773177272</v>
+        <v>3.598433005079375</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.334115959025009</v>
+        <v>-9.332975307566512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5693550761510315</v>
+        <v>-0.1351135422609775</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.865570361611381</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.045305514805891</v>
+        <v>2.476843131856355</v>
       </c>
     </row>
     <row r="1886">
@@ -44926,19 +44926,19 @@
         <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.168638067459121</v>
+        <v>3.602423340765776</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.277044187129079</v>
+        <v>-9.275903535670581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5425360317062582</v>
+        <v>-0.1082944978162041</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.865570361611381</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.049295850492292</v>
+        <v>2.480833467542756</v>
       </c>
     </row>
     <row r="1887">
@@ -44949,19 +44949,19 @@
         <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.167162840560379</v>
+        <v>3.600948113867034</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.418716028853199</v>
+        <v>-9.417575377394702</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.600679995294648</v>
+        <v>-0.166438461404594</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.865570361611381</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.047820623593551</v>
+        <v>2.479358240644014</v>
       </c>
     </row>
     <row r="1888">
@@ -44972,19 +44972,19 @@
         <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.182216250725251</v>
+        <v>3.616001524031906</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.369125184428365</v>
+        <v>-9.367984532969867</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5657902473598422</v>
+        <v>-0.1315487134697881</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.815979517186547</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.092628540413323</v>
+        <v>2.524166157463787</v>
       </c>
     </row>
     <row r="1889">
@@ -44995,19 +44995,19 @@
         <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.169165117078568</v>
+        <v>3.602950390385223</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.220206849956508</v>
+        <v>-9.219066198498011</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5192740472177824</v>
+        <v>-0.08503251332772832</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.784729926451374</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.098327161207744</v>
+        <v>2.529864778258208</v>
       </c>
     </row>
     <row r="1890">
@@ -45018,19 +45018,19 @@
         <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.178744190114777</v>
+        <v>3.612529463421432</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.994361697237096</v>
+        <v>-8.993221045778601</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4193569130938091</v>
+        <v>0.01488462079624409</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.742803250864211</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.133062239596251</v>
+        <v>2.564599856646715</v>
       </c>
     </row>
     <row r="1891">
@@ -45041,19 +45041,19 @@
         <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.179883334670836</v>
+        <v>3.613668607977491</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.869783040899504</v>
+        <v>-8.868642389441009</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3683863060027135</v>
+        <v>0.06585522788733966</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.742803250864211</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.13420138415231</v>
+        <v>2.565739001202774</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.182517108832943</v>
+        <v>3.616302382139598</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.922678328943791</v>
+        <v>-8.921537677485295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3869106470583201</v>
+        <v>0.04733088683173303</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.737847904775764</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.139808365967485</v>
+        <v>2.571345983017949</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.18825081307158</v>
+        <v>3.622036086378235</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.85054515365591</v>
+        <v>-8.849404502197414</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3523236727045314</v>
+        <v>0.0819178611855218</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.737847904775764</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.145542070206122</v>
+        <v>2.577079687256585</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.178513550677715</v>
+        <v>3.61229882398437</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.779178761046262</v>
+        <v>-8.778038109587767</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3335143780545375</v>
+        <v>0.1007271558355156</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.666481512166117</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.178624643378045</v>
+        <v>2.610162260428509</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.168630069364807</v>
+        <v>3.602415342671462</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.685719727061038</v>
+        <v>-8.684579075602542</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3060142457733552</v>
+        <v>0.1282272881166979</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.666481512166117</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.168741162065138</v>
+        <v>2.600278779115602</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.166795508865433</v>
+        <v>3.600580782172088</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.41847792619264</v>
+        <v>-8.417337274734145</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2009520859253699</v>
+        <v>0.2332894479646832</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.666481512166117</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.166906601565764</v>
+        <v>2.598444218616228</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.166495193891973</v>
+        <v>3.600280467198627</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.320570887516149</v>
+        <v>-8.319430236057654</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1620895854282347</v>
+        <v>0.2721519484618184</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.59849576230556</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.207397736508637</v>
+        <v>2.638935353559101</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.167163700037466</v>
+        <v>3.600948973344121</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.296617346540192</v>
+        <v>-8.295476695081696</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1518396628923577</v>
+        <v>0.2824018709976954</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.574542221329603</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.222438367239705</v>
+        <v>2.653975984290169</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.153903383875714</v>
+        <v>3.587688657182369</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.032557408217395</v>
+        <v>-8.031416756758899</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05947600372499107</v>
+        <v>0.3747655301650621</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.310482283006806</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.367614014071631</v>
+        <v>2.799151631122094</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.151116350215413</v>
+        <v>3.584901623522068</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.325477784712557</v>
+        <v>-7.324337133254061</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2205688120166434</v>
+        <v>0.6548103459066965</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.310482283006806</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.36482698041133</v>
+        <v>2.796364597461793</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.151459974103255</v>
+        <v>3.585245247409909</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.285293486346366</v>
+        <v>-7.284152834887871</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2369861552509609</v>
+        <v>0.6712276891410141</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.270297984640615</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.389281183318885</v>
+        <v>2.82081880036935</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626474</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.150826795324011</v>
+        <v>3.584612068630666</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.121893615407004</v>
+        <v>-7.120752963948508</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3017129248474628</v>
+        <v>0.735954458737516</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.106898113701253</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.48668792710326</v>
+        <v>2.918225544153724</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.158751224161864</v>
+        <v>3.592536497468519</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.888412393177405</v>
+        <v>-6.88727174171891</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4030298425771544</v>
+        <v>0.8372713764672075</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8734168914716545</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.634701089278872</v>
+        <v>3.066238706329336</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.58964428715556</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.73874600216989</v>
+        <v>-6.737605350711394</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4600041886672015</v>
+        <v>0.8942457225572547</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7805134002291185</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.687550973711434</v>
+        <v>3.119088590761898</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.585011773902587</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.606470528539004</v>
+        <v>-6.605329877080508</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.508281864866583</v>
+        <v>0.9425233987566362</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6482379265982319</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.762283744636993</v>
+        <v>3.193821361687457</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.587826834590223</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.450732195979262</v>
+        <v>-6.449591544520766</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5733922585781164</v>
+        <v>1.00763379246817</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4924995940384903</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.858541804860474</v>
+        <v>3.290079421910939</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.600733175813882</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.201732397295681</v>
+        <v>-6.200591745837185</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6858985192752076</v>
+        <v>1.120140053165261</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4924995940384903</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.871448146084133</v>
+        <v>3.302985763134597</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>3.472757246214663</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.307322387068785</v>
+        <v>-6.30618173561029</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.515686593766747</v>
+        <v>0.9499281276568001</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.5980895838115947</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.680118222621052</v>
+        <v>3.111655839671516</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.52130158809175</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.326057289187382</v>
+        <v>-6.324916637728887</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5567369747963946</v>
+        <v>0.9909785086864478</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.603685593471726</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.725304958702059</v>
+        <v>3.156842575752524</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>3.401422665403582</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.178117247779783</v>
+        <v>-6.176976596321287</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4960340686712668</v>
+        <v>0.9302756025613199</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5833646775631685</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.617618585559026</v>
+        <v>3.04915620260949</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>3.392708679150104</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.125147725525794</v>
+        <v>-6.124007074067299</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5085078913193839</v>
+        <v>0.9427494252094371</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5303951553091796</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.640686312657941</v>
+        <v>3.072223929708406</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>3.385748067055011</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.081599318755104</v>
+        <v>-6.080458667296608</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5189666419325669</v>
+        <v>0.9532081758226201</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5303951553091796</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.633725700562848</v>
+        <v>3.065263317613312</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>3.400210421436154</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.048236112276335</v>
+        <v>-6.04709546081784</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5467742789052177</v>
+        <v>0.9810158127952708</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5303951553091796</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.648188054943991</v>
+        <v>3.079725671994455</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>3.394742541895349</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.939976975153813</v>
+        <v>-5.938836323695318</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5846100542134214</v>
+        <v>1.018851588103475</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5303951553091796</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.642720175403186</v>
+        <v>3.07425779245365</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>3.392240635905926</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.816685840336683</v>
+        <v>-5.815545188878187</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6314246021508505</v>
+        <v>1.065666136040904</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4071040204920491</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.714192950304042</v>
+        <v>3.145730567354506</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>3.399941614143251</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.795536641433239</v>
+        <v>-5.794395989974744</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6475852599495533</v>
+        <v>1.081826793839606</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3859548215886057</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.734583447883433</v>
+        <v>3.166121064933897</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>3.395722322490302</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.551771199449795</v>
+        <v>-5.550630547991299</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7408721450899813</v>
+        <v>1.175113678980034</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3859548215886057</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.730364156230483</v>
+        <v>3.161901773280948</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>3.397846636410318</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.4500083791725</v>
+        <v>-5.448867727714005</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7837015871209156</v>
+        <v>1.217943121010969</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.372735753196177</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.740419911185957</v>
+        <v>3.171957528236421</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>3.39058871139402</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.200157985223425</v>
+        <v>-5.19901733376493</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8763838196842473</v>
+        <v>1.3106253535743</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.372735753196177</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.733161986169659</v>
+        <v>3.164699603220123</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>3.394187834914669</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.024265892755993</v>
+        <v>-5.023125241297498</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9503397801918689</v>
+        <v>1.384581314081922</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.372735753196177</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.736761109690308</v>
+        <v>3.168298726740772</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>3.407515340969222</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.85281942973353</v>
+        <v>-4.851678778275034</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.032245871455408</v>
+        <v>1.466487405345461</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2012892901737139</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.852956493558339</v>
+        <v>3.284494110608803</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>3.406535818585519</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.778529863995191</v>
+        <v>-4.777389212536695</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.060982175367041</v>
+        <v>1.495223709257094</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1269997244353746</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.89655071061764</v>
+        <v>3.328088327668104</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>3.411230619639837</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.714894121761256</v>
+        <v>-4.713753470302761</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.091131273314932</v>
+        <v>1.525372807204985</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06336398220144007</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.939426957012318</v>
+        <v>3.370964574062782</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>3.392424878423632</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.603467362435336</v>
+        <v>-4.602326710976841</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.116896235829095</v>
+        <v>1.551137769719149</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06336398220144007</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.920621215796114</v>
+        <v>3.352158832846578</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>3.39416795504851</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.62400394128016</v>
+        <v>-4.615122754954449</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.110424680916043</v>
+        <v>1.547762428752983</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.08390056104626314</v>
+        <v>-0.07990611993936614</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.910042345114097</v>
+        <v>3.34622428308489</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>3.39809726888333</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.551761373108965</v>
+        <v>-4.542880186783254</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.143251022019341</v>
+        <v>1.580588769856281</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.08390056104626314</v>
+        <v>-0.07990611993936614</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.913971658948917</v>
+        <v>3.35015359691971</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>3.39877585280067</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.498763050827577</v>
+        <v>-4.489881864501866</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.165128934849237</v>
+        <v>1.602466682686176</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.02856430204432431</v>
+        <v>-0.0245698609374273</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.94785199826742</v>
+        <v>3.384033936238214</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>3.395773924020663</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.38995816534785</v>
+        <v>-4.381076979022139</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.205648960261121</v>
+        <v>1.64298670809806</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.02856430204432431</v>
+        <v>-0.0245698609374273</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.944850069487414</v>
+        <v>3.381032007458207</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>3.397352961031277</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.16993736731084</v>
+        <v>-4.161056180985129</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.295236316486539</v>
+        <v>1.732574064323479</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.1126555430236559</v>
+        <v>0.1166499841305529</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.031161013538816</v>
+        <v>3.467342951509609</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>3.413247143833101</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.037069678247562</v>
+        <v>-4.028188491921851</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.364277574913674</v>
+        <v>1.801615322750613</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.1126555430236559</v>
+        <v>0.1166499841305529</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.04705519634064</v>
+        <v>3.483237134311433</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>3.414392988273403</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.916896594883063</v>
+        <v>-3.908015408557352</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.413492652699775</v>
+        <v>1.850830400536714</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.2328286263881549</v>
+        <v>0.2368230674950519</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.120304890799641</v>
+        <v>3.556486828770434</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>3.424481090834842</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.772224449783326</v>
+        <v>-3.763343263457615</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.48144961330111</v>
+        <v>1.918787361138049</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3775007714878923</v>
+        <v>0.3814952125947893</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.217196280420923</v>
+        <v>3.653378218391716</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>3.410518582236268</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.832099277141018</v>
+        <v>-3.823218090815307</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.443537173759459</v>
+        <v>1.880874921596398</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3176259441302002</v>
+        <v>0.3216203852370972</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.167308875407734</v>
+        <v>3.603490813378527</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.992022478163822</v>
+        <v>3.425807751470477</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.712279046230181</v>
+        <v>-3.70339785990447</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.506754435358002</v>
+        <v>1.944092183194941</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3176259441302002</v>
+        <v>0.3216203852370972</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.182598044641942</v>
+        <v>3.618779982612735</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.899666677486263</v>
+        <v>3.333451950792918</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.714748752691987</v>
+        <v>-3.705867566366276</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.413410752095722</v>
+        <v>1.850748499932661</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.315156237668394</v>
+        <v>0.319150678775291</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.0887604200873</v>
+        <v>3.524942358058093</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.818928538971565</v>
+        <v>3.25271381227822</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.783118939015996</v>
+        <v>-3.774237752690285</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.305324539051419</v>
+        <v>1.742662286888358</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.324431936704609</v>
+        <v>0.328426377811506</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.01358770099433</v>
+        <v>3.449769638965124</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.809365247603456</v>
+        <v>3.243150520910111</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.796906991863043</v>
+        <v>-3.788025805537332</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.290246026544491</v>
+        <v>1.727583774381431</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.324431936704609</v>
+        <v>0.328426377811506</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.004024409626222</v>
+        <v>3.440206347597015</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.946396084295658</v>
+        <v>3.380181357602313</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.852427067755633</v>
+        <v>-3.843545881429922</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.405068832879658</v>
+        <v>1.842406580716597</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.324431936704609</v>
+        <v>0.328426377811506</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.141055246318424</v>
+        <v>3.577237184289217</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.950963316287446</v>
+        <v>3.384748589594101</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.676952807963163</v>
+        <v>-3.960514676362813</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.479825768788434</v>
+        <v>1.800186294735229</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.324431936704609</v>
+        <v>0.328426377811506</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.145622478310212</v>
+        <v>3.581804416281005</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.926705345048653</v>
+        <v>3.360490618355308</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.787889060604412</v>
+        <v>-4.071450929004062</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.411193296493141</v>
+        <v>1.731553822439936</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.324431936704609</v>
+        <v>0.328426377811506</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.121364507071419</v>
+        <v>3.557546445042212</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.855243658450103</v>
+        <v>3.289028931756758</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.75422551513213</v>
+        <v>-4.037787383531779</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.353197028083504</v>
+        <v>1.673557554030299</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3580954821768908</v>
+        <v>0.3620899232837878</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.070100947756238</v>
+        <v>3.506282885727031</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.865416044882235</v>
+        <v>3.29920131818889</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.694372895928407</v>
+        <v>-3.977934764328056</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.387310462197125</v>
+        <v>1.707670988143921</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3580954821768908</v>
+        <v>0.3620899232837878</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.08027333418837</v>
+        <v>3.516455272159163</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.860362315456096</v>
+        <v>3.294147588762751</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.60812943290203</v>
+        <v>-3.891691301301679</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.416754117981537</v>
+        <v>1.737114643928332</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3580954821768908</v>
+        <v>0.3620899232837878</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.075219604762231</v>
+        <v>3.511401542733024</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.852138090900621</v>
+        <v>3.285923364207276</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.65343625230101</v>
+        <v>-3.936998120700658</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.39040716566647</v>
+        <v>1.710767691613266</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.31728531916766</v>
+        <v>0.321279760274557</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.042509282401217</v>
+        <v>3.478691220372011</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.852689963933723</v>
+        <v>3.286475237240378</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.682469357003311</v>
+        <v>-3.96603122540296</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.379345796818651</v>
+        <v>1.699706322765447</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.31728531916766</v>
+        <v>0.321279760274557</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.043061155434319</v>
+        <v>3.479243093405112</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.781962655825089</v>
+        <v>3.215747929131743</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.589658875552452</v>
+        <v>-3.873220743952101</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.345742681290361</v>
+        <v>1.666103207237156</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4100958006185194</v>
+        <v>0.4140902417254164</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.0280201361962</v>
+        <v>3.464202074166994</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.783836131749689</v>
+        <v>3.217621405056344</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.634048344881879</v>
+        <v>-3.917610213281528</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.32986036948319</v>
+        <v>1.650220895429986</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3657063312890917</v>
+        <v>0.3697007723959887</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.003259930523145</v>
+        <v>3.439441868493938</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.778911840261412</v>
+        <v>3.212697113568067</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.521377126645629</v>
+        <v>-3.804938995045278</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.370004565289413</v>
+        <v>1.690365091236209</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4783775495253419</v>
+        <v>0.4823719906322389</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.065938369976618</v>
+        <v>3.502120307947411</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.78440313609208</v>
+        <v>3.218188409398735</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.409000125462957</v>
+        <v>-3.692561993862606</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.42044666159315</v>
+        <v>1.740807187539945</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4783775495253419</v>
+        <v>0.4823719906322389</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.071429665807285</v>
+        <v>3.507611603778078</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.795900337860619</v>
+        <v>3.229685611167274</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.43678052336431</v>
+        <v>-3.720342391763959</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.420831704201147</v>
+        <v>1.741192230147943</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4505971516239888</v>
+        <v>0.4545915927308858</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.066258628835012</v>
+        <v>3.502440566805805</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.634256057861272</v>
+        <v>3.068041331167927</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.555161196094448</v>
+        <v>-3.838723064494097</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.211835155109745</v>
+        <v>1.532195681056541</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3833792994730126</v>
+        <v>0.3873737405799096</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.86428363754508</v>
+        <v>3.300465575515873</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.754405718580478</v>
+        <v>3.188190991887133</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.663775274537779</v>
+        <v>-3.947337142937428</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.288539184451619</v>
+        <v>1.608899710398414</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3833792994730126</v>
+        <v>0.3873737405799096</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.984433298264285</v>
+        <v>3.420615236235078</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.768918744682801</v>
+        <v>3.202704017989455</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.628366236289637</v>
+        <v>-3.911928104689285</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.317215825853199</v>
+        <v>1.637576351799994</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3833792994730126</v>
+        <v>0.3873737405799096</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.998946324366608</v>
+        <v>3.435128262337401</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.766338186025169</v>
+        <v>3.200123459331824</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.589982573731485</v>
+        <v>-3.873544442131134</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.329988732218828</v>
+        <v>1.650349258165623</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4217629620311638</v>
+        <v>0.4257574031380608</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.019395963243868</v>
+        <v>3.455577901214661</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.763067214870471</v>
+        <v>3.196852488177126</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.412866243696319</v>
+        <v>-3.696428112095968</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.397564293078196</v>
+        <v>1.717924819024992</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4217629620311638</v>
+        <v>0.4257574031380608</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.01612499208917</v>
+        <v>3.452306930059963</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.763750606632384</v>
+        <v>3.197535879939039</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.457958488529865</v>
+        <v>-3.741520356929514</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.380210786906691</v>
+        <v>1.700571312853486</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.359866918861774</v>
+        <v>0.363861359968671</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.979670757949449</v>
+        <v>3.415852695920242</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.757537581938799</v>
+        <v>3.191322855245454</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.278583067291097</v>
+        <v>-3.562144935690746</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.445747930708612</v>
+        <v>1.766108456655408</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5166436770324927</v>
+        <v>0.5206381181393898</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.067523788158295</v>
+        <v>3.503705726129088</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.738345037270388</v>
+        <v>3.172130310577043</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.323597280811704</v>
+        <v>-3.607159149211352</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.40854970063196</v>
+        <v>1.728910226578755</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4862947817178881</v>
+        <v>0.4902892228247852</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.030121906301122</v>
+        <v>3.466303844271915</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.744036599609334</v>
+        <v>3.177821872915989</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.590601791084139</v>
+        <v>-3.874163659483788</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.307439458861931</v>
+        <v>1.627799984808727</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2919317436749395</v>
+        <v>0.2959261847818366</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.919195645814298</v>
+        <v>3.355377583785091</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.743240521505836</v>
+        <v>3.17702579481249</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.691799572521312</v>
+        <v>-3.975361440920961</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.266164268183564</v>
+        <v>1.586524794130359</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2235229301296203</v>
+        <v>0.2275173712365174</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.877354279583608</v>
+        <v>3.313536217554401</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.740840483060152</v>
+        <v>3.174625756366807</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.685288605906999</v>
+        <v>-3.968850474306648</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.266368616383605</v>
+        <v>1.586729142330401</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2235229301296203</v>
+        <v>0.2275173712365174</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.874954241137925</v>
+        <v>3.311136179108718</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.737365202268397</v>
+        <v>3.171150475575052</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.666250478199702</v>
+        <v>-3.949812346599351</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.270508586674769</v>
+        <v>1.590869112621565</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1653393187984258</v>
+        <v>0.1693337599053228</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.836568793547453</v>
+        <v>3.272750731518246</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.914947071207078</v>
+        <v>3.348732344513733</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.69737710935032</v>
+        <v>-3.980938977749969</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.435639803153202</v>
+        <v>1.756000329099998</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1653393187984258</v>
+        <v>0.1693337599053228</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.014150662486133</v>
+        <v>3.450332600456927</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.915780400193211</v>
+        <v>3.349565673499866</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.711243870684237</v>
+        <v>-3.994805739083886</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.430926427605769</v>
+        <v>1.751286953552565</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1274814020646028</v>
+        <v>0.1314758431714999</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.992269241431973</v>
+        <v>3.428451179402766</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.921788930590137</v>
+        <v>3.355574203896792</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.666439699144307</v>
+        <v>-3.950001567543956</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.454856626618667</v>
+        <v>1.775217152565463</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1274814020646028</v>
+        <v>0.1314758431714999</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.998277771828899</v>
+        <v>3.434459709799692</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.819739151867337</v>
+        <v>3.253524425173992</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.518696728909305</v>
+        <v>-3.802258597308954</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.411904035989867</v>
+        <v>1.732264561936663</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.295288759299486</v>
+        <v>0.2992832004063831</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.996912407447029</v>
+        <v>3.433094345417822</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.822532773398818</v>
+        <v>3.256318046705473</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.620711411440526</v>
+        <v>-3.893302699509077</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.37389178450886</v>
+        <v>1.698640542588095</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.295288759299486</v>
+        <v>0.2992832004063831</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.99970602897851</v>
+        <v>3.435887966949303</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.823195121790476</v>
+        <v>3.256980395097131</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.614558705387742</v>
+        <v>-3.887149993456292</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.377015215321632</v>
+        <v>1.701763973400867</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3014414653522703</v>
+        <v>0.3054359064591674</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.004060001001839</v>
+        <v>3.440241938972632</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.822275598530586</v>
+        <v>3.256060871837241</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.631368003538243</v>
+        <v>-3.903959291606794</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.369371972801542</v>
+        <v>1.694120730880776</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2846321672017686</v>
+        <v>0.2886266083086657</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.993054898851648</v>
+        <v>3.429236836822441</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.888611152327407</v>
+        <v>3.322396425634062</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.569070004762121</v>
+        <v>-3.841661292830672</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.460626726108811</v>
+        <v>1.785375484188046</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2846321672017686</v>
+        <v>0.2886266083086657</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.059390452648469</v>
+        <v>3.495572390619262</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.690903154041534</v>
+        <v>3.124688427348189</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.367279807096963</v>
+        <v>-3.639871095165514</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.343634806889002</v>
+        <v>1.668383564968236</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.482650359370923</v>
+        <v>0.4866448004778201</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.980493369664088</v>
+        <v>3.416675307634882</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.761193386363709</v>
+        <v>3.194978659670364</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.202466804018116</v>
+        <v>-3.475058092086667</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.479850240442716</v>
+        <v>1.80459899852195</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.64746336244977</v>
+        <v>0.651457803556667</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.149671403833572</v>
+        <v>3.585853341804365</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.775821122479753</v>
+        <v>3.209606395786408</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.300207348643091</v>
+        <v>-3.572798636711641</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.45538175870877</v>
+        <v>1.780130516788004</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6315740843167899</v>
+        <v>0.6355685254236869</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.154765573069827</v>
+        <v>3.59094751104062</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.774357103304425</v>
+        <v>3.20814237661108</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.47654510876602</v>
+        <v>-3.749136396834571</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.38338263548427</v>
+        <v>1.708131393563504</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4552363241938605</v>
+        <v>0.4592307653007575</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.047498897820741</v>
+        <v>3.483680835791534</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397797</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.772848721344353</v>
+        <v>3.206633994651008</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.400123062334093</v>
+        <v>-3.672714350402644</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.412443072096969</v>
+        <v>1.737191830176203</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4552363241938605</v>
+        <v>0.4592307653007575</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.04599051586067</v>
+        <v>3.482172453831463</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316252</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.77271158877979</v>
+        <v>3.206496862086444</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.355749930695525</v>
+        <v>-3.628341218764075</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.430055192187832</v>
+        <v>1.754803950267067</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4996094558324291</v>
+        <v>0.5036038969393262</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.072477262279247</v>
+        <v>3.50865920025004</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.76710538291838</v>
+        <v>3.200890656225035</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.232915709808357</v>
+        <v>-3.505506997876908</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.47358267468129</v>
+        <v>1.798331432760525</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4996094558324291</v>
+        <v>0.5036038969393262</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.066871056417838</v>
+        <v>3.503052994388631</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190328</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.773487139946185</v>
+        <v>3.20727241325284</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.185259979247301</v>
+        <v>-3.457851267315852</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.499026723933517</v>
+        <v>1.823775482012752</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5472651863934848</v>
+        <v>0.5512596275003818</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.101846251782276</v>
+        <v>3.538028189753069</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056962</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.778379513320909</v>
+        <v>3.212164786627564</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.084741820748547</v>
+        <v>-3.357333108817097</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.544126360707744</v>
+        <v>1.868875118786978</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6477833448922393</v>
+        <v>0.6517777859991364</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.167049520256253</v>
+        <v>3.603231458227047</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557296</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.765134185796782</v>
+        <v>3.198919459103437</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.145408411150936</v>
+        <v>-3.417999699219486</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.50661439702266</v>
+        <v>1.831363155101895</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5660850281737057</v>
+        <v>0.5700794692806027</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.104785202701005</v>
+        <v>3.540967140671798</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932771</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.76923188840741</v>
+        <v>3.203017161714065</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.100570009542538</v>
+        <v>-3.373161297611088</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.528647460276648</v>
+        <v>1.853396218355883</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5706284611185751</v>
+        <v>0.5746229022254722</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.111608965078556</v>
+        <v>3.547790903049349</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.773392828038488</v>
+        <v>3.207178101345143</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.120068465784546</v>
+        <v>-3.392659753853096</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.525009017410923</v>
+        <v>1.849757775490157</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5225438198386708</v>
+        <v>0.5265382609455679</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.086919119941691</v>
+        <v>3.523101057912484</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.779272430566325</v>
+        <v>3.21305770387298</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.075865628698645</v>
+        <v>-3.348456916767196</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.54856975477312</v>
+        <v>1.873318512852355</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5667466569245713</v>
+        <v>0.5707410980314683</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.119320424721069</v>
+        <v>3.555502362691862</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.777682431035573</v>
+        <v>3.211467704342228</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.112844656362089</v>
+        <v>-3.385435944430639</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.53218814417699</v>
+        <v>1.856936902256225</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6037205587159018</v>
+        <v>0.6077149998227989</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.139914766265115</v>
+        <v>3.576096704235908</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.828930196218613</v>
+        <v>3.262715469525268</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.954553238822816</v>
+        <v>-3.227144526891367</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.646752476375739</v>
+        <v>1.971501234454974</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6037205587159018</v>
+        <v>0.6077149998227989</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.191162531448154</v>
+        <v>3.627344469418947</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321018</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.827370900812866</v>
+        <v>3.261156174119521</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.74691123518834</v>
+        <v>-3.019502523256891</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.728249982423782</v>
+        <v>2.052998740503017</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.811362562350378</v>
+        <v>0.815357003457275</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.314188438223093</v>
+        <v>3.750370376193886</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.86448984247514</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.822319129051136</v>
+        <v>3.256104402357791</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.695879142465812</v>
+        <v>-2.968470430534363</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.743611047751064</v>
+        <v>2.068359805830299</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8623946550729059</v>
+        <v>0.866389096179803</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.33975592209488</v>
+        <v>3.775937860065673</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.839506533143841</v>
+        <v>3.273291806450496</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.630654961338607</v>
+        <v>-2.903246249407157</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.786888124294651</v>
+        <v>2.111636882373886</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9276188362001115</v>
+        <v>0.9316132773070086</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.396077834863908</v>
+        <v>3.832259772834701</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.835467505443121</v>
+        <v>3.269252778749776</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.593227941267473</v>
+        <v>-2.865819229336024</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.797819904622385</v>
+        <v>2.122568662701619</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9328703742292932</v>
+        <v>0.9368648153361903</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.395189729980697</v>
+        <v>3.83137166795149</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.836724297774361</v>
+        <v>3.270509571081016</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.613339597302181</v>
+        <v>-2.885930885370732</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.791032034539742</v>
+        <v>2.115780792618977</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9438977192267124</v>
+        <v>0.9478921603336095</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.403062929310389</v>
+        <v>3.839244867281182</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.997282068795572</v>
+        <v>3.431067342102227</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.559594782874977</v>
+        <v>-2.832186070943527</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.973087731331834</v>
+        <v>2.297836489411069</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9539610286671744</v>
+        <v>0.9579554697740714</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.569658685995877</v>
+        <v>4.00584062396667</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.117394978013389</v>
+        <v>3.551180251320044</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.484812521849964</v>
+        <v>-2.757403809918515</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.123113544959657</v>
+        <v>2.447862303038892</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.028743289692187</v>
+        <v>1.032737730799084</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.734640951828702</v>
+        <v>4.170822889799495</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.109102954027248</v>
+        <v>3.542888227333903</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.458728437586156</v>
+        <v>-2.731319725654707</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.125255154679039</v>
+        <v>2.450003912758273</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.028743289692187</v>
+        <v>1.032737730799084</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.726348927842561</v>
+        <v>4.162530865813354</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.107296149611028</v>
+        <v>3.541081422917683</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.380597256737209</v>
+        <v>-2.65318854480576</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.154700822602397</v>
+        <v>2.479449580681631</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.102920100575872</v>
+        <v>1.106914541682769</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.769048209956551</v>
+        <v>4.205230147927344</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.124850555337819</v>
+        <v>3.558635828644474</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.371704795343926</v>
+        <v>-2.644296083412477</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.175812212886501</v>
+        <v>2.500560970965736</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.102920100575872</v>
+        <v>1.106914541682769</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.786602615683342</v>
+        <v>4.222784553654136</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.116705602742403</v>
+        <v>3.550490876049058</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.540180912313804</v>
+        <v>-2.812772200382355</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.100276813503134</v>
+        <v>2.425025571582369</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.074972264859291</v>
+        <v>1.078966705966188</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.761688961657978</v>
+        <v>4.197870899628771</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.097975299930265</v>
+        <v>3.53176057323692</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.842381383452221</v>
+        <v>-2.114972671520771</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.360666322235629</v>
+        <v>2.685415080314864</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.00462420548888</v>
+        <v>1.008618646595777</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.700749823223593</v>
+        <v>4.136931761194386</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.08863932242717</v>
+        <v>3.522424595733824</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.819660279769068</v>
+        <v>-2.092251567837619</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.360418786205795</v>
+        <v>2.68516754428503</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.00462420548888</v>
+        <v>1.008618646595777</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.691413845720498</v>
+        <v>4.127595783691291</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.247545448278339</v>
+        <v>3.681330721584994</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.817935236479024</v>
+        <v>-2.090526524547575</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.520014929372981</v>
+        <v>2.844763687452216</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.006349248778924</v>
+        <v>1.010343689885821</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.851354997545693</v>
+        <v>4.287536935516487</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.284623270771985</v>
+        <v>3.71840854407864</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.97271624325728</v>
+        <v>-2.24530753132583</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.495180349155326</v>
+        <v>2.819929107234561</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9729815747244479</v>
+        <v>0.9769760158313447</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.868412215606654</v>
+        <v>4.304594153577447</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.28129862676153</v>
+        <v>3.715083900068185</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.965661553042106</v>
+        <v>-2.238252841110656</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.494677581230941</v>
+        <v>2.819426339310175</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9800362649396217</v>
+        <v>0.9840307060465185</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.869320385725303</v>
+        <v>4.305502323696096</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.291304780406272</v>
+        <v>3.725090053712927</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.938710328715618</v>
+        <v>-2.211301616784168</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.515464224606277</v>
+        <v>2.840212982685512</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9949166109673409</v>
+        <v>0.9989110520742377</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.888254746986677</v>
+        <v>4.32443668495747</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.475407912551232</v>
+        <v>3.909193185857887</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.074663336771934</v>
+        <v>-2.347254624840485</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.645186153528711</v>
+        <v>2.969934911607945</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9949166109673409</v>
+        <v>0.9989110520742377</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.072357879131636</v>
+        <v>4.508539817102429</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.467524607454225</v>
+        <v>3.90130988076088</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.097071454576806</v>
+        <v>-2.369662742645357</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.628339601309755</v>
+        <v>2.95308835938899</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9949166109673409</v>
+        <v>0.9989110520742377</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.064474574034629</v>
+        <v>4.500656512005422</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.469578607003862</v>
+        <v>3.903363880310517</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.245077222056206</v>
+        <v>-2.517668510124756</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.571191293867633</v>
+        <v>2.895940051946868</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9081896021037994</v>
+        <v>0.9121840432106962</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.014492368266142</v>
+        <v>4.450674306236935</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.525832324725709</v>
+        <v>3.959617598032365</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.254518147944736</v>
+        <v>-2.527109436013286</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.623668641234068</v>
+        <v>2.948417399313303</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.030616719647191</v>
+        <v>1.034611160754088</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.144202356514024</v>
+        <v>4.580384294484817</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.52872341927101</v>
+        <v>3.962508692577666</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.306791755280377</v>
+        <v>-2.579383043348928</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.605650292845112</v>
+        <v>2.930399050924348</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9783431123115497</v>
+        <v>0.9823375534184465</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.11572928665794</v>
+        <v>4.551911224628734</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.526835232164785</v>
+        <v>3.960620505471441</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.383121732881283</v>
+        <v>-2.655713020949833</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.573230114698525</v>
+        <v>2.89797887277776</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9783431123115497</v>
+        <v>0.9823375534184465</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.113841099551715</v>
+        <v>4.550023037522509</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887749</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.521655461767648</v>
+        <v>3.955440735074303</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.494878685496584</v>
+        <v>-2.767469973565134</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.523347563255267</v>
+        <v>2.848096321334502</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8665861596962485</v>
+        <v>0.8705806008031454</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.041607157585397</v>
+        <v>4.47778909555619</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.5200894719778</v>
+        <v>3.953874745284455</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.493037666438333</v>
+        <v>-2.765628954506883</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.52251798108872</v>
+        <v>2.847266739167955</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8678543863677169</v>
+        <v>0.8718488274746138</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.040802103798431</v>
+        <v>4.476984041769224</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647107</v>
+        <v>3.754911907647101</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.533162878843719</v>
+        <v>3.966948152150374</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.625338958535886</v>
+        <v>-2.897930246604437</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.482670871115617</v>
+        <v>2.807419629194852</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8678543863677169</v>
+        <v>0.8718488274746138</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.053875510664349</v>
+        <v>4.490057448635142</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763533</v>
+        <v>3.749896851763528</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.533162878843719</v>
+        <v>3.966948152150374</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.626900601350746</v>
+        <v>-2.899491889419297</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.482046213989673</v>
+        <v>2.806794972068908</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8678543863677169</v>
+        <v>0.8718488274746138</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.053875510664349</v>
+        <v>4.490057448635142</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392117</v>
+        <v>3.715834055392111</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.531686919970721</v>
+        <v>3.965472193277376</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.654801388460219</v>
+        <v>-2.92739267652877</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.469409940272886</v>
+        <v>2.79415869835212</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8332574622247821</v>
+        <v>0.837251903331679</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.03164139730559</v>
+        <v>4.467823335276384</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172522</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.528451363947919</v>
+        <v>3.962236637254574</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.777327491163113</v>
+        <v>-3.049918779231664</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.417163943168927</v>
+        <v>2.741912701248162</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7107313595218883</v>
+        <v>0.7147258006287851</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.954890179661053</v>
+        <v>4.391072117631846</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971074</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.595157323538423</v>
+        <v>4.028942596845078</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.79738881243962</v>
+        <v>-3.06998010050817</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.475845374248828</v>
+        <v>2.800594132328063</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6906700382453812</v>
+        <v>0.694664479352278</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.009559346485652</v>
+        <v>4.445741284456445</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199806</v>
+        <v>3.640764248199801</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.73546904254027</v>
+        <v>4.169254315846925</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.054109630434444</v>
+        <v>-3.326700918502994</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.513468766052745</v>
+        <v>2.83821752413198</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5822554641015664</v>
+        <v>0.5862499052084632</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.08482232100121</v>
+        <v>4.521004258972003</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622231</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.80444931168591</v>
+        <v>4.238234584992565</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.208096048210584</v>
+        <v>-3.480687336279135</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.520854468087929</v>
+        <v>2.845603226167164</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5822554641015664</v>
+        <v>0.5862499052084632</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.15380259014685</v>
+        <v>4.589984528117643</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808524</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.790500513806031</v>
+        <v>4.224285787112686</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.157574144382918</v>
+        <v>-3.430165432451469</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.527114431739116</v>
+        <v>2.851863189818351</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5822554641015664</v>
+        <v>0.5862499052084632</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.139853792266971</v>
+        <v>4.576035730237765</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.656346893994889</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.802371002861445</v>
+        <v>4.2361562761681</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.410049298390643</v>
+        <v>-3.682640586459193</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.43799485919144</v>
+        <v>2.762743617270676</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5822554641015664</v>
+        <v>0.5862499052084632</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.151724281322385</v>
+        <v>4.587906219293179</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.674042696358293</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.803581537380389</v>
+        <v>4.237366810687044</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.679522100312351</v>
+        <v>-3.952113388380901</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.331416272941701</v>
+        <v>2.656165031020937</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5822554641015664</v>
+        <v>0.5862499052084632</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.152934815841329</v>
+        <v>4.589116753812123</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637087</v>
+        <v>3.663523617637082</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.80770327960771</v>
+        <v>4.241488552914366</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.837066172041792</v>
+        <v>-4.216127028206125</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.272520386477246</v>
+        <v>2.554681317318169</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5153536589612919</v>
+        <v>0.4986896940093016</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.116915474984485</v>
+        <v>4.540702369319948</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301344</v>
+        <v>3.652163313301338</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.802781132343899</v>
+        <v>4.236566405650556</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.965916722743839</v>
+        <v>-4.344977578908171</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.216058018932617</v>
+        <v>2.49821894977354</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4743602501105704</v>
+        <v>0.4576962851585801</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.087397282410242</v>
+        <v>4.511184176745704</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66797646721547</v>
+        <v>3.667976467215465</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.964985189042944</v>
+        <v>4.3987704623496</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.08288441538273</v>
+        <v>-4.461945271547062</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.331474998576105</v>
+        <v>2.613635929417028</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4743602501105704</v>
+        <v>0.4576962851585801</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.249601339109286</v>
+        <v>4.673388233444749</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456693</v>
+        <v>3.696553628456687</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.959831827006758</v>
+        <v>4.393617100313414</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.167602357603683</v>
+        <v>-4.546663213768015</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.292434459651537</v>
+        <v>2.574595390492461</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.389244221182524</v>
+        <v>0.3725802562305337</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.193378359716272</v>
+        <v>4.617165254051735</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253289</v>
+        <v>3.750058176253283</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.970061244575249</v>
+        <v>4.403846517881906</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.249537175872566</v>
+        <v>-4.628598032036899</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.269889949912475</v>
+        <v>2.552050880753399</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3793094755954438</v>
+        <v>0.3626455106434535</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.197646929932516</v>
+        <v>4.621433824267978</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717833</v>
+        <v>3.783647027717827</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.978986883031151</v>
+        <v>4.412772156337808</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.195799002472304</v>
+        <v>-4.574859858636636</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.300310857728483</v>
+        <v>2.582471788569406</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4330476489957059</v>
+        <v>0.4163836840437156</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.238815472428575</v>
+        <v>4.662602366764037</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616949</v>
+        <v>3.798310944616944</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.971139770275327</v>
+        <v>4.404925043581984</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.085792718995083</v>
+        <v>-4.464853575159415</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.336466258363547</v>
+        <v>2.618627189204471</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4562522209129811</v>
+        <v>0.4395882559609908</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.244891102823116</v>
+        <v>4.668677997158579</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203663</v>
+        <v>3.785578085203658</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.975389780997301</v>
+        <v>4.409175054303958</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.942733143254157</v>
+        <v>-4.321793999418489</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.397940099381891</v>
+        <v>2.680101030222815</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4642656475029604</v>
+        <v>0.4476016825509701</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.253949169499077</v>
+        <v>4.677736063834541</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436929</v>
+        <v>3.777251572436923</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.982650663879838</v>
+        <v>4.416435937186495</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.64128641778232</v>
+        <v>-4.020347273946651</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.525779672453162</v>
+        <v>2.807940603294087</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7657123729747977</v>
+        <v>0.7490484080228074</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.442078087664717</v>
+        <v>4.865864982000179</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064767</v>
+        <v>3.812650101064762</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.983621841632548</v>
+        <v>4.417407114939205</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.696241614225389</v>
+        <v>-4.075302470389721</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.504768771628645</v>
+        <v>2.786929702469569</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7657123729747977</v>
+        <v>0.7490484080228074</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.443049265417427</v>
+        <v>4.866836159752889</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859301</v>
+        <v>3.821198342859295</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.984464746012303</v>
+        <v>4.41825001931896</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.645203238218869</v>
+        <v>-4.0242640943832</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.526027026411009</v>
+        <v>2.808187957251933</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7657123729747977</v>
+        <v>0.7490484080228074</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.443892169797182</v>
+        <v>4.867679064132645</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354686</v>
+        <v>3.831748677354682</v>
       </c>
       <c r="C2032" t="n">
-        <v>4.003502844886449</v>
+        <v>4.437288118193106</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.604063943352238</v>
+        <v>-3.372613608945848</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.561520843231807</v>
+        <v>3.087886250301019</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8068516678414285</v>
+        <v>1.40069889346016</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.487613845591306</v>
+        <v>5.277707454269201</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.465382938752114</v>
+        <v>3.835346054550117</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.717571630186394</v>
+        <v>4.432276621145237</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.604063943352238</v>
+        <v>-3.385186267143184</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.561520843231807</v>
+        <v>3.077845689974216</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8068516678414285</v>
+        <v>1.388126235262824</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.710635427172762</v>
+        <v>5.265152362302932</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240722.xlsx
+++ b/tame_output/ON/bt/strategyON_20240722.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>103.8%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>131.6%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-72.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>110.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>102.9%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.3%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.7%</t>
+          <t>-67.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.8%</t>
+          <t>457.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-500.1%</t>
+          <t>-507.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>-39.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>-125.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>188.9%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-108.3%</t>
+          <t>-131.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-85.2%</t>
+          <t>-116.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>119.2%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -44420,19 +44420,19 @@
         <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.549225793250327</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
         <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.142692023523782</v>
+        <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.895500868648388</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44443,19 +44443,19 @@
         <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.544411225721787</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
         <v>-6.129203775554858</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.092373291186097</v>
+        <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.890686301119848</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.542405276330665</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
         <v>-6.545595649841855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9238105920801751</v>
+        <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.888680351728726</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.552663966999344</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-6.914997051364124</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8363607224580263</v>
+        <v>0.3525234488332916</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.898939042397405</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.548763532145039</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.995118069805685</v>
+        <v>-7.120248070600884</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7503598799090172</v>
+        <v>0.2665226062842829</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.8950386075431</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.54716845220004</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.043320887048029</v>
+        <v>-7.168450887843228</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.7294836730670808</v>
+        <v>0.2456463994423461</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.893443527598101</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.550947428129248</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.339982228858227</v>
+        <v>-7.465112229653426</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6145981122722097</v>
+        <v>0.1307608386474755</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.855976622086982</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.546921123594845</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.526701937167529</v>
+        <v>-7.651831937962728</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5358839244140858</v>
+        <v>0.05204665078935111</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.851950317552579</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.546819022273261</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.909703325910161</v>
+        <v>-8.034833326705359</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.382581267595449</v>
+        <v>-0.1012560060292849</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.851848216230995</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.549390538244691</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.914189771111549</v>
+        <v>-8.039319771906747</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.3833582054863238</v>
+        <v>-0.1004790681384105</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.851727865081592</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.554740841542741</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.273720093615552</v>
+        <v>-8.398850094410749</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.244896379782773</v>
+        <v>-0.2389408938419608</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.857078168379642</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.562656861499919</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.324069157069774</v>
+        <v>-8.449199157864971</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.2326727743582615</v>
+        <v>-0.2511644992664723</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.834784750264286</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.565698612121687</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.42168843449117</v>
+        <v>-8.546818435286367</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.196666814011472</v>
+        <v>-0.2871704596132618</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.779254934433217</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.56859216844326</v>
+        <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.475759933999528</v>
+        <v>-8.600889934794726</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.177931770529701</v>
+        <v>-0.3059055030950328</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.749705591049774</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.574105365561902</v>
+        <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.680018109329392</v>
+        <v>-8.805148110124589</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.1017416975163976</v>
+        <v>-0.3820955761083362</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.678635421400023</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.578587920046338</v>
+        <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.713670947837866</v>
+        <v>-8.838800948633063</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.0927631165974443</v>
+        <v>-0.3910741570272895</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.622869955134236</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.593959621539759</v>
+        <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.640201116170417</v>
+        <v>-8.765331116965614</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.1375227507578449</v>
+        <v>-0.3463145228668889</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.682323555628126</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.608514842287276</v>
+        <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.81532553355696</v>
+        <v>-8.940455534352157</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.08202820455074455</v>
+        <v>-0.4018090690739893</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.591804125943717</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.60129567738568</v>
+        <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.04977762757145</v>
+        <v>-9.174907628366647</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.0189717979566475</v>
+        <v>-0.5028090715813813</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.584584961042121</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.594623486611704</v>
+        <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.279282359393093</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.06739388114120226</v>
+        <v>-0.5512311547659361</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.515287931652277</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.59573927645026</v>
+        <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.33206851499342</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.08739255354277642</v>
+        <v>-0.5712298271675103</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.458998429541396</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.598433005079375</v>
+        <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.458105308361709</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.1351135422609775</v>
+        <v>-0.6189508158857113</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.476843131856355</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.602423340765776</v>
+        <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.401033536465778</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.1082944978162041</v>
+        <v>-0.592131771440938</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.480833467542756</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.600948113867034</v>
+        <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.542705378189899</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.166438461404594</v>
+        <v>-0.6502757350293278</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.479358240644014</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.616001524031906</v>
+        <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.493114533765064</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.1315487134697881</v>
+        <v>-0.615385987094522</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.524166157463787</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.602950390385223</v>
+        <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.344196199293208</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.08503251332772832</v>
+        <v>-0.5688697869524622</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.529864778258208</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.612529463421432</v>
+        <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-9.118351046573796</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.01488462079624409</v>
+        <v>-0.4689526528284889</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.564599856646715</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.613668607977491</v>
+        <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-8.993772390236204</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.06585522788733966</v>
+        <v>-0.4179820457373933</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.565739001202774</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.616302382139598</v>
+        <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-9.046667678280491</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.04733088683173303</v>
+        <v>-0.4365063867930004</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.571345983017949</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.622036086378235</v>
+        <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-8.97453450299261</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.0819178611855218</v>
+        <v>-0.4019194124392111</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.577079687256585</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.61229882398437</v>
+        <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-8.903168110382962</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.1007271558355156</v>
+        <v>-0.3831101177892178</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.610162260428509</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.602415342671462</v>
+        <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.809709076397738</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.1282272881166979</v>
+        <v>-0.3556099855080355</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.600278779115602</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.600580782172088</v>
+        <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.54246727552934</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.2332894479646832</v>
+        <v>-0.2505478256600502</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.598444218616228</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.600280467198627</v>
+        <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.444560236852849</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.2721519484618184</v>
+        <v>-0.2116853251629145</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.638935353559101</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.600948973344121</v>
+        <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.420606695876891</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.2824018709976954</v>
+        <v>-0.201435402627038</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.653975984290169</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.587688657182369</v>
+        <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-8.156546757554095</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.3747655301650621</v>
+        <v>-0.1090717434596713</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.799151631122094</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.584901623522068</v>
+        <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.449467134049256</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.6548103459066965</v>
+        <v>0.1709730722819631</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.796364597461793</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.585245247409909</v>
+        <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.409282835683066</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.6712276891410141</v>
+        <v>0.1873904155162807</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.82081880036935</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.584612068630666</v>
+        <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.245882964743704</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.735954458737516</v>
+        <v>0.2521171851127826</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.918225544153724</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.592536497468519</v>
+        <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-7.012401742514105</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.8372713764672075</v>
+        <v>0.3534341028424746</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.066238706329336</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.58964428715556</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-6.86273535150659</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.8942457225572547</v>
+        <v>0.4104084489325213</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.119088590761898</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.585011773902587</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.730459877875703</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.9425233987566362</v>
+        <v>0.4586861251319028</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.193821361687457</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.587826834590223</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.574721545315962</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.00763379246817</v>
+        <v>0.5237965188434366</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.290079421910939</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.600733175813882</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.325721746632381</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.120140053165261</v>
+        <v>0.6363027795405274</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.302985763134597</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.472757246214663</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.431311736405485</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.9499281276568001</v>
+        <v>0.4660908540320672</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.111655839671516</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.52130158809175</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.450046638524082</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.9909785086864478</v>
+        <v>0.5071412350617148</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.156842575752524</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.401422665403582</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.302106597116483</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.9302756025613199</v>
+        <v>0.446438328936587</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.04915620260949</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.392708679150104</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.249137074862494</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.9427494252094371</v>
+        <v>0.4589121515847041</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.072223929708406</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.385748067055011</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.205588668091804</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.9532081758226201</v>
+        <v>0.4693709021978871</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.065263317613312</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.400210421436154</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.04709546081784</v>
+        <v>-6.172225461613035</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.9810158127952708</v>
+        <v>0.4971785391705374</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.079725671994455</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.394742541895349</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.938836323695318</v>
+        <v>-6.063966324490513</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.018851588103475</v>
+        <v>0.5350143144787411</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.07425779245365</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.392240635905926</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.815545188878187</v>
+        <v>-5.940675189673382</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.065666136040904</v>
+        <v>0.5818288624161707</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.145730567354506</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.399941614143251</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.794395989974744</v>
+        <v>-5.919525990769939</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.081826793839606</v>
+        <v>0.5979895202148731</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.166121064933897</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.395722322490302</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.550630547991299</v>
+        <v>-5.675760548786495</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.175113678980034</v>
+        <v>0.6912764053553015</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.161901773280948</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.397846636410318</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.448867727714005</v>
+        <v>-5.5739977285092</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.217943121010969</v>
+        <v>0.7341058473862354</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.171957528236421</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.39058871139402</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.19901733376493</v>
+        <v>-5.324147334560125</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.3106253535743</v>
+        <v>0.8267880799495675</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.164699603220123</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.394187834914669</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.023125241297498</v>
+        <v>-5.148255242092693</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.384581314081922</v>
+        <v>0.9007440404571891</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.168298726740772</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.407515340969222</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.851678778275034</v>
+        <v>-4.97680877907023</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.466487405345461</v>
+        <v>0.9826501317207281</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.284494110608803</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.406535818585519</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.777389212536695</v>
+        <v>-4.902519213331891</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.495223709257094</v>
+        <v>1.011386435632361</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.328088327668104</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.411230619639837</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.713753470302761</v>
+        <v>-4.838883471097956</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.525372807204985</v>
+        <v>1.041535533580252</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.370964574062782</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.392424878423632</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.727456711772036</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.551137769719149</v>
+        <v>1.067300496094415</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.352158832846578</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.39416795504851</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.615122754954449</v>
+        <v>-4.487026214967176</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.547762428752983</v>
+        <v>1.165215771441237</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.07990611993936614</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.34622428308489</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367681</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.39809726888333</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.542880186783254</v>
+        <v>-4.498460759178897</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.580588769856281</v>
+        <v>1.164571267591369</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.07990611993936614</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.35015359691971</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.39877585280067</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.489881864501866</v>
+        <v>-4.445462436897509</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.602466682686176</v>
+        <v>1.186449180421264</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.0245698609374273</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.384033936238214</v>
+        <v>3.10218458740104</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.395773924020663</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.381076979022139</v>
+        <v>-4.336657551417782</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.64298670809806</v>
+        <v>1.226969205833148</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.0245698609374273</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.381032007458207</v>
+        <v>3.099182658621033</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.397352961031277</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.161056180985129</v>
+        <v>-4.116636753380772</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.732574064323479</v>
+        <v>1.316556562058566</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.1166499841305529</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.467342951509609</v>
+        <v>3.185493602672435</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.413247143833101</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.028188491921851</v>
+        <v>-3.983769064317494</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.801615322750613</v>
+        <v>1.385597820485701</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.1166499841305529</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.483237134311433</v>
+        <v>3.201387785474259</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.414392988273403</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.908015408557352</v>
+        <v>-3.863595980952995</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.850830400536714</v>
+        <v>1.434812898271802</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.2368230674950519</v>
+        <v>0.4900496082775201</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.556486828770434</v>
+        <v>3.27463747993326</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.424481090834842</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.763343263457615</v>
+        <v>-3.718923835853257</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.918787361138049</v>
+        <v>1.502769858873137</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3814952125947893</v>
+        <v>0.6347217533772576</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.653378218391716</v>
+        <v>3.371528869554542</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.410518582236268</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.823218090815307</v>
+        <v>-3.778798663210949</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.880874921596398</v>
+        <v>1.464857419331486</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3216203852370972</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.603490813378527</v>
+        <v>3.321641464541353</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.425807751470477</v>
+        <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.70339785990447</v>
+        <v>-3.658978432300112</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.944092183194941</v>
+        <v>1.52807468093003</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3216203852370972</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.618779982612735</v>
+        <v>3.336930633775562</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.333451950792918</v>
+        <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.705867566366276</v>
+        <v>-3.661448138761918</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.850748499932661</v>
+        <v>1.434730997667749</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.319150678775291</v>
+        <v>0.5723772195577592</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.524942358058093</v>
+        <v>3.243093009220919</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.25271381227822</v>
+        <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.774237752690285</v>
+        <v>-3.729818325085928</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.742662286888358</v>
+        <v>1.326644784623446</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.328426377811506</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.449769638965124</v>
+        <v>3.16792029012795</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.243150520910111</v>
+        <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.788025805537332</v>
+        <v>-3.743606377932974</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.727583774381431</v>
+        <v>1.311566272116519</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.328426377811506</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.440206347597015</v>
+        <v>3.158356998759841</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.380181357602313</v>
+        <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.843545881429922</v>
+        <v>-3.799126453825564</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.842406580716597</v>
+        <v>1.426389078451685</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.328426377811506</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.577237184289217</v>
+        <v>3.295387835452043</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.384748589594101</v>
+        <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.960514676362813</v>
+        <v>-3.623652194033095</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.800186294735229</v>
+        <v>1.501146014360461</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.328426377811506</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.581804416281005</v>
+        <v>3.299955067443831</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
-        <v>3.360490618355308</v>
+        <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.071450929004062</v>
+        <v>-3.734588446674343</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.731553822439936</v>
+        <v>1.432513542065169</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.328426377811506</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.557546445042212</v>
+        <v>3.275697096205038</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>3.289028931756758</v>
+        <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.037787383531779</v>
+        <v>-3.700924901202062</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.673557554030299</v>
+        <v>1.374517273655531</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3620899232837878</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.506282885727031</v>
+        <v>3.224433536889857</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>3.29920131818889</v>
+        <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.977934764328056</v>
+        <v>-3.641072281998338</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.707670988143921</v>
+        <v>1.408630707769153</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3620899232837878</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.516455272159163</v>
+        <v>3.234605923321989</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>3.294147588762751</v>
+        <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.891691301301679</v>
+        <v>-3.554828818971961</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.737114643928332</v>
+        <v>1.438074363553564</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3620899232837878</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.511401542733024</v>
+        <v>3.22955219389585</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>3.285923364207276</v>
+        <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.936998120700658</v>
+        <v>-3.600135638370941</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.710767691613266</v>
+        <v>1.411727411238498</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.321279760274557</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.478691220372011</v>
+        <v>3.196841871534837</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>3.286475237240378</v>
+        <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.96603122540296</v>
+        <v>-3.629168743073242</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.699706322765447</v>
+        <v>1.400666042390679</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.321279760274557</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.479243093405112</v>
+        <v>3.197393744567938</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
-        <v>3.215747929131743</v>
+        <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.873220743952101</v>
+        <v>-3.536358261622383</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.666103207237156</v>
+        <v>1.367062926862388</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4140902417254164</v>
+        <v>0.6673167825078846</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.464202074166994</v>
+        <v>3.18235272532982</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>3.217621405056344</v>
+        <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.917610213281528</v>
+        <v>-3.580747730951811</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.650220895429986</v>
+        <v>1.351180615055218</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3697007723959887</v>
+        <v>0.622927313178457</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.439441868493938</v>
+        <v>3.157592519656764</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>3.212697113568067</v>
+        <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.804938995045278</v>
+        <v>-3.468076512715561</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.690365091236209</v>
+        <v>1.391324810861441</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4823719906322389</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.502120307947411</v>
+        <v>3.220270959110237</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>3.218188409398735</v>
+        <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.692561993862606</v>
+        <v>-3.355699511532888</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.740807187539945</v>
+        <v>1.441766907165177</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4823719906322389</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.507611603778078</v>
+        <v>3.225762254940904</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>3.229685611167274</v>
+        <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.720342391763959</v>
+        <v>-3.383479909434241</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.741192230147943</v>
+        <v>1.442151949773175</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4545915927308858</v>
+        <v>0.707818133513354</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.502440566805805</v>
+        <v>3.220591217968631</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>3.068041331167927</v>
+        <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.838723064494097</v>
+        <v>-3.50186058216438</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.532195681056541</v>
+        <v>1.233155400681773</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3873737405799096</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.300465575515873</v>
+        <v>3.018616226678699</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>3.188190991887133</v>
+        <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.947337142937428</v>
+        <v>-3.610474660607711</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.608899710398414</v>
+        <v>1.309859430023646</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3873737405799096</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.420615236235078</v>
+        <v>3.138765887397904</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>3.202704017989455</v>
+        <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.911928104689285</v>
+        <v>-3.575065622359568</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.637576351799994</v>
+        <v>1.338536071425226</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3873737405799096</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.435128262337401</v>
+        <v>3.153278913500227</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>3.200123459331824</v>
+        <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.873544442131134</v>
+        <v>-3.536681959801417</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.650349258165623</v>
+        <v>1.351308977790855</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4257574031380608</v>
+        <v>0.678983943920529</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.455577901214661</v>
+        <v>3.173728552377487</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
-        <v>3.196852488177126</v>
+        <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.696428112095968</v>
+        <v>-3.359565629766251</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.717924819024992</v>
+        <v>1.418884538650224</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4257574031380608</v>
+        <v>0.678983943920529</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.452306930059963</v>
+        <v>3.170457581222789</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
-        <v>3.197535879939039</v>
+        <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.741520356929514</v>
+        <v>-3.404657874599796</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.700571312853486</v>
+        <v>1.401531032478718</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.363861359968671</v>
+        <v>0.6170879007511392</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.415852695920242</v>
+        <v>3.134003347083068</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
-        <v>3.191322855245454</v>
+        <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.562144935690746</v>
+        <v>-3.225282453361029</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.766108456655408</v>
+        <v>1.46706817628064</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5206381181393898</v>
+        <v>0.7738646589218579</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.503705726129088</v>
+        <v>3.221856377291914</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
-        <v>3.172130310577043</v>
+        <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.607159149211352</v>
+        <v>-3.270296666881635</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.728910226578755</v>
+        <v>1.429869946203987</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4902892228247852</v>
+        <v>0.7435157636072532</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.466303844271915</v>
+        <v>3.18445449543474</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>3.177821872915989</v>
+        <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.874163659483788</v>
+        <v>-3.53730117715407</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.627799984808727</v>
+        <v>1.328759704433959</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2959261847818366</v>
+        <v>0.5491527255643047</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.355377583785091</v>
+        <v>3.073528234947917</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>3.17702579481249</v>
+        <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.975361440920961</v>
+        <v>-3.638498958591243</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.586524794130359</v>
+        <v>1.287484513755591</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2275173712365174</v>
+        <v>0.4807439120189855</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.313536217554401</v>
+        <v>3.031686868717227</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>3.174625756366807</v>
+        <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.968850474306648</v>
+        <v>-3.63198799197693</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.586729142330401</v>
+        <v>1.287688861955633</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2275173712365174</v>
+        <v>0.4807439120189855</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.311136179108718</v>
+        <v>3.029286830271544</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
-        <v>3.171150475575052</v>
+        <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.949812346599351</v>
+        <v>-3.612949864269633</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.590869112621565</v>
+        <v>1.291828832246797</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1693337599053228</v>
+        <v>0.422560300687791</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.272750731518246</v>
+        <v>2.990901382681072</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>3.348732344513733</v>
+        <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.980938977749969</v>
+        <v>-3.644076495420251</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.756000329099998</v>
+        <v>1.45696004872523</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1693337599053228</v>
+        <v>0.422560300687791</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.450332600456927</v>
+        <v>3.168483251619753</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
-        <v>3.349565673499866</v>
+        <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.994805739083886</v>
+        <v>-3.657943256754169</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.751286953552565</v>
+        <v>1.452246673177797</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1314758431714999</v>
+        <v>0.3847023839539681</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.428451179402766</v>
+        <v>3.146601830565592</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.355574203896792</v>
+        <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.950001567543956</v>
+        <v>-3.613139085214239</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.775217152565463</v>
+        <v>1.476176872190694</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1314758431714999</v>
+        <v>0.3847023839539681</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.434459709799692</v>
+        <v>3.152610360962518</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.253524425173992</v>
+        <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.802258597308954</v>
+        <v>-3.465396114979236</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.732264561936663</v>
+        <v>1.433224281561895</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2992832004063831</v>
+        <v>0.5525097411888512</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.433094345417822</v>
+        <v>3.151244996580647</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.256318046705473</v>
+        <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.893302699509077</v>
+        <v>-3.567410797510457</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.698640542588095</v>
+        <v>1.395212030080887</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2992832004063831</v>
+        <v>0.5525097411888512</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.435887966949303</v>
+        <v>3.154038618112128</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.256980395097131</v>
+        <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.887149993456292</v>
+        <v>-3.561258091457673</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.701763973400867</v>
+        <v>1.39833546089366</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3054359064591674</v>
+        <v>0.5586624472416355</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.440241938972632</v>
+        <v>3.158392590135457</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.256060871837241</v>
+        <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.903959291606794</v>
+        <v>-3.578067389608174</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.694120730880776</v>
+        <v>1.390692218373569</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2886266083086657</v>
+        <v>0.5418531490911338</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.429236836822441</v>
+        <v>3.147387487985267</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.322396425634062</v>
+        <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.841661292830672</v>
+        <v>-3.515769390832053</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.785375484188046</v>
+        <v>1.481946971680839</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2886266083086657</v>
+        <v>0.5418531490911338</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.495572390619262</v>
+        <v>3.213723041782088</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>3.124688427348189</v>
+        <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.639871095165514</v>
+        <v>-3.313979193166895</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.668383564968236</v>
+        <v>1.364955052461029</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4866448004778201</v>
+        <v>0.7398713412602882</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.416675307634882</v>
+        <v>3.134825958797707</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
-        <v>3.194978659670364</v>
+        <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.475058092086667</v>
+        <v>-3.149166190088048</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.80459899852195</v>
+        <v>1.501170486014743</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.651457803556667</v>
+        <v>0.9046843443391351</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.585853341804365</v>
+        <v>3.304003992967191</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>3.209606395786408</v>
+        <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.572798636711641</v>
+        <v>-3.246906734713022</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.780130516788004</v>
+        <v>1.476702004280797</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6355685254236869</v>
+        <v>0.888795066206155</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.59094751104062</v>
+        <v>3.309098162203446</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>3.20814237661108</v>
+        <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.749136396834571</v>
+        <v>-3.423244494835951</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.708131393563504</v>
+        <v>1.404702881056297</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4592307653007575</v>
+        <v>0.7124573060832255</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.483680835791534</v>
+        <v>3.20183148695436</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>3.206633994651008</v>
+        <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.672714350402644</v>
+        <v>-3.346822448404025</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.737191830176203</v>
+        <v>1.433763317668996</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4592307653007575</v>
+        <v>0.7124573060832255</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.482172453831463</v>
+        <v>3.200323104994289</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>3.206496862086444</v>
+        <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.628341218764075</v>
+        <v>-3.302449316765456</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.754803950267067</v>
+        <v>1.45137543775986</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5036038969393262</v>
+        <v>0.7568304377217941</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.50865920025004</v>
+        <v>3.226809851412866</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>3.200890656225035</v>
+        <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.505506997876908</v>
+        <v>-3.179615095878288</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.798331432760525</v>
+        <v>1.494902920253317</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5036038969393262</v>
+        <v>0.7568304377217941</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.503052994388631</v>
+        <v>3.221203645551457</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
-        <v>3.20727241325284</v>
+        <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.457851267315852</v>
+        <v>-3.131959365317233</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.823775482012752</v>
+        <v>1.520346969505544</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5512596275003818</v>
+        <v>0.8044861682828498</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.538028189753069</v>
+        <v>3.256178840915895</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>3.212164786627564</v>
+        <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.357333108817097</v>
+        <v>-3.031441206818478</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.868875118786978</v>
+        <v>1.565446606279771</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6517777859991364</v>
+        <v>0.9050043267816044</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.603231458227047</v>
+        <v>3.321382109389872</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
-        <v>3.198919459103437</v>
+        <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.417999699219486</v>
+        <v>-3.092107797220867</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.831363155101895</v>
+        <v>1.527934642594688</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5700794692806027</v>
+        <v>0.8233060100630707</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.540967140671798</v>
+        <v>3.259117791834624</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>3.203017161714065</v>
+        <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.373161297611088</v>
+        <v>-3.047269395612469</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.853396218355883</v>
+        <v>1.549967705848675</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5746229022254722</v>
+        <v>0.8278494430079402</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.547790903049349</v>
+        <v>3.265941554212175</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>3.207178101345143</v>
+        <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.392659753853096</v>
+        <v>-3.066767851854477</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.849757775490157</v>
+        <v>1.54632926298295</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5265382609455679</v>
+        <v>0.7797648017280359</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.523101057912484</v>
+        <v>3.24125170907531</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>3.21305770387298</v>
+        <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.348456916767196</v>
+        <v>-3.022565014768577</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.873318512852355</v>
+        <v>1.569890000345147</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5707410980314683</v>
+        <v>0.8239676388139363</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.555502362691862</v>
+        <v>3.273653013854688</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>3.211467704342228</v>
+        <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.385435944430639</v>
+        <v>-3.05954404243202</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.856936902256225</v>
+        <v>1.553508389749018</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6077149998227989</v>
+        <v>0.8609415406052668</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.576096704235908</v>
+        <v>3.294247355398733</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>3.262715469525268</v>
+        <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.227144526891367</v>
+        <v>-2.901252624892748</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.971501234454974</v>
+        <v>1.668072721947766</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6077149998227989</v>
+        <v>0.8609415406052668</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.627344469418947</v>
+        <v>3.345495120581773</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321018</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>3.261156174119521</v>
+        <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.019502523256891</v>
+        <v>-2.693610621258272</v>
       </c>
       <c r="E1986" t="n">
-        <v>2.052998740503017</v>
+        <v>1.74957022799581</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.815357003457275</v>
+        <v>1.068583544239743</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.750370376193886</v>
+        <v>3.468521027356712</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>3.256104402357791</v>
+        <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.968470430534363</v>
+        <v>-2.642578528535743</v>
       </c>
       <c r="E1987" t="n">
-        <v>2.068359805830299</v>
+        <v>1.764931293323091</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.866389096179803</v>
+        <v>1.119615636962271</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.775937860065673</v>
+        <v>3.494088511228499</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>3.273291806450496</v>
+        <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.903246249407157</v>
+        <v>-2.577354347408538</v>
       </c>
       <c r="E1988" t="n">
-        <v>2.111636882373886</v>
+        <v>1.808208369866678</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9316132773070086</v>
+        <v>1.184839818089477</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.832259772834701</v>
+        <v>3.550410423997527</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>3.269252778749776</v>
+        <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.865819229336024</v>
+        <v>-2.539927327337404</v>
       </c>
       <c r="E1989" t="n">
-        <v>2.122568662701619</v>
+        <v>1.819140150194412</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9368648153361903</v>
+        <v>1.190091356118658</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.83137166795149</v>
+        <v>3.549522319114316</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>3.270509571081016</v>
+        <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.885930885370732</v>
+        <v>-2.560038983372113</v>
       </c>
       <c r="E1990" t="n">
-        <v>2.115780792618977</v>
+        <v>1.812352280111769</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9478921603336095</v>
+        <v>1.201118701116078</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.839244867281182</v>
+        <v>3.557395518444008</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.431067342102227</v>
+        <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.832186070943527</v>
+        <v>-2.506294168944908</v>
       </c>
       <c r="E1991" t="n">
-        <v>2.297836489411069</v>
+        <v>1.994407976903862</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9579554697740714</v>
+        <v>1.21118201055654</v>
       </c>
       <c r="G1991" t="n">
-        <v>4.00584062396667</v>
+        <v>3.723991275129496</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.551180251320044</v>
+        <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.757403809918515</v>
+        <v>-2.431511907919895</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.447862303038892</v>
+        <v>2.144433790531684</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.032737730799084</v>
+        <v>1.285964271581552</v>
       </c>
       <c r="G1992" t="n">
-        <v>4.170822889799495</v>
+        <v>3.888973540962321</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.542888227333903</v>
+        <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.731319725654707</v>
+        <v>-2.405427823656087</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.450003912758273</v>
+        <v>2.146575400251066</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.032737730799084</v>
+        <v>1.285964271581552</v>
       </c>
       <c r="G1993" t="n">
-        <v>4.162530865813354</v>
+        <v>3.88068151697618</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.541081422917683</v>
+        <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.65318854480576</v>
+        <v>-2.32729664280714</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.479449580681631</v>
+        <v>2.176021068174424</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.106914541682769</v>
+        <v>1.360141082465237</v>
       </c>
       <c r="G1994" t="n">
-        <v>4.205230147927344</v>
+        <v>3.92338079909017</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.558635828644474</v>
+        <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.644296083412477</v>
+        <v>-2.318404181413857</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.500560970965736</v>
+        <v>2.197132458458529</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.106914541682769</v>
+        <v>1.360141082465237</v>
       </c>
       <c r="G1995" t="n">
-        <v>4.222784553654136</v>
+        <v>3.940935204816961</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.550490876049058</v>
+        <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.812772200382355</v>
+        <v>-2.486880298383735</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.425025571582369</v>
+        <v>2.121597059075162</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.078966705966188</v>
+        <v>1.332193246748656</v>
       </c>
       <c r="G1996" t="n">
-        <v>4.197870899628771</v>
+        <v>3.916021550791597</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.53176057323692</v>
+        <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.114972671520771</v>
+        <v>-1.789080769522152</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.685415080314864</v>
+        <v>2.381986567807657</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.008618646595777</v>
+        <v>1.261845187378245</v>
       </c>
       <c r="G1997" t="n">
-        <v>4.136931761194386</v>
+        <v>3.855082412357213</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.522424595733824</v>
+        <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.092251567837619</v>
+        <v>-1.766359665839</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.68516754428503</v>
+        <v>2.381739031777823</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.008618646595777</v>
+        <v>1.261845187378245</v>
       </c>
       <c r="G1998" t="n">
-        <v>4.127595783691291</v>
+        <v>3.845746434854117</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.681330721584994</v>
+        <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.090526524547575</v>
+        <v>-1.764634622548956</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.844763687452216</v>
+        <v>2.541335174945009</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.010343689885821</v>
+        <v>1.263570230668289</v>
       </c>
       <c r="G1999" t="n">
-        <v>4.287536935516487</v>
+        <v>4.005687586679312</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.71840854407864</v>
+        <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.24530753132583</v>
+        <v>-1.919415629327211</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.819929107234561</v>
+        <v>2.516500594727353</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9769760158313447</v>
+        <v>1.230202556613813</v>
       </c>
       <c r="G2000" t="n">
-        <v>4.304594153577447</v>
+        <v>4.022744804740273</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.715083900068185</v>
+        <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.238252841110656</v>
+        <v>-1.912360939112037</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.819426339310175</v>
+        <v>2.515997826802968</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9840307060465185</v>
+        <v>1.237257246828987</v>
       </c>
       <c r="G2001" t="n">
-        <v>4.305502323696096</v>
+        <v>4.023652974858923</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.725090053712927</v>
+        <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.211301616784168</v>
+        <v>-1.885409714785549</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.840212982685512</v>
+        <v>2.536784470178305</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9989110520742377</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2002" t="n">
-        <v>4.32443668495747</v>
+        <v>4.042587336120295</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.909193185857887</v>
+        <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.347254624840485</v>
+        <v>-2.021362722841865</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.969934911607945</v>
+        <v>2.666506399100738</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9989110520742377</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.508539817102429</v>
+        <v>4.226690468265256</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.90130988076088</v>
+        <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.369662742645357</v>
+        <v>-2.043770840646737</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.95308835938899</v>
+        <v>2.649659846881783</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9989110520742377</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.500656512005422</v>
+        <v>4.218807163168249</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.903363880310517</v>
+        <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.517668510124756</v>
+        <v>-2.191776608126137</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.895940051946868</v>
+        <v>2.59251153943966</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9121840432106962</v>
+        <v>1.165410583993165</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.450674306236935</v>
+        <v>4.168824957399761</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.959617598032365</v>
+        <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.527109436013286</v>
+        <v>-2.201217534014667</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.948417399313303</v>
+        <v>2.644988886806095</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.034611160754088</v>
+        <v>1.287837701536556</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.580384294484817</v>
+        <v>4.298534945647643</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.962508692577666</v>
+        <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.579383043348928</v>
+        <v>-2.253491141350308</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.930399050924348</v>
+        <v>2.62697053841714</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9823375534184465</v>
+        <v>1.235564094200915</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.551911224628734</v>
+        <v>4.270061875791559</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.960620505471441</v>
+        <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.655713020949833</v>
+        <v>-2.329821118951214</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.89797887277776</v>
+        <v>2.594550360270552</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9823375534184465</v>
+        <v>1.235564094200915</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.550023037522509</v>
+        <v>4.268173688685335</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.955440735074303</v>
+        <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.767469973565134</v>
+        <v>-2.441578071566515</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.848096321334502</v>
+        <v>2.544667808827294</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8705806008031454</v>
+        <v>1.123807141585614</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.47778909555619</v>
+        <v>4.195939746719016</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.953874745284455</v>
+        <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.765628954506883</v>
+        <v>-2.439737052508264</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.847266739167955</v>
+        <v>2.543838226660747</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8718488274746138</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.476984041769224</v>
+        <v>4.195134692932049</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647101</v>
+        <v>3.754911907647106</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.966948152150374</v>
+        <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.897930246604437</v>
+        <v>-2.572038344605817</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.807419629194852</v>
+        <v>2.503991116687645</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8718488274746138</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.490057448635142</v>
+        <v>4.208208099797968</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763528</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.966948152150374</v>
+        <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.899491889419297</v>
+        <v>-2.573599987420677</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.806794972068908</v>
+        <v>2.5033664595617</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8718488274746138</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.490057448635142</v>
+        <v>4.208208099797968</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392111</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.965472193277376</v>
+        <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.92739267652877</v>
+        <v>-2.60150077453015</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.79415869835212</v>
+        <v>2.490730185844913</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.837251903331679</v>
+        <v>1.090478444114147</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.467823335276384</v>
+        <v>4.185973986439209</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172522</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.962236637254574</v>
+        <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.049918779231664</v>
+        <v>-2.724026877233044</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.741912701248162</v>
+        <v>2.438484188740954</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7147258006287851</v>
+        <v>0.9679523414112534</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.391072117631846</v>
+        <v>4.109222768794671</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971074</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>4.028942596845078</v>
+        <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.06998010050817</v>
+        <v>-2.744088198509551</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.800594132328063</v>
+        <v>2.497165619820855</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.694664479352278</v>
+        <v>0.9478910201347464</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.445741284456445</v>
+        <v>4.163891935619271</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199801</v>
+        <v>3.640764248199806</v>
       </c>
       <c r="C2016" t="n">
-        <v>4.169254315846925</v>
+        <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.326700918502994</v>
+        <v>-3.000809016504375</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.83821752413198</v>
+        <v>2.534789011624773</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5862499052084632</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.521004258972003</v>
+        <v>4.239154910134829</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622231</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>4.238234584992565</v>
+        <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.480687336279135</v>
+        <v>-3.154795434280516</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.845603226167164</v>
+        <v>2.542174713659956</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5862499052084632</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.589984528117643</v>
+        <v>4.308135179280469</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808524</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
-        <v>4.224285787112686</v>
+        <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.430165432451469</v>
+        <v>-3.10427353045285</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.851863189818351</v>
+        <v>2.548434677311143</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5862499052084632</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.576035730237765</v>
+        <v>4.29418638140059</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994889</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
-        <v>4.2361562761681</v>
+        <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.682640586459193</v>
+        <v>-3.356748684460574</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.762743617270676</v>
+        <v>2.459315104763468</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5862499052084632</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.587906219293179</v>
+        <v>4.306056870456004</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358293</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
-        <v>4.237366810687044</v>
+        <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.952113388380901</v>
+        <v>-3.626221486382282</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.656165031020937</v>
+        <v>2.352736518513728</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5862499052084632</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.589116753812123</v>
+        <v>4.307267404974947</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637082</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
-        <v>4.241488552914366</v>
+        <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.216127028206125</v>
+        <v>-3.783765558111723</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.554681317318169</v>
+        <v>2.293840632049273</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4986896940093016</v>
+        <v>0.7725746408506571</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.540702369319948</v>
+        <v>4.271248064118105</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301338</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
-        <v>4.236566405650556</v>
+        <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.344977578908171</v>
+        <v>-3.91261610881377</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.49821894977354</v>
+        <v>2.237378264504644</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4576962851585801</v>
+        <v>0.7315812319999355</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.511184176745704</v>
+        <v>4.24172987154386</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215465</v>
+        <v>3.667976467215469</v>
       </c>
       <c r="C2023" t="n">
-        <v>4.3987704623496</v>
+        <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.461945271547062</v>
+        <v>-4.029583801452661</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.613635929417028</v>
+        <v>2.352795244148131</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4576962851585801</v>
+        <v>0.7315812319999355</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.673388233444749</v>
+        <v>4.403933928242905</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456687</v>
+        <v>3.696553628456692</v>
       </c>
       <c r="C2024" t="n">
-        <v>4.393617100313414</v>
+        <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.546663213768015</v>
+        <v>-4.114301743673614</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.574595390492461</v>
+        <v>2.313754705223564</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3725802562305337</v>
+        <v>0.6464652030718891</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.617165254051735</v>
+        <v>4.347710948849891</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253283</v>
+        <v>3.750058176253288</v>
       </c>
       <c r="C2025" t="n">
-        <v>4.403846517881906</v>
+        <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.628598032036899</v>
+        <v>-4.196236561942498</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.552050880753399</v>
+        <v>2.291210195484503</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3626455106434535</v>
+        <v>0.636530457484809</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.621433824267978</v>
+        <v>4.351979519066135</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717827</v>
+        <v>3.783647027717832</v>
       </c>
       <c r="C2026" t="n">
-        <v>4.412772156337808</v>
+        <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.574859858636636</v>
+        <v>-4.142498388542236</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.582471788569406</v>
+        <v>2.321631103300509</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4163836840437156</v>
+        <v>0.6902686308850711</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.662602366764037</v>
+        <v>4.393148061562195</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616944</v>
+        <v>3.798310944616949</v>
       </c>
       <c r="C2027" t="n">
-        <v>4.404925043581984</v>
+        <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.464853575159415</v>
+        <v>-4.032492105065014</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.618627189204471</v>
+        <v>2.357786503935574</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4395882559609908</v>
+        <v>0.7134732028023463</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.668677997158579</v>
+        <v>4.399223691956735</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203658</v>
+        <v>3.785578085203664</v>
       </c>
       <c r="C2028" t="n">
-        <v>4.409175054303958</v>
+        <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.321793999418489</v>
+        <v>-3.889432529324088</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.680101030222815</v>
+        <v>2.419260344953919</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4476016825509701</v>
+        <v>0.7214866293923256</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.677736063834541</v>
+        <v>4.408281758632697</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436923</v>
+        <v>3.77725157243693</v>
       </c>
       <c r="C2029" t="n">
-        <v>4.416435937186495</v>
+        <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.020347273946651</v>
+        <v>-3.587985803852251</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.807940603294087</v>
+        <v>2.54709991802519</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7490484080228074</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.865864982000179</v>
+        <v>4.596410676798335</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064762</v>
+        <v>3.812650101064767</v>
       </c>
       <c r="C2030" t="n">
-        <v>4.417407114939205</v>
+        <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.075302470389721</v>
+        <v>-3.64294100029532</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.786929702469569</v>
+        <v>2.526089017200673</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7490484080228074</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.866836159752889</v>
+        <v>4.597381854551045</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859295</v>
+        <v>3.821198342859301</v>
       </c>
       <c r="C2031" t="n">
-        <v>4.41825001931896</v>
+        <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.0242640943832</v>
+        <v>-3.5919026242888</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.808187957251933</v>
+        <v>2.547347271983036</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7490484080228074</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.867679064132645</v>
+        <v>4.598224758930801</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354682</v>
+        <v>3.831748677354685</v>
       </c>
       <c r="C2032" t="n">
-        <v>4.437288118193106</v>
+        <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.372613608945848</v>
+        <v>-3.550763329422169</v>
       </c>
       <c r="E2032" t="n">
-        <v>3.087886250301019</v>
+        <v>2.582841088803834</v>
       </c>
       <c r="F2032" t="n">
-        <v>1.40069889346016</v>
+        <v>1.064072649730794</v>
       </c>
       <c r="G2032" t="n">
-        <v>5.277707454269201</v>
+        <v>4.641946434724925</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.835346054550117</v>
+        <v>3.811482327953734</v>
       </c>
       <c r="C2033" t="n">
-        <v>4.432276621145237</v>
+        <v>3.894242117794604</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.385186267143184</v>
+        <v>-3.455221423378677</v>
       </c>
       <c r="E2033" t="n">
-        <v>3.077845689974216</v>
+        <v>2.511797124129386</v>
       </c>
       <c r="F2033" t="n">
-        <v>1.388126235262824</v>
+        <v>1.072210665275704</v>
       </c>
       <c r="G2033" t="n">
-        <v>5.265152362302932</v>
+        <v>4.537568516960027</v>
       </c>
     </row>
   </sheetData>
